--- a/Info para Claude/Reportes/Empaque/PNG Reportes/Empaque_Hoy.xlsx
+++ b/Info para Claude/Reportes/Empaque/PNG Reportes/Empaque_Hoy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f087611319785eae/Documentos/GitHub/H2E-Crown/Info para Claude/Reportes/Empaque/PNG Reportes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{62FC8FF9-F488-46BD-B4C6-E467AFC29EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69C7143F-AD79-48A4-A6D1-03B22890F36D}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{62FC8FF9-F488-46BD-B4C6-E467AFC29EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{639F9143-B60B-4909-B9EA-F76D239B12C1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3C31BBD7-DEED-4F95-A4CD-7DCF87BD03C6}"/>
   </bookViews>
@@ -903,7 +903,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="204">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1146,69 +1146,6 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1226,6 +1163,70 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -1304,76 +1305,6 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls driveId="F087611319785EAE" itemId="F087611319785EAE!s7c1e8e829e4c4ea1bb203222ae643022">
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Liq"/>
-      <sheetName val="Liq-P&amp;P"/>
-      <sheetName val="Listado"/>
-      <sheetName val="Prom x Semana"/>
-      <sheetName val="Transacciones"/>
-      <sheetName val="Ing - Egr Pend"/>
-      <sheetName val="Reporte Semanal"/>
-      <sheetName val="VENTAS"/>
-      <sheetName val="Retorno x Cliente Nac"/>
-      <sheetName val="Hoja1"/>
-      <sheetName val="Pending 2 Inv (26-1)"/>
-      <sheetName val="GWR Transactions"/>
-      <sheetName val="Listado (2)"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>191554</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="1">
-          <cell r="T1">
-            <v>1532.432</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6">
-        <row r="74">
-          <cell r="C74">
-            <v>2.4123999999999999</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="C75">
-            <v>0.1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7">
-        <row r="2">
-          <cell r="G2">
-            <v>141942</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
       <xxl21:relativeUrl r:id="rId3"/>
@@ -1389,14 +1320,14 @@
       <sheetName val="Empaque (8)"/>
       <sheetName val="Empaque (9)"/>
       <sheetName val="Empaque (10)"/>
-      <sheetName val="Corte"/>
-      <sheetName val="p PDF"/>
       <sheetName val="Empaque (11)"/>
       <sheetName val="Empaque (12)"/>
       <sheetName val="Empaque (13)"/>
       <sheetName val="Empaque (14)"/>
       <sheetName val="Empaque (15)"/>
       <sheetName val="Empaque (16)"/>
+      <sheetName val="Corte"/>
+      <sheetName val="p PDF"/>
       <sheetName val="Empaque (17)"/>
       <sheetName val="Empaque (18)"/>
       <sheetName val="Empaque (19)"/>
@@ -2886,19 +2817,19 @@
         </row>
       </sheetData>
       <sheetData sheetId="9"/>
-      <sheetData sheetId="10">
-        <row r="7">
-          <cell r="J7">
-            <v>46134</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
+      <sheetData sheetId="16">
+        <row r="7">
+          <cell r="J7">
+            <v>46134</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
@@ -5824,6 +5755,70 @@
       </sheetData>
       <sheetData sheetId="92"/>
       <sheetData sheetId="93"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls driveId="F087611319785EAE" itemId="F087611319785EAE!s7c1e8e829e4c4ea1bb203222ae643022">
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Liq"/>
+      <sheetName val="Liq-P&amp;P"/>
+      <sheetName val="Listado"/>
+      <sheetName val="Prom x Semana"/>
+      <sheetName val="Transacciones"/>
+      <sheetName val="Ing - Egr Pend"/>
+      <sheetName val="Reporte Semanal"/>
+      <sheetName val="VENTAS"/>
+      <sheetName val="Retorno x Cliente Nac"/>
+      <sheetName val="Hoja1"/>
+      <sheetName val="Pending 2 Inv (26-1)"/>
+      <sheetName val="GWR Transactions"/>
+      <sheetName val="Listado (2)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>191554</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="1">
+          <cell r="T1">
+            <v>1532.432</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6">
+        <row r="74">
+          <cell r="C74">
+            <v>2.4123999999999999</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="C75">
+            <v>0.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -9513,18 +9508,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="176" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
+      <c r="A1" s="199" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="199"/>
+      <c r="C1" s="199"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="N1" s="2"/>
-      <c r="P1" s="177"/>
-      <c r="Q1" s="177"/>
-      <c r="R1" s="177"/>
+      <c r="P1" s="183"/>
+      <c r="Q1" s="183"/>
+      <c r="R1" s="183"/>
       <c r="S1" s="3"/>
       <c r="V1" s="4" t="s">
         <v>1</v>
@@ -9538,13 +9533,13 @@
       <c r="Y1" s="7"/>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="G2" s="178" t="s">
+      <c r="G2" s="200" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="178"/>
-      <c r="I2" s="178"/>
+      <c r="H2" s="200"/>
+      <c r="I2" s="200"/>
       <c r="J2" s="9">
-        <f>'[2]Empaque (9)'!K2</f>
+        <f>'[1]Empaque (9)'!K2</f>
         <v>9</v>
       </c>
       <c r="L2" s="10"/>
@@ -9568,15 +9563,15 @@
       <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="179" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="179"/>
-      <c r="D3" s="179"/>
+      <c r="B3" s="201" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="201"/>
+      <c r="D3" s="201"/>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
       <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+      <c r="M3" s="204"/>
       <c r="N3" s="16"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="17"/>
@@ -9593,21 +9588,21 @@
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="180"/>
-      <c r="C4" s="180"/>
+      <c r="B4" s="202"/>
+      <c r="C4" s="202"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="181">
-        <f>'[2]Empaque (9)'!H4</f>
+      <c r="G4" s="203">
+        <f>'[1]Empaque (9)'!H4</f>
         <v>46153</v>
       </c>
-      <c r="H4" s="181"/>
-      <c r="I4" s="181"/>
-      <c r="J4" s="181"/>
+      <c r="H4" s="203"/>
+      <c r="I4" s="203"/>
+      <c r="J4" s="203"/>
       <c r="L4" s="10"/>
       <c r="M4" s="18"/>
       <c r="N4" s="16"/>
@@ -9655,30 +9650,30 @@
       <c r="AI5" s="24"/>
     </row>
     <row r="6" spans="1:36" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="183" t="s">
+      <c r="A6" s="186" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="183" t="s">
+      <c r="B6" s="186" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="185" t="s">
+      <c r="C6" s="188" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="187" t="s">
+      <c r="D6" s="193" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="25"/>
-      <c r="F6" s="172" t="s">
+      <c r="F6" s="195" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="173"/>
-      <c r="H6" s="174"/>
+      <c r="G6" s="196"/>
+      <c r="H6" s="197"/>
       <c r="I6" s="26"/>
       <c r="J6" s="27"/>
-      <c r="K6" s="175"/>
+      <c r="K6" s="198"/>
       <c r="N6" s="28"/>
-      <c r="Q6" s="177"/>
-      <c r="R6" s="177"/>
+      <c r="Q6" s="183"/>
+      <c r="R6" s="183"/>
       <c r="V6" s="4" t="s">
         <v>17</v>
       </c>
@@ -9693,10 +9688,10 @@
       <c r="AI6" s="24"/>
     </row>
     <row r="7" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="184"/>
-      <c r="B7" s="184"/>
-      <c r="C7" s="186"/>
-      <c r="D7" s="188"/>
+      <c r="A7" s="187"/>
+      <c r="B7" s="187"/>
+      <c r="C7" s="189"/>
+      <c r="D7" s="194"/>
       <c r="E7" s="29" t="s">
         <v>18</v>
       </c>
@@ -9715,7 +9710,7 @@
       <c r="J7" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="175"/>
+      <c r="K7" s="198"/>
       <c r="M7" s="35"/>
       <c r="N7" s="36"/>
       <c r="P7" s="11"/>
@@ -9737,24 +9732,24 @@
       <c r="X7" s="39">
         <v>0</v>
       </c>
-      <c r="Z7" s="189" t="s">
+      <c r="Z7" s="184" t="s">
         <v>12</v>
       </c>
-      <c r="AA7" s="183" t="s">
+      <c r="AA7" s="186" t="s">
         <v>13</v>
       </c>
-      <c r="AB7" s="185" t="s">
+      <c r="AB7" s="188" t="s">
         <v>14</v>
       </c>
-      <c r="AC7" s="191" t="s">
+      <c r="AC7" s="190" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="182" t="s">
+      <c r="A8" s="192" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="182"/>
+      <c r="B8" s="192"/>
       <c r="M8" s="8"/>
       <c r="N8" s="36"/>
       <c r="P8" s="11"/>
@@ -9776,10 +9771,10 @@
       <c r="X8" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="Z8" s="190"/>
-      <c r="AA8" s="184"/>
-      <c r="AB8" s="186"/>
-      <c r="AC8" s="192"/>
+      <c r="Z8" s="185"/>
+      <c r="AA8" s="187"/>
+      <c r="AB8" s="189"/>
+      <c r="AC8" s="191"/>
       <c r="AH8" s="40" t="s">
         <v>16</v>
       </c>
@@ -9790,11 +9785,11 @@
     </row>
     <row r="9" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="41" t="str">
-        <f>'[2]Empaque (9)'!A9</f>
+        <f>'[1]Empaque (9)'!A9</f>
         <v>Campo Gusto x 72</v>
       </c>
       <c r="B9" s="42" t="str">
-        <f>'[2]Empaque (9)'!B9</f>
+        <f>'[1]Empaque (9)'!B9</f>
         <v>lb</v>
       </c>
       <c r="K9" s="43" t="s">
@@ -9809,11 +9804,11 @@
       <c r="N9" s="20"/>
       <c r="O9" s="20"/>
       <c r="Z9" s="41" t="str">
-        <f>'[2]Empaque (9)'!AA9</f>
+        <f>'[1]Empaque (9)'!AA9</f>
         <v>Campo Gusto x 72</v>
       </c>
       <c r="AA9" s="44" t="str">
-        <f>'[2]Empaque (9)'!AB9</f>
+        <f>'[1]Empaque (9)'!AB9</f>
         <v>lb</v>
       </c>
       <c r="AE9" s="6" t="s">
@@ -9831,43 +9826,43 @@
     </row>
     <row r="10" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="46" t="str">
-        <f>'[2]Empaque (9)'!A10</f>
+        <f>'[1]Empaque (9)'!A10</f>
         <v>Jb</v>
       </c>
       <c r="B10" s="47">
-        <f>'[2]Empaque (9)'!B10</f>
+        <f>'[1]Empaque (9)'!B10</f>
         <v>25</v>
       </c>
       <c r="C10" s="48">
-        <f>'[2]Empaque (9)'!C10</f>
+        <f>'[1]Empaque (9)'!C10</f>
         <v>0</v>
       </c>
       <c r="D10" s="49" t="str">
-        <f>'[2]Empaque (9)'!D10</f>
+        <f>'[1]Empaque (9)'!D10</f>
         <v/>
       </c>
       <c r="E10" s="50">
-        <f>'[2]Empaque (9)'!F10</f>
+        <f>'[1]Empaque (9)'!F10</f>
         <v>0</v>
       </c>
       <c r="F10" s="51">
-        <f>'[2]Empaque (9)'!G10</f>
+        <f>'[1]Empaque (9)'!G10</f>
         <v>0</v>
       </c>
       <c r="G10" s="52">
-        <f>'[2]Empaque (9)'!H10</f>
+        <f>'[1]Empaque (9)'!H10</f>
         <v>0</v>
       </c>
       <c r="H10" s="48">
-        <f>'[2]Empaque (9)'!I10</f>
+        <f>'[1]Empaque (9)'!I10</f>
         <v>0</v>
       </c>
       <c r="I10" s="53">
-        <f>'[2]Empaque (9)'!J10</f>
+        <f>'[1]Empaque (9)'!J10</f>
         <v>0</v>
       </c>
       <c r="J10" s="54">
-        <f>'[2]Empaque (9)'!K10</f>
+        <f>'[1]Empaque (9)'!K10</f>
         <v>0</v>
       </c>
       <c r="K10" s="55"/>
@@ -9900,19 +9895,19 @@
         <v>0</v>
       </c>
       <c r="Z10" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA10</f>
+        <f>'[1]Empaque (9)'!AA10</f>
         <v>Jb</v>
       </c>
       <c r="AA10" s="61">
-        <f>'[2]Empaque (9)'!AB10</f>
+        <f>'[1]Empaque (9)'!AB10</f>
         <v>25</v>
       </c>
       <c r="AB10" s="62">
-        <f>'[2]Empaque (9)'!AC10</f>
+        <f>'[1]Empaque (9)'!AC10</f>
         <v>0</v>
       </c>
       <c r="AC10" s="63">
-        <f>'[2]Empaque (9)'!AD10</f>
+        <f>'[1]Empaque (9)'!AD10</f>
         <v>0</v>
       </c>
       <c r="AG10" s="64"/>
@@ -9925,43 +9920,43 @@
     </row>
     <row r="11" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="46" t="str">
-        <f>'[2]Empaque (9)'!A11</f>
+        <f>'[1]Empaque (9)'!A11</f>
         <v>Xl</v>
       </c>
       <c r="B11" s="66">
-        <f>'[2]Empaque (9)'!B11</f>
+        <f>'[1]Empaque (9)'!B11</f>
         <v>25</v>
       </c>
       <c r="C11" s="67">
-        <f>'[2]Empaque (9)'!C11</f>
+        <f>'[1]Empaque (9)'!C11</f>
         <v>0</v>
       </c>
       <c r="D11" s="49" t="str">
-        <f>'[2]Empaque (9)'!D11</f>
+        <f>'[1]Empaque (9)'!D11</f>
         <v/>
       </c>
       <c r="E11" s="50">
-        <f>'[2]Empaque (9)'!F11</f>
+        <f>'[1]Empaque (9)'!F11</f>
         <v>0</v>
       </c>
       <c r="F11" s="51">
-        <f>'[2]Empaque (9)'!G11</f>
+        <f>'[1]Empaque (9)'!G11</f>
         <v>0</v>
       </c>
       <c r="G11" s="68">
-        <f>'[2]Empaque (9)'!H11</f>
+        <f>'[1]Empaque (9)'!H11</f>
         <v>0</v>
       </c>
       <c r="H11" s="67">
-        <f>'[2]Empaque (9)'!I11</f>
+        <f>'[1]Empaque (9)'!I11</f>
         <v>0</v>
       </c>
       <c r="I11" s="53">
-        <f>'[2]Empaque (9)'!J11</f>
+        <f>'[1]Empaque (9)'!J11</f>
         <v>0</v>
       </c>
       <c r="J11" s="54">
-        <f>'[2]Empaque (9)'!K11</f>
+        <f>'[1]Empaque (9)'!K11</f>
         <v>0</v>
       </c>
       <c r="K11" s="69"/>
@@ -9979,19 +9974,19 @@
       </c>
       <c r="S11" s="10"/>
       <c r="Z11" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA11</f>
+        <f>'[1]Empaque (9)'!AA11</f>
         <v>Xl</v>
       </c>
       <c r="AA11" s="72">
-        <f>'[2]Empaque (9)'!AB11</f>
+        <f>'[1]Empaque (9)'!AB11</f>
         <v>25</v>
       </c>
       <c r="AB11" s="62">
-        <f>'[2]Empaque (9)'!AC11</f>
+        <f>'[1]Empaque (9)'!AC11</f>
         <v>0</v>
       </c>
       <c r="AC11" s="63">
-        <f>'[2]Empaque (9)'!AD11</f>
+        <f>'[1]Empaque (9)'!AD11</f>
         <v>0</v>
       </c>
       <c r="AG11" s="73"/>
@@ -10004,43 +9999,43 @@
     </row>
     <row r="12" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="46" t="str">
-        <f>'[2]Empaque (9)'!A12</f>
+        <f>'[1]Empaque (9)'!A12</f>
         <v>Lg</v>
       </c>
       <c r="B12" s="47">
-        <f>'[2]Empaque (9)'!B12</f>
+        <f>'[1]Empaque (9)'!B12</f>
         <v>25</v>
       </c>
       <c r="C12" s="67">
-        <f>'[2]Empaque (9)'!C12</f>
+        <f>'[1]Empaque (9)'!C12</f>
         <v>0</v>
       </c>
       <c r="D12" s="49" t="str">
-        <f>'[2]Empaque (9)'!D12</f>
+        <f>'[1]Empaque (9)'!D12</f>
         <v/>
       </c>
       <c r="E12" s="50">
-        <f>'[2]Empaque (9)'!F12</f>
+        <f>'[1]Empaque (9)'!F12</f>
         <v>0</v>
       </c>
       <c r="F12" s="51">
-        <f>'[2]Empaque (9)'!G12</f>
+        <f>'[1]Empaque (9)'!G12</f>
         <v>0</v>
       </c>
       <c r="G12" s="68">
-        <f>'[2]Empaque (9)'!H12</f>
+        <f>'[1]Empaque (9)'!H12</f>
         <v>0</v>
       </c>
       <c r="H12" s="67">
-        <f>'[2]Empaque (9)'!I12</f>
+        <f>'[1]Empaque (9)'!I12</f>
         <v>0</v>
       </c>
       <c r="I12" s="53">
-        <f>'[2]Empaque (9)'!J12</f>
+        <f>'[1]Empaque (9)'!J12</f>
         <v>0</v>
       </c>
       <c r="J12" s="54">
-        <f>'[2]Empaque (9)'!K12</f>
+        <f>'[1]Empaque (9)'!K12</f>
         <v>0</v>
       </c>
       <c r="K12" s="69"/>
@@ -10058,19 +10053,19 @@
       </c>
       <c r="S12" s="10"/>
       <c r="Z12" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA12</f>
+        <f>'[1]Empaque (9)'!AA12</f>
         <v>Lg</v>
       </c>
       <c r="AA12" s="61">
-        <f>'[2]Empaque (9)'!AB12</f>
+        <f>'[1]Empaque (9)'!AB12</f>
         <v>25</v>
       </c>
       <c r="AB12" s="62">
-        <f>'[2]Empaque (9)'!AC12</f>
+        <f>'[1]Empaque (9)'!AC12</f>
         <v>0</v>
       </c>
       <c r="AC12" s="63">
-        <f>'[2]Empaque (9)'!AD12</f>
+        <f>'[1]Empaque (9)'!AD12</f>
         <v>0</v>
       </c>
       <c r="AG12" s="73"/>
@@ -10083,43 +10078,43 @@
     </row>
     <row r="13" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="46" t="str">
-        <f>'[2]Empaque (9)'!A13</f>
+        <f>'[1]Empaque (9)'!A13</f>
         <v>Md</v>
       </c>
       <c r="B13" s="66">
-        <f>'[2]Empaque (9)'!B13</f>
+        <f>'[1]Empaque (9)'!B13</f>
         <v>25</v>
       </c>
       <c r="C13" s="67">
-        <f>'[2]Empaque (9)'!C13</f>
+        <f>'[1]Empaque (9)'!C13</f>
         <v>0</v>
       </c>
       <c r="D13" s="49" t="str">
-        <f>'[2]Empaque (9)'!D13</f>
+        <f>'[1]Empaque (9)'!D13</f>
         <v/>
       </c>
       <c r="E13" s="50">
-        <f>'[2]Empaque (9)'!F13</f>
+        <f>'[1]Empaque (9)'!F13</f>
         <v>0</v>
       </c>
       <c r="F13" s="51">
-        <f>'[2]Empaque (9)'!G13</f>
+        <f>'[1]Empaque (9)'!G13</f>
         <v>0</v>
       </c>
       <c r="G13" s="68">
-        <f>'[2]Empaque (9)'!H13</f>
+        <f>'[1]Empaque (9)'!H13</f>
         <v>0</v>
       </c>
       <c r="H13" s="67">
-        <f>'[2]Empaque (9)'!I13</f>
+        <f>'[1]Empaque (9)'!I13</f>
         <v>0</v>
       </c>
       <c r="I13" s="53">
-        <f>'[2]Empaque (9)'!J13</f>
+        <f>'[1]Empaque (9)'!J13</f>
         <v>0</v>
       </c>
       <c r="J13" s="54">
-        <f>'[2]Empaque (9)'!K13</f>
+        <f>'[1]Empaque (9)'!K13</f>
         <v>0</v>
       </c>
       <c r="K13" s="69"/>
@@ -10137,19 +10132,19 @@
       </c>
       <c r="S13" s="10"/>
       <c r="Z13" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA13</f>
+        <f>'[1]Empaque (9)'!AA13</f>
         <v>Md</v>
       </c>
       <c r="AA13" s="72">
-        <f>'[2]Empaque (9)'!AB13</f>
+        <f>'[1]Empaque (9)'!AB13</f>
         <v>25</v>
       </c>
       <c r="AB13" s="62">
-        <f>'[2]Empaque (9)'!AC13</f>
+        <f>'[1]Empaque (9)'!AC13</f>
         <v>0</v>
       </c>
       <c r="AC13" s="63">
-        <f>'[2]Empaque (9)'!AD13</f>
+        <f>'[1]Empaque (9)'!AD13</f>
         <v>0</v>
       </c>
       <c r="AG13" s="73"/>
@@ -10162,43 +10157,43 @@
     </row>
     <row r="14" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="46" t="str">
-        <f>'[2]Empaque (9)'!A14</f>
+        <f>'[1]Empaque (9)'!A14</f>
         <v>Sm</v>
       </c>
       <c r="B14" s="47">
-        <f>'[2]Empaque (9)'!B14</f>
+        <f>'[1]Empaque (9)'!B14</f>
         <v>25</v>
       </c>
       <c r="C14" s="67">
-        <f>'[2]Empaque (9)'!C14</f>
+        <f>'[1]Empaque (9)'!C14</f>
         <v>0</v>
       </c>
       <c r="D14" s="49" t="str">
-        <f>'[2]Empaque (9)'!D14</f>
+        <f>'[1]Empaque (9)'!D14</f>
         <v/>
       </c>
       <c r="E14" s="50">
-        <f>'[2]Empaque (9)'!F14</f>
+        <f>'[1]Empaque (9)'!F14</f>
         <v>0</v>
       </c>
       <c r="F14" s="51">
-        <f>'[2]Empaque (9)'!G14</f>
+        <f>'[1]Empaque (9)'!G14</f>
         <v>0</v>
       </c>
       <c r="G14" s="68">
-        <f>'[2]Empaque (9)'!H14</f>
+        <f>'[1]Empaque (9)'!H14</f>
         <v>0</v>
       </c>
       <c r="H14" s="67">
-        <f>'[2]Empaque (9)'!I14</f>
+        <f>'[1]Empaque (9)'!I14</f>
         <v>0</v>
       </c>
       <c r="I14" s="53">
-        <f>'[2]Empaque (9)'!J14</f>
+        <f>'[1]Empaque (9)'!J14</f>
         <v>0</v>
       </c>
       <c r="J14" s="54">
-        <f>'[2]Empaque (9)'!K14</f>
+        <f>'[1]Empaque (9)'!K14</f>
         <v>0</v>
       </c>
       <c r="K14" s="69"/>
@@ -10216,19 +10211,19 @@
       </c>
       <c r="S14" s="10"/>
       <c r="Z14" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA14</f>
+        <f>'[1]Empaque (9)'!AA14</f>
         <v>Sm</v>
       </c>
       <c r="AA14" s="61">
-        <f>'[2]Empaque (9)'!AB14</f>
+        <f>'[1]Empaque (9)'!AB14</f>
         <v>25</v>
       </c>
       <c r="AB14" s="77">
-        <f>'[2]Empaque (9)'!AC14</f>
+        <f>'[1]Empaque (9)'!AC14</f>
         <v>0</v>
       </c>
       <c r="AC14" s="63">
-        <f>'[2]Empaque (9)'!AD14</f>
+        <f>'[1]Empaque (9)'!AD14</f>
         <v>0</v>
       </c>
       <c r="AG14" s="64"/>
@@ -10241,43 +10236,43 @@
     </row>
     <row r="15" spans="1:36" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="79" t="str">
-        <f>'[2]Empaque (9)'!A15</f>
+        <f>'[1]Empaque (9)'!A15</f>
         <v>Mixto</v>
       </c>
       <c r="B15" s="80">
-        <f>'[2]Empaque (9)'!B15</f>
+        <f>'[1]Empaque (9)'!B15</f>
         <v>25</v>
       </c>
       <c r="C15" s="81">
-        <f>'[2]Empaque (9)'!C15</f>
+        <f>'[1]Empaque (9)'!C15</f>
         <v>0</v>
       </c>
       <c r="D15" s="82" t="str">
-        <f>'[2]Empaque (9)'!D15</f>
+        <f>'[1]Empaque (9)'!D15</f>
         <v/>
       </c>
       <c r="E15" s="83">
-        <f>'[2]Empaque (9)'!F15</f>
+        <f>'[1]Empaque (9)'!F15</f>
         <v>0</v>
       </c>
       <c r="F15" s="84">
-        <f>'[2]Empaque (9)'!G15</f>
+        <f>'[1]Empaque (9)'!G15</f>
         <v>0</v>
       </c>
       <c r="G15" s="85">
-        <f>'[2]Empaque (9)'!H15</f>
+        <f>'[1]Empaque (9)'!H15</f>
         <v>0</v>
       </c>
       <c r="H15" s="81">
-        <f>'[2]Empaque (9)'!I15</f>
+        <f>'[1]Empaque (9)'!I15</f>
         <v>0</v>
       </c>
       <c r="I15" s="86">
-        <f>'[2]Empaque (9)'!J15</f>
+        <f>'[1]Empaque (9)'!J15</f>
         <v>0</v>
       </c>
       <c r="J15" s="87">
-        <f>'[2]Empaque (9)'!K15</f>
+        <f>'[1]Empaque (9)'!K15</f>
         <v>0</v>
       </c>
       <c r="K15" s="88"/>
@@ -10295,19 +10290,19 @@
       </c>
       <c r="S15" s="10"/>
       <c r="Z15" s="90" t="str">
-        <f>'[2]Empaque (9)'!AA15</f>
+        <f>'[1]Empaque (9)'!AA15</f>
         <v>xs</v>
       </c>
       <c r="AA15" s="91">
-        <f>'[2]Empaque (9)'!AB15</f>
+        <f>'[1]Empaque (9)'!AB15</f>
         <v>25</v>
       </c>
       <c r="AB15" s="92">
-        <f>'[2]Empaque (9)'!AC15</f>
+        <f>'[1]Empaque (9)'!AC15</f>
         <v>0</v>
       </c>
       <c r="AC15" s="93">
-        <f>'[2]Empaque (9)'!AD15</f>
+        <f>'[1]Empaque (9)'!AD15</f>
         <v>0</v>
       </c>
       <c r="AG15" s="94"/>
@@ -10320,35 +10315,35 @@
     </row>
     <row r="16" spans="1:36" ht="15" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C16" s="96">
-        <f>'[2]Empaque (9)'!C16</f>
+        <f>'[1]Empaque (9)'!C16</f>
         <v>0</v>
       </c>
       <c r="D16" s="97" t="str">
-        <f>'[2]Empaque (9)'!D16</f>
+        <f>'[1]Empaque (9)'!D16</f>
         <v/>
       </c>
       <c r="E16" s="98">
-        <f>'[2]Empaque (9)'!F16</f>
+        <f>'[1]Empaque (9)'!F16</f>
         <v>0</v>
       </c>
       <c r="F16" s="99">
-        <f>'[2]Empaque (9)'!G16</f>
+        <f>'[1]Empaque (9)'!G16</f>
         <v>0</v>
       </c>
       <c r="G16" s="100">
-        <f>'[2]Empaque (9)'!H16</f>
+        <f>'[1]Empaque (9)'!H16</f>
         <v>0</v>
       </c>
       <c r="H16" s="100">
-        <f>'[2]Empaque (9)'!I16</f>
+        <f>'[1]Empaque (9)'!I16</f>
         <v>0</v>
       </c>
       <c r="I16" s="100">
-        <f>'[2]Empaque (9)'!J16</f>
+        <f>'[1]Empaque (9)'!J16</f>
         <v>0</v>
       </c>
       <c r="J16" s="101">
-        <f>'[2]Empaque (9)'!K16</f>
+        <f>'[1]Empaque (9)'!K16</f>
         <v>0</v>
       </c>
       <c r="K16" s="102">
@@ -10367,11 +10362,11 @@
       <c r="S16" s="10"/>
       <c r="AA16" s="104"/>
       <c r="AB16" s="105">
-        <f>'[2]Empaque (9)'!AC16</f>
+        <f>'[1]Empaque (9)'!AC16</f>
         <v>0</v>
       </c>
       <c r="AC16" s="106">
-        <f>'[2]Empaque (9)'!AD16</f>
+        <f>'[1]Empaque (9)'!AD16</f>
         <v>0</v>
       </c>
       <c r="AH16" s="107">
@@ -10386,11 +10381,11 @@
     </row>
     <row r="17" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="41" t="str">
-        <f>'[2]Empaque (9)'!A17</f>
+        <f>'[1]Empaque (9)'!A17</f>
         <v>H2E (2da) x 72</v>
       </c>
       <c r="B17" s="42" t="str">
-        <f>'[2]Empaque (9)'!B17</f>
+        <f>'[1]Empaque (9)'!B17</f>
         <v>lb</v>
       </c>
       <c r="C17" s="109"/>
@@ -10412,11 +10407,11 @@
       <c r="P17" s="58"/>
       <c r="S17" s="10"/>
       <c r="Z17" s="41" t="str">
-        <f>'[2]Empaque (9)'!AA17</f>
+        <f>'[1]Empaque (9)'!AA17</f>
         <v>H2E (2da) x 72</v>
       </c>
       <c r="AA17" s="44" t="str">
-        <f>'[2]Empaque (9)'!AB17</f>
+        <f>'[1]Empaque (9)'!AB17</f>
         <v>lb</v>
       </c>
       <c r="AE17" s="6" t="s">
@@ -10430,43 +10425,43 @@
     </row>
     <row r="18" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="46" t="str">
-        <f>'[2]Empaque (9)'!A18</f>
+        <f>'[1]Empaque (9)'!A18</f>
         <v>Jb</v>
       </c>
       <c r="B18" s="47">
-        <f>'[2]Empaque (9)'!B18</f>
+        <f>'[1]Empaque (9)'!B18</f>
         <v>25</v>
       </c>
       <c r="C18" s="48">
-        <f>'[2]Empaque (9)'!C18</f>
+        <f>'[1]Empaque (9)'!C18</f>
         <v>0</v>
       </c>
       <c r="D18" s="49" t="str">
-        <f>'[2]Empaque (9)'!D18</f>
+        <f>'[1]Empaque (9)'!D18</f>
         <v/>
       </c>
       <c r="E18" s="50">
-        <f>'[2]Empaque (9)'!F18</f>
+        <f>'[1]Empaque (9)'!F18</f>
         <v>0</v>
       </c>
       <c r="F18" s="51">
-        <f>'[2]Empaque (9)'!G18</f>
+        <f>'[1]Empaque (9)'!G18</f>
         <v>0</v>
       </c>
       <c r="G18" s="52">
-        <f>'[2]Empaque (9)'!H18</f>
+        <f>'[1]Empaque (9)'!H18</f>
         <v>0</v>
       </c>
       <c r="H18" s="48">
-        <f>'[2]Empaque (9)'!I18</f>
+        <f>'[1]Empaque (9)'!I18</f>
         <v>0</v>
       </c>
       <c r="I18" s="53">
-        <f>'[2]Empaque (9)'!J18</f>
+        <f>'[1]Empaque (9)'!J18</f>
         <v>0</v>
       </c>
       <c r="J18" s="54">
-        <f>'[2]Empaque (9)'!K18</f>
+        <f>'[1]Empaque (9)'!K18</f>
         <v>0</v>
       </c>
       <c r="K18" s="55"/>
@@ -10499,19 +10494,19 @@
         <v>0</v>
       </c>
       <c r="Z18" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA18</f>
+        <f>'[1]Empaque (9)'!AA18</f>
         <v>Jb</v>
       </c>
       <c r="AA18" s="61">
-        <f>'[2]Empaque (9)'!AB18</f>
+        <f>'[1]Empaque (9)'!AB18</f>
         <v>25</v>
       </c>
       <c r="AB18" s="62">
-        <f>'[2]Empaque (9)'!AC18</f>
+        <f>'[1]Empaque (9)'!AC18</f>
         <v>0</v>
       </c>
       <c r="AC18" s="63">
-        <f>'[2]Empaque (9)'!AD18</f>
+        <f>'[1]Empaque (9)'!AD18</f>
         <v>0</v>
       </c>
       <c r="AG18" s="64"/>
@@ -10524,43 +10519,43 @@
     </row>
     <row r="19" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="46" t="str">
-        <f>'[2]Empaque (9)'!A19</f>
+        <f>'[1]Empaque (9)'!A19</f>
         <v>Xl</v>
       </c>
       <c r="B19" s="66">
-        <f>'[2]Empaque (9)'!B19</f>
+        <f>'[1]Empaque (9)'!B19</f>
         <v>25</v>
       </c>
       <c r="C19" s="67">
-        <f>'[2]Empaque (9)'!C19</f>
+        <f>'[1]Empaque (9)'!C19</f>
         <v>0</v>
       </c>
       <c r="D19" s="49" t="str">
-        <f>'[2]Empaque (9)'!D19</f>
+        <f>'[1]Empaque (9)'!D19</f>
         <v/>
       </c>
       <c r="E19" s="50">
-        <f>'[2]Empaque (9)'!F19</f>
+        <f>'[1]Empaque (9)'!F19</f>
         <v>0</v>
       </c>
       <c r="F19" s="51">
-        <f>'[2]Empaque (9)'!G19</f>
+        <f>'[1]Empaque (9)'!G19</f>
         <v>0</v>
       </c>
       <c r="G19" s="68">
-        <f>'[2]Empaque (9)'!H19</f>
+        <f>'[1]Empaque (9)'!H19</f>
         <v>0</v>
       </c>
       <c r="H19" s="67">
-        <f>'[2]Empaque (9)'!I19</f>
+        <f>'[1]Empaque (9)'!I19</f>
         <v>0</v>
       </c>
       <c r="I19" s="53">
-        <f>'[2]Empaque (9)'!J19</f>
+        <f>'[1]Empaque (9)'!J19</f>
         <v>0</v>
       </c>
       <c r="J19" s="54">
-        <f>'[2]Empaque (9)'!K19</f>
+        <f>'[1]Empaque (9)'!K19</f>
         <v>0</v>
       </c>
       <c r="K19" s="69"/>
@@ -10578,19 +10573,19 @@
       </c>
       <c r="S19" s="10"/>
       <c r="Z19" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA19</f>
+        <f>'[1]Empaque (9)'!AA19</f>
         <v>Xl</v>
       </c>
       <c r="AA19" s="72">
-        <f>'[2]Empaque (9)'!AB19</f>
+        <f>'[1]Empaque (9)'!AB19</f>
         <v>25</v>
       </c>
       <c r="AB19" s="62">
-        <f>'[2]Empaque (9)'!AC19</f>
+        <f>'[1]Empaque (9)'!AC19</f>
         <v>0</v>
       </c>
       <c r="AC19" s="63">
-        <f>'[2]Empaque (9)'!AD19</f>
+        <f>'[1]Empaque (9)'!AD19</f>
         <v>0</v>
       </c>
       <c r="AG19" s="73"/>
@@ -10603,43 +10598,43 @@
     </row>
     <row r="20" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="46" t="str">
-        <f>'[2]Empaque (9)'!A20</f>
+        <f>'[1]Empaque (9)'!A20</f>
         <v>Lg</v>
       </c>
       <c r="B20" s="47">
-        <f>'[2]Empaque (9)'!B20</f>
+        <f>'[1]Empaque (9)'!B20</f>
         <v>25</v>
       </c>
       <c r="C20" s="67">
-        <f>'[2]Empaque (9)'!C20</f>
+        <f>'[1]Empaque (9)'!C20</f>
         <v>0</v>
       </c>
       <c r="D20" s="49" t="str">
-        <f>'[2]Empaque (9)'!D20</f>
+        <f>'[1]Empaque (9)'!D20</f>
         <v/>
       </c>
       <c r="E20" s="50">
-        <f>'[2]Empaque (9)'!F20</f>
+        <f>'[1]Empaque (9)'!F20</f>
         <v>0</v>
       </c>
       <c r="F20" s="51">
-        <f>'[2]Empaque (9)'!G20</f>
+        <f>'[1]Empaque (9)'!G20</f>
         <v>0</v>
       </c>
       <c r="G20" s="68">
-        <f>'[2]Empaque (9)'!H20</f>
+        <f>'[1]Empaque (9)'!H20</f>
         <v>0</v>
       </c>
       <c r="H20" s="67">
-        <f>'[2]Empaque (9)'!I20</f>
+        <f>'[1]Empaque (9)'!I20</f>
         <v>0</v>
       </c>
       <c r="I20" s="53">
-        <f>'[2]Empaque (9)'!J20</f>
+        <f>'[1]Empaque (9)'!J20</f>
         <v>0</v>
       </c>
       <c r="J20" s="54">
-        <f>'[2]Empaque (9)'!K20</f>
+        <f>'[1]Empaque (9)'!K20</f>
         <v>0</v>
       </c>
       <c r="K20" s="69"/>
@@ -10657,19 +10652,19 @@
       </c>
       <c r="S20" s="10"/>
       <c r="Z20" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA20</f>
+        <f>'[1]Empaque (9)'!AA20</f>
         <v>Lg</v>
       </c>
       <c r="AA20" s="61">
-        <f>'[2]Empaque (9)'!AB20</f>
+        <f>'[1]Empaque (9)'!AB20</f>
         <v>25</v>
       </c>
       <c r="AB20" s="62">
-        <f>'[2]Empaque (9)'!AC20</f>
+        <f>'[1]Empaque (9)'!AC20</f>
         <v>0</v>
       </c>
       <c r="AC20" s="63">
-        <f>'[2]Empaque (9)'!AD20</f>
+        <f>'[1]Empaque (9)'!AD20</f>
         <v>0</v>
       </c>
       <c r="AG20" s="73"/>
@@ -10682,43 +10677,43 @@
     </row>
     <row r="21" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="46" t="str">
-        <f>'[2]Empaque (9)'!A21</f>
+        <f>'[1]Empaque (9)'!A21</f>
         <v>Md</v>
       </c>
       <c r="B21" s="66">
-        <f>'[2]Empaque (9)'!B21</f>
+        <f>'[1]Empaque (9)'!B21</f>
         <v>25</v>
       </c>
       <c r="C21" s="67">
-        <f>'[2]Empaque (9)'!C21</f>
+        <f>'[1]Empaque (9)'!C21</f>
         <v>0</v>
       </c>
       <c r="D21" s="49" t="str">
-        <f>'[2]Empaque (9)'!D21</f>
+        <f>'[1]Empaque (9)'!D21</f>
         <v/>
       </c>
       <c r="E21" s="50">
-        <f>'[2]Empaque (9)'!F21</f>
+        <f>'[1]Empaque (9)'!F21</f>
         <v>0</v>
       </c>
       <c r="F21" s="51">
-        <f>'[2]Empaque (9)'!G21</f>
+        <f>'[1]Empaque (9)'!G21</f>
         <v>0</v>
       </c>
       <c r="G21" s="68">
-        <f>'[2]Empaque (9)'!H21</f>
+        <f>'[1]Empaque (9)'!H21</f>
         <v>0</v>
       </c>
       <c r="H21" s="67">
-        <f>'[2]Empaque (9)'!I21</f>
+        <f>'[1]Empaque (9)'!I21</f>
         <v>0</v>
       </c>
       <c r="I21" s="53">
-        <f>'[2]Empaque (9)'!J21</f>
+        <f>'[1]Empaque (9)'!J21</f>
         <v>0</v>
       </c>
       <c r="J21" s="54">
-        <f>'[2]Empaque (9)'!K21</f>
+        <f>'[1]Empaque (9)'!K21</f>
         <v>0</v>
       </c>
       <c r="K21" s="69"/>
@@ -10736,19 +10731,19 @@
       </c>
       <c r="S21" s="10"/>
       <c r="Z21" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA21</f>
+        <f>'[1]Empaque (9)'!AA21</f>
         <v>Md</v>
       </c>
       <c r="AA21" s="72">
-        <f>'[2]Empaque (9)'!AB21</f>
+        <f>'[1]Empaque (9)'!AB21</f>
         <v>25</v>
       </c>
       <c r="AB21" s="62">
-        <f>'[2]Empaque (9)'!AC21</f>
+        <f>'[1]Empaque (9)'!AC21</f>
         <v>0</v>
       </c>
       <c r="AC21" s="63">
-        <f>'[2]Empaque (9)'!AD21</f>
+        <f>'[1]Empaque (9)'!AD21</f>
         <v>0</v>
       </c>
       <c r="AG21" s="73"/>
@@ -10761,43 +10756,43 @@
     </row>
     <row r="22" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="46" t="str">
-        <f>'[2]Empaque (9)'!A22</f>
+        <f>'[1]Empaque (9)'!A22</f>
         <v>Sm</v>
       </c>
       <c r="B22" s="47">
-        <f>'[2]Empaque (9)'!B22</f>
+        <f>'[1]Empaque (9)'!B22</f>
         <v>25</v>
       </c>
       <c r="C22" s="67">
-        <f>'[2]Empaque (9)'!C22</f>
+        <f>'[1]Empaque (9)'!C22</f>
         <v>0</v>
       </c>
       <c r="D22" s="49" t="str">
-        <f>'[2]Empaque (9)'!D22</f>
+        <f>'[1]Empaque (9)'!D22</f>
         <v/>
       </c>
       <c r="E22" s="50">
-        <f>'[2]Empaque (9)'!F22</f>
+        <f>'[1]Empaque (9)'!F22</f>
         <v>0</v>
       </c>
       <c r="F22" s="51">
-        <f>'[2]Empaque (9)'!G22</f>
+        <f>'[1]Empaque (9)'!G22</f>
         <v>0</v>
       </c>
       <c r="G22" s="68">
-        <f>'[2]Empaque (9)'!H22</f>
+        <f>'[1]Empaque (9)'!H22</f>
         <v>0</v>
       </c>
       <c r="H22" s="67">
-        <f>'[2]Empaque (9)'!I22</f>
+        <f>'[1]Empaque (9)'!I22</f>
         <v>0</v>
       </c>
       <c r="I22" s="53">
-        <f>'[2]Empaque (9)'!J22</f>
+        <f>'[1]Empaque (9)'!J22</f>
         <v>0</v>
       </c>
       <c r="J22" s="54">
-        <f>'[2]Empaque (9)'!K22</f>
+        <f>'[1]Empaque (9)'!K22</f>
         <v>0</v>
       </c>
       <c r="K22" s="69"/>
@@ -10815,19 +10810,19 @@
       </c>
       <c r="S22" s="10"/>
       <c r="Z22" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA22</f>
+        <f>'[1]Empaque (9)'!AA22</f>
         <v>Sm</v>
       </c>
       <c r="AA22" s="61">
-        <f>'[2]Empaque (9)'!AB22</f>
+        <f>'[1]Empaque (9)'!AB22</f>
         <v>25</v>
       </c>
       <c r="AB22" s="77">
-        <f>'[2]Empaque (9)'!AC22</f>
+        <f>'[1]Empaque (9)'!AC22</f>
         <v>0</v>
       </c>
       <c r="AC22" s="63">
-        <f>'[2]Empaque (9)'!AD22</f>
+        <f>'[1]Empaque (9)'!AD22</f>
         <v>0</v>
       </c>
       <c r="AG22" s="64"/>
@@ -10840,43 +10835,43 @@
     </row>
     <row r="23" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="79" t="str">
-        <f>'[2]Empaque (9)'!A23</f>
+        <f>'[1]Empaque (9)'!A23</f>
         <v>Mixto</v>
       </c>
       <c r="B23" s="80">
-        <f>'[2]Empaque (9)'!B23</f>
+        <f>'[1]Empaque (9)'!B23</f>
         <v>25</v>
       </c>
       <c r="C23" s="81">
-        <f>'[2]Empaque (9)'!C23</f>
+        <f>'[1]Empaque (9)'!C23</f>
         <v>0</v>
       </c>
       <c r="D23" s="82" t="str">
-        <f>'[2]Empaque (9)'!D23</f>
+        <f>'[1]Empaque (9)'!D23</f>
         <v/>
       </c>
       <c r="E23" s="83">
-        <f>'[2]Empaque (9)'!F23</f>
+        <f>'[1]Empaque (9)'!F23</f>
         <v>0</v>
       </c>
       <c r="F23" s="84">
-        <f>'[2]Empaque (9)'!G23</f>
+        <f>'[1]Empaque (9)'!G23</f>
         <v>0</v>
       </c>
       <c r="G23" s="85">
-        <f>'[2]Empaque (9)'!H23</f>
+        <f>'[1]Empaque (9)'!H23</f>
         <v>0</v>
       </c>
       <c r="H23" s="81">
-        <f>'[2]Empaque (9)'!I23</f>
+        <f>'[1]Empaque (9)'!I23</f>
         <v>0</v>
       </c>
       <c r="I23" s="86">
-        <f>'[2]Empaque (9)'!J23</f>
+        <f>'[1]Empaque (9)'!J23</f>
         <v>0</v>
       </c>
       <c r="J23" s="87">
-        <f>'[2]Empaque (9)'!K23</f>
+        <f>'[1]Empaque (9)'!K23</f>
         <v>0</v>
       </c>
       <c r="K23" s="88"/>
@@ -10895,19 +10890,19 @@
       </c>
       <c r="S23" s="10"/>
       <c r="Z23" s="90" t="str">
-        <f>'[2]Empaque (9)'!AA23</f>
+        <f>'[1]Empaque (9)'!AA23</f>
         <v>xs</v>
       </c>
       <c r="AA23" s="91">
-        <f>'[2]Empaque (9)'!AB23</f>
+        <f>'[1]Empaque (9)'!AB23</f>
         <v>25</v>
       </c>
       <c r="AB23" s="92">
-        <f>'[2]Empaque (9)'!AC23</f>
+        <f>'[1]Empaque (9)'!AC23</f>
         <v>0</v>
       </c>
       <c r="AC23" s="93">
-        <f>'[2]Empaque (9)'!AD23</f>
+        <f>'[1]Empaque (9)'!AD23</f>
         <v>0</v>
       </c>
       <c r="AG23" s="94"/>
@@ -10920,35 +10915,35 @@
     </row>
     <row r="24" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C24" s="96">
-        <f>'[2]Empaque (9)'!C24</f>
+        <f>'[1]Empaque (9)'!C24</f>
         <v>0</v>
       </c>
       <c r="D24" s="97" t="str">
-        <f>'[2]Empaque (9)'!D24</f>
+        <f>'[1]Empaque (9)'!D24</f>
         <v/>
       </c>
       <c r="E24" s="98">
-        <f>'[2]Empaque (9)'!F24</f>
+        <f>'[1]Empaque (9)'!F24</f>
         <v>0</v>
       </c>
       <c r="F24" s="99">
-        <f>'[2]Empaque (9)'!G24</f>
+        <f>'[1]Empaque (9)'!G24</f>
         <v>0</v>
       </c>
       <c r="G24" s="100">
-        <f>'[2]Empaque (9)'!H24</f>
+        <f>'[1]Empaque (9)'!H24</f>
         <v>0</v>
       </c>
       <c r="H24" s="100">
-        <f>'[2]Empaque (9)'!I24</f>
+        <f>'[1]Empaque (9)'!I24</f>
         <v>0</v>
       </c>
       <c r="I24" s="100">
-        <f>'[2]Empaque (9)'!J24</f>
+        <f>'[1]Empaque (9)'!J24</f>
         <v>0</v>
       </c>
       <c r="J24" s="101">
-        <f>'[2]Empaque (9)'!K24</f>
+        <f>'[1]Empaque (9)'!K24</f>
         <v>0</v>
       </c>
       <c r="K24" s="102">
@@ -10969,11 +10964,11 @@
       <c r="S24" s="10"/>
       <c r="AA24" s="104"/>
       <c r="AB24" s="105">
-        <f>'[2]Empaque (9)'!AC24</f>
+        <f>'[1]Empaque (9)'!AC24</f>
         <v>0</v>
       </c>
       <c r="AC24" s="106">
-        <f>'[2]Empaque (9)'!AD24</f>
+        <f>'[1]Empaque (9)'!AD24</f>
         <v>0</v>
       </c>
       <c r="AH24" s="107">
@@ -10988,11 +10983,11 @@
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A25" s="41" t="str">
-        <f>'[2]Empaque (9)'!A25</f>
+        <f>'[1]Empaque (9)'!A25</f>
         <v>H2E (Orig.) x 80</v>
       </c>
       <c r="B25" s="42" t="str">
-        <f>'[2]Empaque (9)'!B25</f>
+        <f>'[1]Empaque (9)'!B25</f>
         <v>kg</v>
       </c>
       <c r="C25" s="109"/>
@@ -11014,11 +11009,11 @@
       <c r="P25" s="58"/>
       <c r="S25" s="10"/>
       <c r="Z25" s="41" t="str">
-        <f>'[2]Empaque (9)'!AA25</f>
+        <f>'[1]Empaque (9)'!AA25</f>
         <v>H2E (Orig.) x 80</v>
       </c>
       <c r="AA25" s="44" t="str">
-        <f>'[2]Empaque (9)'!AB25</f>
+        <f>'[1]Empaque (9)'!AB25</f>
         <v>kg</v>
       </c>
       <c r="AE25" s="6" t="s">
@@ -11032,43 +11027,43 @@
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A26" s="46" t="str">
-        <f>'[2]Empaque (9)'!A26</f>
+        <f>'[1]Empaque (9)'!A26</f>
         <v>Jb</v>
       </c>
       <c r="B26" s="47">
-        <f>'[2]Empaque (9)'!B26</f>
+        <f>'[1]Empaque (9)'!B26</f>
         <v>12.5</v>
       </c>
       <c r="C26" s="48">
-        <f>'[2]Empaque (9)'!C26</f>
+        <f>'[1]Empaque (9)'!C26</f>
         <v>288</v>
       </c>
       <c r="D26" s="49">
-        <f>'[2]Empaque (9)'!D26</f>
+        <f>'[1]Empaque (9)'!D26</f>
         <v>0.77419354838709675</v>
       </c>
       <c r="E26" s="50">
-        <f>'[2]Empaque (9)'!F26</f>
+        <f>'[1]Empaque (9)'!F26</f>
         <v>0</v>
       </c>
       <c r="F26" s="51">
-        <f>'[2]Empaque (9)'!G26</f>
+        <f>'[1]Empaque (9)'!G26</f>
         <v>0</v>
       </c>
       <c r="G26" s="52">
-        <f>'[2]Empaque (9)'!H26</f>
+        <f>'[1]Empaque (9)'!H26</f>
         <v>0</v>
       </c>
       <c r="H26" s="48">
-        <f>'[2]Empaque (9)'!I26</f>
+        <f>'[1]Empaque (9)'!I26</f>
         <v>516</v>
       </c>
       <c r="I26" s="53">
-        <f>'[2]Empaque (9)'!J26</f>
+        <f>'[1]Empaque (9)'!J26</f>
         <v>0</v>
       </c>
       <c r="J26" s="54">
-        <f>'[2]Empaque (9)'!K26</f>
+        <f>'[1]Empaque (9)'!K26</f>
         <v>0</v>
       </c>
       <c r="K26" s="55">
@@ -11103,19 +11098,19 @@
         <v>0</v>
       </c>
       <c r="Z26" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA26</f>
+        <f>'[1]Empaque (9)'!AA26</f>
         <v>Jb</v>
       </c>
       <c r="AA26" s="61">
-        <f>'[2]Empaque (9)'!AB26</f>
+        <f>'[1]Empaque (9)'!AB26</f>
         <v>12.5</v>
       </c>
       <c r="AB26" s="62">
-        <f>'[2]Empaque (9)'!AC26</f>
+        <f>'[1]Empaque (9)'!AC26</f>
         <v>1316</v>
       </c>
       <c r="AC26" s="63">
-        <f>'[2]Empaque (9)'!AD26</f>
+        <f>'[1]Empaque (9)'!AD26</f>
         <v>0.8292375551354757</v>
       </c>
       <c r="AG26" s="64"/>
@@ -11128,43 +11123,43 @@
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A27" s="46" t="str">
-        <f>'[2]Empaque (9)'!A27</f>
+        <f>'[1]Empaque (9)'!A27</f>
         <v>Xl</v>
       </c>
       <c r="B27" s="66">
-        <f>'[2]Empaque (9)'!B27</f>
+        <f>'[1]Empaque (9)'!B27</f>
         <v>12.5</v>
       </c>
       <c r="C27" s="67">
-        <f>'[2]Empaque (9)'!C27</f>
+        <f>'[1]Empaque (9)'!C27</f>
         <v>51</v>
       </c>
       <c r="D27" s="49">
-        <f>'[2]Empaque (9)'!D27</f>
+        <f>'[1]Empaque (9)'!D27</f>
         <v>0.13709677419354838</v>
       </c>
       <c r="E27" s="50">
-        <f>'[2]Empaque (9)'!F27</f>
+        <f>'[1]Empaque (9)'!F27</f>
         <v>0</v>
       </c>
       <c r="F27" s="51">
-        <f>'[2]Empaque (9)'!G27</f>
+        <f>'[1]Empaque (9)'!G27</f>
         <v>0</v>
       </c>
       <c r="G27" s="68">
-        <f>'[2]Empaque (9)'!H27</f>
+        <f>'[1]Empaque (9)'!H27</f>
         <v>0</v>
       </c>
       <c r="H27" s="67">
-        <f>'[2]Empaque (9)'!I27</f>
+        <f>'[1]Empaque (9)'!I27</f>
         <v>110</v>
       </c>
       <c r="I27" s="53">
-        <f>'[2]Empaque (9)'!J27</f>
+        <f>'[1]Empaque (9)'!J27</f>
         <v>0</v>
       </c>
       <c r="J27" s="54">
-        <f>'[2]Empaque (9)'!K27</f>
+        <f>'[1]Empaque (9)'!K27</f>
         <v>0</v>
       </c>
       <c r="K27" s="69">
@@ -11184,19 +11179,19 @@
       </c>
       <c r="S27" s="10"/>
       <c r="Z27" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA27</f>
+        <f>'[1]Empaque (9)'!AA27</f>
         <v>Xl</v>
       </c>
       <c r="AA27" s="72">
-        <f>'[2]Empaque (9)'!AB27</f>
+        <f>'[1]Empaque (9)'!AB27</f>
         <v>12.5</v>
       </c>
       <c r="AB27" s="62">
-        <f>'[2]Empaque (9)'!AC27</f>
+        <f>'[1]Empaque (9)'!AC27</f>
         <v>150</v>
       </c>
       <c r="AC27" s="63">
-        <f>'[2]Empaque (9)'!AD27</f>
+        <f>'[1]Empaque (9)'!AD27</f>
         <v>9.4517958412098299E-2</v>
       </c>
       <c r="AG27" s="73"/>
@@ -11209,43 +11204,43 @@
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A28" s="46" t="str">
-        <f>'[2]Empaque (9)'!A28</f>
+        <f>'[1]Empaque (9)'!A28</f>
         <v>Lg</v>
       </c>
       <c r="B28" s="47">
-        <f>'[2]Empaque (9)'!B28</f>
+        <f>'[1]Empaque (9)'!B28</f>
         <v>12.5</v>
       </c>
       <c r="C28" s="67">
-        <f>'[2]Empaque (9)'!C28</f>
+        <f>'[1]Empaque (9)'!C28</f>
         <v>20</v>
       </c>
       <c r="D28" s="49">
-        <f>'[2]Empaque (9)'!D28</f>
+        <f>'[1]Empaque (9)'!D28</f>
         <v>5.3763440860215055E-2</v>
       </c>
       <c r="E28" s="50">
-        <f>'[2]Empaque (9)'!F28</f>
+        <f>'[1]Empaque (9)'!F28</f>
         <v>0</v>
       </c>
       <c r="F28" s="51">
-        <f>'[2]Empaque (9)'!G28</f>
+        <f>'[1]Empaque (9)'!G28</f>
         <v>0</v>
       </c>
       <c r="G28" s="68">
-        <f>'[2]Empaque (9)'!H28</f>
+        <f>'[1]Empaque (9)'!H28</f>
         <v>0</v>
       </c>
       <c r="H28" s="67">
-        <f>'[2]Empaque (9)'!I28</f>
+        <f>'[1]Empaque (9)'!I28</f>
         <v>38</v>
       </c>
       <c r="I28" s="53">
-        <f>'[2]Empaque (9)'!J28</f>
+        <f>'[1]Empaque (9)'!J28</f>
         <v>0</v>
       </c>
       <c r="J28" s="54">
-        <f>'[2]Empaque (9)'!K28</f>
+        <f>'[1]Empaque (9)'!K28</f>
         <v>0</v>
       </c>
       <c r="K28" s="69">
@@ -11265,19 +11260,19 @@
       </c>
       <c r="S28" s="10"/>
       <c r="Z28" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA28</f>
+        <f>'[1]Empaque (9)'!AA28</f>
         <v>Lg</v>
       </c>
       <c r="AA28" s="61">
-        <f>'[2]Empaque (9)'!AB28</f>
+        <f>'[1]Empaque (9)'!AB28</f>
         <v>12.5</v>
       </c>
       <c r="AB28" s="62">
-        <f>'[2]Empaque (9)'!AC28</f>
+        <f>'[1]Empaque (9)'!AC28</f>
         <v>65</v>
       </c>
       <c r="AC28" s="63">
-        <f>'[2]Empaque (9)'!AD28</f>
+        <f>'[1]Empaque (9)'!AD28</f>
         <v>4.0957781978575927E-2</v>
       </c>
       <c r="AG28" s="73"/>
@@ -11290,43 +11285,43 @@
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A29" s="46" t="str">
-        <f>'[2]Empaque (9)'!A29</f>
+        <f>'[1]Empaque (9)'!A29</f>
         <v>Md</v>
       </c>
       <c r="B29" s="66">
-        <f>'[2]Empaque (9)'!B29</f>
+        <f>'[1]Empaque (9)'!B29</f>
         <v>12.5</v>
       </c>
       <c r="C29" s="67">
-        <f>'[2]Empaque (9)'!C29</f>
+        <f>'[1]Empaque (9)'!C29</f>
         <v>4</v>
       </c>
       <c r="D29" s="49">
-        <f>'[2]Empaque (9)'!D29</f>
+        <f>'[1]Empaque (9)'!D29</f>
         <v>1.0752688172043012E-2</v>
       </c>
       <c r="E29" s="50">
-        <f>'[2]Empaque (9)'!F29</f>
+        <f>'[1]Empaque (9)'!F29</f>
         <v>0</v>
       </c>
       <c r="F29" s="51">
-        <f>'[2]Empaque (9)'!G29</f>
+        <f>'[1]Empaque (9)'!G29</f>
         <v>0</v>
       </c>
       <c r="G29" s="68">
-        <f>'[2]Empaque (9)'!H29</f>
+        <f>'[1]Empaque (9)'!H29</f>
         <v>0</v>
       </c>
       <c r="H29" s="67">
-        <f>'[2]Empaque (9)'!I29</f>
+        <f>'[1]Empaque (9)'!I29</f>
         <v>14</v>
       </c>
       <c r="I29" s="53">
-        <f>'[2]Empaque (9)'!J29</f>
+        <f>'[1]Empaque (9)'!J29</f>
         <v>0</v>
       </c>
       <c r="J29" s="54">
-        <f>'[2]Empaque (9)'!K29</f>
+        <f>'[1]Empaque (9)'!K29</f>
         <v>0</v>
       </c>
       <c r="K29" s="69">
@@ -11346,19 +11341,19 @@
       </c>
       <c r="S29" s="10"/>
       <c r="Z29" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA29</f>
+        <f>'[1]Empaque (9)'!AA29</f>
         <v>Md</v>
       </c>
       <c r="AA29" s="72">
-        <f>'[2]Empaque (9)'!AB29</f>
+        <f>'[1]Empaque (9)'!AB29</f>
         <v>12.5</v>
       </c>
       <c r="AB29" s="62">
-        <f>'[2]Empaque (9)'!AC29</f>
+        <f>'[1]Empaque (9)'!AC29</f>
         <v>30</v>
       </c>
       <c r="AC29" s="63">
-        <f>'[2]Empaque (9)'!AD29</f>
+        <f>'[1]Empaque (9)'!AD29</f>
         <v>1.890359168241966E-2</v>
       </c>
       <c r="AG29" s="73"/>
@@ -11371,43 +11366,43 @@
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A30" s="46" t="str">
-        <f>'[2]Empaque (9)'!A30</f>
+        <f>'[1]Empaque (9)'!A30</f>
         <v>Sm</v>
       </c>
       <c r="B30" s="47">
-        <f>'[2]Empaque (9)'!B30</f>
+        <f>'[1]Empaque (9)'!B30</f>
         <v>12.5</v>
       </c>
       <c r="C30" s="67">
-        <f>'[2]Empaque (9)'!C30</f>
+        <f>'[1]Empaque (9)'!C30</f>
         <v>4</v>
       </c>
       <c r="D30" s="49">
-        <f>'[2]Empaque (9)'!D30</f>
+        <f>'[1]Empaque (9)'!D30</f>
         <v>1.0752688172043012E-2</v>
       </c>
       <c r="E30" s="50">
-        <f>'[2]Empaque (9)'!F30</f>
+        <f>'[1]Empaque (9)'!F30</f>
         <v>0</v>
       </c>
       <c r="F30" s="51">
-        <f>'[2]Empaque (9)'!G30</f>
+        <f>'[1]Empaque (9)'!G30</f>
         <v>0</v>
       </c>
       <c r="G30" s="68">
-        <f>'[2]Empaque (9)'!H30</f>
+        <f>'[1]Empaque (9)'!H30</f>
         <v>0</v>
       </c>
       <c r="H30" s="67">
-        <f>'[2]Empaque (9)'!I30</f>
+        <f>'[1]Empaque (9)'!I30</f>
         <v>13</v>
       </c>
       <c r="I30" s="53">
-        <f>'[2]Empaque (9)'!J30</f>
+        <f>'[1]Empaque (9)'!J30</f>
         <v>0</v>
       </c>
       <c r="J30" s="54">
-        <f>'[2]Empaque (9)'!K30</f>
+        <f>'[1]Empaque (9)'!K30</f>
         <v>0</v>
       </c>
       <c r="K30" s="69">
@@ -11427,19 +11422,19 @@
       </c>
       <c r="S30" s="10"/>
       <c r="Z30" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA30</f>
+        <f>'[1]Empaque (9)'!AA30</f>
         <v>Sm</v>
       </c>
       <c r="AA30" s="61">
-        <f>'[2]Empaque (9)'!AB30</f>
+        <f>'[1]Empaque (9)'!AB30</f>
         <v>12.5</v>
       </c>
       <c r="AB30" s="77">
-        <f>'[2]Empaque (9)'!AC30</f>
+        <f>'[1]Empaque (9)'!AC30</f>
         <v>21</v>
       </c>
       <c r="AC30" s="63">
-        <f>'[2]Empaque (9)'!AD30</f>
+        <f>'[1]Empaque (9)'!AD30</f>
         <v>1.3232514177693762E-2</v>
       </c>
       <c r="AG30" s="64"/>
@@ -11452,43 +11447,43 @@
     </row>
     <row r="31" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="79" t="str">
-        <f>'[2]Empaque (9)'!A31</f>
+        <f>'[1]Empaque (9)'!A31</f>
         <v>Mixto</v>
       </c>
       <c r="B31" s="111">
-        <f>'[2]Empaque (9)'!B31</f>
+        <f>'[1]Empaque (9)'!B31</f>
         <v>12.5</v>
       </c>
       <c r="C31" s="81">
-        <f>'[2]Empaque (9)'!C31</f>
+        <f>'[1]Empaque (9)'!C31</f>
         <v>5</v>
       </c>
       <c r="D31" s="82">
-        <f>'[2]Empaque (9)'!D31</f>
+        <f>'[1]Empaque (9)'!D31</f>
         <v>1.3440860215053764E-2</v>
       </c>
       <c r="E31" s="83">
-        <f>'[2]Empaque (9)'!F31</f>
+        <f>'[1]Empaque (9)'!F31</f>
         <v>0</v>
       </c>
       <c r="F31" s="84">
-        <f>'[2]Empaque (9)'!G31</f>
+        <f>'[1]Empaque (9)'!G31</f>
         <v>0</v>
       </c>
       <c r="G31" s="85">
-        <f>'[2]Empaque (9)'!H31</f>
+        <f>'[1]Empaque (9)'!H31</f>
         <v>0</v>
       </c>
       <c r="H31" s="81">
-        <f>'[2]Empaque (9)'!I31</f>
+        <f>'[1]Empaque (9)'!I31</f>
         <v>5</v>
       </c>
       <c r="I31" s="86">
-        <f>'[2]Empaque (9)'!J31</f>
+        <f>'[1]Empaque (9)'!J31</f>
         <v>0</v>
       </c>
       <c r="J31" s="87">
-        <f>'[2]Empaque (9)'!K31</f>
+        <f>'[1]Empaque (9)'!K31</f>
         <v>0</v>
       </c>
       <c r="K31" s="88">
@@ -11509,19 +11504,19 @@
       </c>
       <c r="S31" s="10"/>
       <c r="Z31" s="90" t="str">
-        <f>'[2]Empaque (9)'!AA31</f>
+        <f>'[1]Empaque (9)'!AA31</f>
         <v>xs</v>
       </c>
       <c r="AA31" s="91">
-        <f>'[2]Empaque (9)'!AB31</f>
+        <f>'[1]Empaque (9)'!AB31</f>
         <v>12.5</v>
       </c>
       <c r="AB31" s="92">
-        <f>'[2]Empaque (9)'!AC31</f>
+        <f>'[1]Empaque (9)'!AC31</f>
         <v>5</v>
       </c>
       <c r="AC31" s="93">
-        <f>'[2]Empaque (9)'!AD31</f>
+        <f>'[1]Empaque (9)'!AD31</f>
         <v>3.1505986137366098E-3</v>
       </c>
       <c r="AG31" s="94"/>
@@ -11534,35 +11529,35 @@
     </row>
     <row r="32" spans="1:36" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C32" s="96">
-        <f>'[2]Empaque (9)'!C32</f>
+        <f>'[1]Empaque (9)'!C32</f>
         <v>372</v>
       </c>
       <c r="D32" s="97">
-        <f>'[2]Empaque (9)'!D32</f>
+        <f>'[1]Empaque (9)'!D32</f>
         <v>1</v>
       </c>
       <c r="E32" s="98">
-        <f>'[2]Empaque (9)'!F32</f>
+        <f>'[1]Empaque (9)'!F32</f>
         <v>0</v>
       </c>
       <c r="F32" s="99">
-        <f>'[2]Empaque (9)'!G32</f>
+        <f>'[1]Empaque (9)'!G32</f>
         <v>0</v>
       </c>
       <c r="G32" s="100">
-        <f>'[2]Empaque (9)'!H32</f>
+        <f>'[1]Empaque (9)'!H32</f>
         <v>0</v>
       </c>
       <c r="H32" s="100">
-        <f>'[2]Empaque (9)'!I32</f>
+        <f>'[1]Empaque (9)'!I32</f>
         <v>696</v>
       </c>
       <c r="I32" s="100">
-        <f>'[2]Empaque (9)'!J32</f>
+        <f>'[1]Empaque (9)'!J32</f>
         <v>0</v>
       </c>
       <c r="J32" s="101">
-        <f>'[2]Empaque (9)'!K32</f>
+        <f>'[1]Empaque (9)'!K32</f>
         <v>0</v>
       </c>
       <c r="K32" s="102">
@@ -11583,11 +11578,11 @@
       <c r="S32" s="10"/>
       <c r="AA32" s="104"/>
       <c r="AB32" s="105">
-        <f>'[2]Empaque (9)'!AC32</f>
+        <f>'[1]Empaque (9)'!AC32</f>
         <v>1587</v>
       </c>
       <c r="AC32" s="106">
-        <f>'[2]Empaque (9)'!AD32</f>
+        <f>'[1]Empaque (9)'!AD32</f>
         <v>0.99999999999999989</v>
       </c>
       <c r="AH32" s="107">
@@ -11602,11 +11597,11 @@
     </row>
     <row r="33" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="41" t="str">
-        <f>'[2]Empaque (9)'!A33</f>
+        <f>'[1]Empaque (9)'!A33</f>
         <v>Genérica x 80</v>
       </c>
-      <c r="B33" s="193" t="str">
-        <f>'[2]Empaque (9)'!B33</f>
+      <c r="B33" s="172" t="str">
+        <f>'[1]Empaque (9)'!B33</f>
         <v>kg</v>
       </c>
       <c r="C33" s="109"/>
@@ -11628,11 +11623,11 @@
       <c r="P33" s="58"/>
       <c r="S33" s="10"/>
       <c r="Z33" s="41" t="str">
-        <f>'[2]Empaque (9)'!AA33</f>
+        <f>'[1]Empaque (9)'!AA33</f>
         <v>Genérica x 80</v>
       </c>
       <c r="AA33" s="44" t="str">
-        <f>'[2]Empaque (9)'!AB33</f>
+        <f>'[1]Empaque (9)'!AB33</f>
         <v>kg</v>
       </c>
       <c r="AE33" s="6" t="s">
@@ -11646,48 +11641,48 @@
     </row>
     <row r="34" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="46" t="str">
-        <f>'[2]Empaque (9)'!A34</f>
+        <f>'[1]Empaque (9)'!A34</f>
         <v>Jb</v>
       </c>
-      <c r="B34" s="194">
-        <f>'[2]Empaque (9)'!B34</f>
+      <c r="B34" s="173">
+        <f>'[1]Empaque (9)'!B34</f>
         <v>13</v>
       </c>
       <c r="C34" s="48">
-        <f>'[2]Empaque (9)'!C34</f>
+        <f>'[1]Empaque (9)'!C34</f>
         <v>0</v>
       </c>
       <c r="D34" s="49" t="str">
-        <f>'[2]Empaque (9)'!D34</f>
+        <f>'[1]Empaque (9)'!D34</f>
         <v/>
       </c>
       <c r="E34" s="50">
-        <f>'[2]Empaque (9)'!F34</f>
+        <f>'[1]Empaque (9)'!F34</f>
         <v>0</v>
       </c>
       <c r="F34" s="51">
-        <f>'[2]Empaque (9)'!G34</f>
+        <f>'[1]Empaque (9)'!G34</f>
         <v>0</v>
       </c>
       <c r="G34" s="52">
-        <f>'[2]Empaque (9)'!H34</f>
+        <f>'[1]Empaque (9)'!H34</f>
         <v>0</v>
       </c>
       <c r="H34" s="48">
-        <f>'[2]Empaque (9)'!I34</f>
+        <f>'[1]Empaque (9)'!I34</f>
         <v>0</v>
       </c>
       <c r="I34" s="53">
-        <f>'[2]Empaque (9)'!J34</f>
+        <f>'[1]Empaque (9)'!J34</f>
         <v>0</v>
       </c>
       <c r="J34" s="54">
-        <f>'[2]Empaque (9)'!K34</f>
+        <f>'[1]Empaque (9)'!K34</f>
         <v>0</v>
       </c>
       <c r="K34" s="55"/>
       <c r="L34" s="55">
-        <f>IF(C34=0+E34-F34,0,(K34-'[1]Reporte Semanal'!$C$74)-(K34*'[1]Reporte Semanal'!$C$75))</f>
+        <f>IF(C34=0+E34-F34,0,(K34-'[2]Reporte Semanal'!$C$74)-(K34*'[2]Reporte Semanal'!$C$75))</f>
         <v>0</v>
       </c>
       <c r="M34" s="55">
@@ -11715,19 +11710,19 @@
         <v>0</v>
       </c>
       <c r="Z34" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA34</f>
+        <f>'[1]Empaque (9)'!AA34</f>
         <v>Jb</v>
       </c>
       <c r="AA34" s="61">
-        <f>'[2]Empaque (9)'!AB34</f>
+        <f>'[1]Empaque (9)'!AB34</f>
         <v>13</v>
       </c>
       <c r="AB34" s="62">
-        <f>'[2]Empaque (9)'!AC34</f>
+        <f>'[1]Empaque (9)'!AC34</f>
         <v>0</v>
       </c>
       <c r="AC34" s="63">
-        <f>'[2]Empaque (9)'!AD34</f>
+        <f>'[1]Empaque (9)'!AD34</f>
         <v>0</v>
       </c>
       <c r="AG34" s="64"/>
@@ -11740,48 +11735,48 @@
     </row>
     <row r="35" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="46" t="str">
-        <f>'[2]Empaque (9)'!A35</f>
+        <f>'[1]Empaque (9)'!A35</f>
         <v>Xl</v>
       </c>
-      <c r="B35" s="195">
-        <f>'[2]Empaque (9)'!B35</f>
+      <c r="B35" s="174">
+        <f>'[1]Empaque (9)'!B35</f>
         <v>13</v>
       </c>
       <c r="C35" s="67">
-        <f>'[2]Empaque (9)'!C35</f>
+        <f>'[1]Empaque (9)'!C35</f>
         <v>0</v>
       </c>
       <c r="D35" s="49" t="str">
-        <f>'[2]Empaque (9)'!D35</f>
+        <f>'[1]Empaque (9)'!D35</f>
         <v/>
       </c>
       <c r="E35" s="50">
-        <f>'[2]Empaque (9)'!F35</f>
+        <f>'[1]Empaque (9)'!F35</f>
         <v>0</v>
       </c>
       <c r="F35" s="51">
-        <f>'[2]Empaque (9)'!G35</f>
+        <f>'[1]Empaque (9)'!G35</f>
         <v>0</v>
       </c>
       <c r="G35" s="68">
-        <f>'[2]Empaque (9)'!H35</f>
+        <f>'[1]Empaque (9)'!H35</f>
         <v>0</v>
       </c>
       <c r="H35" s="67">
-        <f>'[2]Empaque (9)'!I35</f>
+        <f>'[1]Empaque (9)'!I35</f>
         <v>0</v>
       </c>
       <c r="I35" s="53">
-        <f>'[2]Empaque (9)'!J35</f>
+        <f>'[1]Empaque (9)'!J35</f>
         <v>0</v>
       </c>
       <c r="J35" s="54">
-        <f>'[2]Empaque (9)'!K35</f>
+        <f>'[1]Empaque (9)'!K35</f>
         <v>0</v>
       </c>
       <c r="K35" s="69"/>
       <c r="L35" s="69">
-        <f>IF(C35=0+E35-F35,0,(K35-'[1]Reporte Semanal'!$C$74)-(K35*'[1]Reporte Semanal'!$C$75))</f>
+        <f>IF(C35=0+E35-F35,0,(K35-'[2]Reporte Semanal'!$C$74)-(K35*'[2]Reporte Semanal'!$C$75))</f>
         <v>0</v>
       </c>
       <c r="M35" s="69">
@@ -11794,19 +11789,19 @@
       </c>
       <c r="S35" s="10"/>
       <c r="Z35" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA35</f>
+        <f>'[1]Empaque (9)'!AA35</f>
         <v>Xl</v>
       </c>
       <c r="AA35" s="72">
-        <f>'[2]Empaque (9)'!AB35</f>
+        <f>'[1]Empaque (9)'!AB35</f>
         <v>13</v>
       </c>
       <c r="AB35" s="62">
-        <f>'[2]Empaque (9)'!AC35</f>
+        <f>'[1]Empaque (9)'!AC35</f>
         <v>0</v>
       </c>
       <c r="AC35" s="63">
-        <f>'[2]Empaque (9)'!AD35</f>
+        <f>'[1]Empaque (9)'!AD35</f>
         <v>0</v>
       </c>
       <c r="AG35" s="73"/>
@@ -11819,48 +11814,48 @@
     </row>
     <row r="36" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="46" t="str">
-        <f>'[2]Empaque (9)'!A36</f>
+        <f>'[1]Empaque (9)'!A36</f>
         <v>Lg</v>
       </c>
-      <c r="B36" s="194">
-        <f>'[2]Empaque (9)'!B36</f>
+      <c r="B36" s="173">
+        <f>'[1]Empaque (9)'!B36</f>
         <v>13</v>
       </c>
       <c r="C36" s="67">
-        <f>'[2]Empaque (9)'!C36</f>
+        <f>'[1]Empaque (9)'!C36</f>
         <v>0</v>
       </c>
       <c r="D36" s="49" t="str">
-        <f>'[2]Empaque (9)'!D36</f>
+        <f>'[1]Empaque (9)'!D36</f>
         <v/>
       </c>
       <c r="E36" s="50">
-        <f>'[2]Empaque (9)'!F36</f>
+        <f>'[1]Empaque (9)'!F36</f>
         <v>0</v>
       </c>
       <c r="F36" s="51">
-        <f>'[2]Empaque (9)'!G36</f>
+        <f>'[1]Empaque (9)'!G36</f>
         <v>0</v>
       </c>
       <c r="G36" s="68">
-        <f>'[2]Empaque (9)'!H36</f>
+        <f>'[1]Empaque (9)'!H36</f>
         <v>0</v>
       </c>
       <c r="H36" s="67">
-        <f>'[2]Empaque (9)'!I36</f>
+        <f>'[1]Empaque (9)'!I36</f>
         <v>0</v>
       </c>
       <c r="I36" s="53">
-        <f>'[2]Empaque (9)'!J36</f>
+        <f>'[1]Empaque (9)'!J36</f>
         <v>0</v>
       </c>
       <c r="J36" s="54">
-        <f>'[2]Empaque (9)'!K36</f>
+        <f>'[1]Empaque (9)'!K36</f>
         <v>0</v>
       </c>
       <c r="K36" s="69"/>
       <c r="L36" s="69">
-        <f>IF(C36=0+E36-F36,0,(K36-'[1]Reporte Semanal'!$C$74)-(K36*'[1]Reporte Semanal'!$C$75))</f>
+        <f>IF(C36=0+E36-F36,0,(K36-'[2]Reporte Semanal'!$C$74)-(K36*'[2]Reporte Semanal'!$C$75))</f>
         <v>0</v>
       </c>
       <c r="M36" s="69">
@@ -11873,19 +11868,19 @@
       </c>
       <c r="S36" s="10"/>
       <c r="Z36" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA36</f>
+        <f>'[1]Empaque (9)'!AA36</f>
         <v>Lg</v>
       </c>
       <c r="AA36" s="61">
-        <f>'[2]Empaque (9)'!AB36</f>
+        <f>'[1]Empaque (9)'!AB36</f>
         <v>13</v>
       </c>
       <c r="AB36" s="62">
-        <f>'[2]Empaque (9)'!AC36</f>
+        <f>'[1]Empaque (9)'!AC36</f>
         <v>0</v>
       </c>
       <c r="AC36" s="63">
-        <f>'[2]Empaque (9)'!AD36</f>
+        <f>'[1]Empaque (9)'!AD36</f>
         <v>0</v>
       </c>
       <c r="AG36" s="73"/>
@@ -11898,48 +11893,48 @@
     </row>
     <row r="37" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="46" t="str">
-        <f>'[2]Empaque (9)'!A37</f>
+        <f>'[1]Empaque (9)'!A37</f>
         <v>Md</v>
       </c>
-      <c r="B37" s="195">
-        <f>'[2]Empaque (9)'!B37</f>
+      <c r="B37" s="174">
+        <f>'[1]Empaque (9)'!B37</f>
         <v>13</v>
       </c>
       <c r="C37" s="67">
-        <f>'[2]Empaque (9)'!C37</f>
+        <f>'[1]Empaque (9)'!C37</f>
         <v>0</v>
       </c>
       <c r="D37" s="49" t="str">
-        <f>'[2]Empaque (9)'!D37</f>
+        <f>'[1]Empaque (9)'!D37</f>
         <v/>
       </c>
       <c r="E37" s="50">
-        <f>'[2]Empaque (9)'!F37</f>
+        <f>'[1]Empaque (9)'!F37</f>
         <v>0</v>
       </c>
       <c r="F37" s="51">
-        <f>'[2]Empaque (9)'!G37</f>
+        <f>'[1]Empaque (9)'!G37</f>
         <v>0</v>
       </c>
       <c r="G37" s="68">
-        <f>'[2]Empaque (9)'!H37</f>
+        <f>'[1]Empaque (9)'!H37</f>
         <v>0</v>
       </c>
       <c r="H37" s="67">
-        <f>'[2]Empaque (9)'!I37</f>
+        <f>'[1]Empaque (9)'!I37</f>
         <v>0</v>
       </c>
       <c r="I37" s="53">
-        <f>'[2]Empaque (9)'!J37</f>
+        <f>'[1]Empaque (9)'!J37</f>
         <v>0</v>
       </c>
       <c r="J37" s="54">
-        <f>'[2]Empaque (9)'!K37</f>
+        <f>'[1]Empaque (9)'!K37</f>
         <v>0</v>
       </c>
       <c r="K37" s="69"/>
       <c r="L37" s="69">
-        <f>IF(C37=0+E37-F37,0,(K37-'[1]Reporte Semanal'!$C$74)-(K37*'[1]Reporte Semanal'!$C$75))</f>
+        <f>IF(C37=0+E37-F37,0,(K37-'[2]Reporte Semanal'!$C$74)-(K37*'[2]Reporte Semanal'!$C$75))</f>
         <v>0</v>
       </c>
       <c r="M37" s="69">
@@ -11952,19 +11947,19 @@
       </c>
       <c r="S37" s="10"/>
       <c r="Z37" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA37</f>
+        <f>'[1]Empaque (9)'!AA37</f>
         <v>Md</v>
       </c>
       <c r="AA37" s="72">
-        <f>'[2]Empaque (9)'!AB37</f>
+        <f>'[1]Empaque (9)'!AB37</f>
         <v>13</v>
       </c>
       <c r="AB37" s="62">
-        <f>'[2]Empaque (9)'!AC37</f>
+        <f>'[1]Empaque (9)'!AC37</f>
         <v>0</v>
       </c>
       <c r="AC37" s="63">
-        <f>'[2]Empaque (9)'!AD37</f>
+        <f>'[1]Empaque (9)'!AD37</f>
         <v>0</v>
       </c>
       <c r="AG37" s="73"/>
@@ -11977,48 +11972,48 @@
     </row>
     <row r="38" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="46" t="str">
-        <f>'[2]Empaque (9)'!A38</f>
+        <f>'[1]Empaque (9)'!A38</f>
         <v>Sm</v>
       </c>
-      <c r="B38" s="194">
-        <f>'[2]Empaque (9)'!B38</f>
+      <c r="B38" s="173">
+        <f>'[1]Empaque (9)'!B38</f>
         <v>13</v>
       </c>
       <c r="C38" s="67">
-        <f>'[2]Empaque (9)'!C38</f>
+        <f>'[1]Empaque (9)'!C38</f>
         <v>0</v>
       </c>
       <c r="D38" s="49" t="str">
-        <f>'[2]Empaque (9)'!D38</f>
+        <f>'[1]Empaque (9)'!D38</f>
         <v/>
       </c>
       <c r="E38" s="50">
-        <f>'[2]Empaque (9)'!F38</f>
+        <f>'[1]Empaque (9)'!F38</f>
         <v>0</v>
       </c>
       <c r="F38" s="51">
-        <f>'[2]Empaque (9)'!G38</f>
+        <f>'[1]Empaque (9)'!G38</f>
         <v>0</v>
       </c>
       <c r="G38" s="68">
-        <f>'[2]Empaque (9)'!H38</f>
+        <f>'[1]Empaque (9)'!H38</f>
         <v>0</v>
       </c>
       <c r="H38" s="67">
-        <f>'[2]Empaque (9)'!I38</f>
+        <f>'[1]Empaque (9)'!I38</f>
         <v>0</v>
       </c>
       <c r="I38" s="53">
-        <f>'[2]Empaque (9)'!J38</f>
+        <f>'[1]Empaque (9)'!J38</f>
         <v>0</v>
       </c>
       <c r="J38" s="54">
-        <f>'[2]Empaque (9)'!K38</f>
+        <f>'[1]Empaque (9)'!K38</f>
         <v>0</v>
       </c>
       <c r="K38" s="69"/>
       <c r="L38" s="69">
-        <f>IF(C38=0+E38-F38,0,(K38-'[1]Reporte Semanal'!$C$74)-(K38*'[1]Reporte Semanal'!$C$75))</f>
+        <f>IF(C38=0+E38-F38,0,(K38-'[2]Reporte Semanal'!$C$74)-(K38*'[2]Reporte Semanal'!$C$75))</f>
         <v>0</v>
       </c>
       <c r="M38" s="69">
@@ -12031,19 +12026,19 @@
       </c>
       <c r="S38" s="10"/>
       <c r="Z38" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA38</f>
+        <f>'[1]Empaque (9)'!AA38</f>
         <v>Sm</v>
       </c>
       <c r="AA38" s="61">
-        <f>'[2]Empaque (9)'!AB38</f>
+        <f>'[1]Empaque (9)'!AB38</f>
         <v>13</v>
       </c>
       <c r="AB38" s="77">
-        <f>'[2]Empaque (9)'!AC38</f>
+        <f>'[1]Empaque (9)'!AC38</f>
         <v>0</v>
       </c>
       <c r="AC38" s="63">
-        <f>'[2]Empaque (9)'!AD38</f>
+        <f>'[1]Empaque (9)'!AD38</f>
         <v>0</v>
       </c>
       <c r="AG38" s="64"/>
@@ -12056,48 +12051,48 @@
     </row>
     <row r="39" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="79" t="str">
-        <f>'[2]Empaque (9)'!A39</f>
+        <f>'[1]Empaque (9)'!A39</f>
         <v>Mixto</v>
       </c>
-      <c r="B39" s="196">
-        <f>'[2]Empaque (9)'!B39</f>
+      <c r="B39" s="175">
+        <f>'[1]Empaque (9)'!B39</f>
         <v>0</v>
       </c>
       <c r="C39" s="81">
-        <f>'[2]Empaque (9)'!C39</f>
+        <f>'[1]Empaque (9)'!C39</f>
         <v>0</v>
       </c>
       <c r="D39" s="82" t="str">
-        <f>'[2]Empaque (9)'!D39</f>
+        <f>'[1]Empaque (9)'!D39</f>
         <v/>
       </c>
       <c r="E39" s="83">
-        <f>'[2]Empaque (9)'!F39</f>
+        <f>'[1]Empaque (9)'!F39</f>
         <v>0</v>
       </c>
       <c r="F39" s="84">
-        <f>'[2]Empaque (9)'!G39</f>
+        <f>'[1]Empaque (9)'!G39</f>
         <v>0</v>
       </c>
       <c r="G39" s="85">
-        <f>'[2]Empaque (9)'!H39</f>
+        <f>'[1]Empaque (9)'!H39</f>
         <v>0</v>
       </c>
       <c r="H39" s="81">
-        <f>'[2]Empaque (9)'!I39</f>
+        <f>'[1]Empaque (9)'!I39</f>
         <v>0</v>
       </c>
       <c r="I39" s="86">
-        <f>'[2]Empaque (9)'!J39</f>
+        <f>'[1]Empaque (9)'!J39</f>
         <v>0</v>
       </c>
       <c r="J39" s="87">
-        <f>'[2]Empaque (9)'!K39</f>
+        <f>'[1]Empaque (9)'!K39</f>
         <v>0</v>
       </c>
       <c r="K39" s="88"/>
       <c r="L39" s="88">
-        <f>IF(C39=0+E39-F39,0,(K39-'[1]Reporte Semanal'!$C$74)-(K39*'[1]Reporte Semanal'!$C$75))</f>
+        <f>IF(C39=0+E39-F39,0,(K39-'[2]Reporte Semanal'!$C$74)-(K39*'[2]Reporte Semanal'!$C$75))</f>
         <v>0</v>
       </c>
       <c r="M39" s="88">
@@ -12111,19 +12106,19 @@
       </c>
       <c r="S39" s="10"/>
       <c r="Z39" s="90" t="str">
-        <f>'[2]Empaque (9)'!AA39</f>
+        <f>'[1]Empaque (9)'!AA39</f>
         <v>xs</v>
       </c>
       <c r="AA39" s="91">
-        <f>'[2]Empaque (9)'!AB39</f>
+        <f>'[1]Empaque (9)'!AB39</f>
         <v>0</v>
       </c>
       <c r="AB39" s="92">
-        <f>'[2]Empaque (9)'!AC39</f>
+        <f>'[1]Empaque (9)'!AC39</f>
         <v>0</v>
       </c>
       <c r="AC39" s="93">
-        <f>'[2]Empaque (9)'!AD39</f>
+        <f>'[1]Empaque (9)'!AD39</f>
         <v>0</v>
       </c>
       <c r="AG39" s="94"/>
@@ -12136,35 +12131,35 @@
     </row>
     <row r="40" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C40" s="96">
-        <f>'[2]Empaque (9)'!C40</f>
+        <f>'[1]Empaque (9)'!C40</f>
         <v>0</v>
       </c>
       <c r="D40" s="97" t="str">
-        <f>'[2]Empaque (9)'!D40</f>
+        <f>'[1]Empaque (9)'!D40</f>
         <v/>
       </c>
       <c r="E40" s="98">
-        <f>'[2]Empaque (9)'!F40</f>
+        <f>'[1]Empaque (9)'!F40</f>
         <v>0</v>
       </c>
       <c r="F40" s="99">
-        <f>'[2]Empaque (9)'!G40</f>
+        <f>'[1]Empaque (9)'!G40</f>
         <v>0</v>
       </c>
       <c r="G40" s="100">
-        <f>'[2]Empaque (9)'!H40</f>
+        <f>'[1]Empaque (9)'!H40</f>
         <v>0</v>
       </c>
       <c r="H40" s="100">
-        <f>'[2]Empaque (9)'!I40</f>
+        <f>'[1]Empaque (9)'!I40</f>
         <v>0</v>
       </c>
       <c r="I40" s="100">
-        <f>'[2]Empaque (9)'!J40</f>
+        <f>'[1]Empaque (9)'!J40</f>
         <v>0</v>
       </c>
       <c r="J40" s="101">
-        <f>'[2]Empaque (9)'!K40</f>
+        <f>'[1]Empaque (9)'!K40</f>
         <v>0</v>
       </c>
       <c r="K40" s="102" t="e">
@@ -12185,11 +12180,11 @@
       <c r="S40" s="10"/>
       <c r="AA40" s="104"/>
       <c r="AB40" s="105">
-        <f>'[2]Empaque (9)'!AC40</f>
+        <f>'[1]Empaque (9)'!AC40</f>
         <v>0</v>
       </c>
       <c r="AC40" s="106">
-        <f>'[2]Empaque (9)'!AD40</f>
+        <f>'[1]Empaque (9)'!AD40</f>
         <v>0</v>
       </c>
       <c r="AH40" s="107">
@@ -12204,11 +12199,11 @@
     </row>
     <row r="41" spans="1:36" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="41" t="str">
-        <f>'[2]Empaque (9)'!A41</f>
+        <f>'[1]Empaque (9)'!A41</f>
         <v>1 1/9 x 80</v>
       </c>
-      <c r="B41" s="193" t="str">
-        <f>'[2]Empaque (9)'!B41</f>
+      <c r="B41" s="172" t="str">
+        <f>'[1]Empaque (9)'!B41</f>
         <v>kg</v>
       </c>
       <c r="C41" s="109"/>
@@ -12237,43 +12232,43 @@
     </row>
     <row r="42" spans="1:36" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="46" t="str">
-        <f>'[2]Empaque (9)'!A42</f>
+        <f>'[1]Empaque (9)'!A42</f>
         <v>Jb</v>
       </c>
-      <c r="B42" s="194">
-        <f>'[2]Empaque (9)'!B42</f>
+      <c r="B42" s="173">
+        <f>'[1]Empaque (9)'!B42</f>
         <v>22</v>
       </c>
       <c r="C42" s="48">
-        <f>'[2]Empaque (9)'!C42</f>
+        <f>'[1]Empaque (9)'!C42</f>
         <v>0</v>
       </c>
       <c r="D42" s="49" t="str">
-        <f>'[2]Empaque (9)'!D42</f>
+        <f>'[1]Empaque (9)'!D42</f>
         <v/>
       </c>
       <c r="E42" s="50">
-        <f>'[2]Empaque (9)'!F42</f>
+        <f>'[1]Empaque (9)'!F42</f>
         <v>0</v>
       </c>
       <c r="F42" s="51">
-        <f>'[2]Empaque (9)'!G42</f>
+        <f>'[1]Empaque (9)'!G42</f>
         <v>0</v>
       </c>
       <c r="G42" s="52">
-        <f>'[2]Empaque (9)'!H42</f>
+        <f>'[1]Empaque (9)'!H42</f>
         <v>0</v>
       </c>
       <c r="H42" s="48">
-        <f>'[2]Empaque (9)'!I42</f>
+        <f>'[1]Empaque (9)'!I42</f>
         <v>0</v>
       </c>
       <c r="I42" s="53">
-        <f>'[2]Empaque (9)'!J42</f>
+        <f>'[1]Empaque (9)'!J42</f>
         <v>0</v>
       </c>
       <c r="J42" s="54">
-        <f>'[2]Empaque (9)'!K42</f>
+        <f>'[1]Empaque (9)'!K42</f>
         <v>0</v>
       </c>
       <c r="K42" s="55"/>
@@ -12297,43 +12292,43 @@
     </row>
     <row r="43" spans="1:36" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="46" t="str">
-        <f>'[2]Empaque (9)'!A43</f>
+        <f>'[1]Empaque (9)'!A43</f>
         <v>Xl</v>
       </c>
-      <c r="B43" s="195">
-        <f>'[2]Empaque (9)'!B43</f>
+      <c r="B43" s="174">
+        <f>'[1]Empaque (9)'!B43</f>
         <v>22</v>
       </c>
       <c r="C43" s="67">
-        <f>'[2]Empaque (9)'!C43</f>
+        <f>'[1]Empaque (9)'!C43</f>
         <v>0</v>
       </c>
       <c r="D43" s="49" t="str">
-        <f>'[2]Empaque (9)'!D43</f>
+        <f>'[1]Empaque (9)'!D43</f>
         <v/>
       </c>
       <c r="E43" s="50">
-        <f>'[2]Empaque (9)'!F43</f>
+        <f>'[1]Empaque (9)'!F43</f>
         <v>0</v>
       </c>
       <c r="F43" s="51">
-        <f>'[2]Empaque (9)'!G43</f>
+        <f>'[1]Empaque (9)'!G43</f>
         <v>0</v>
       </c>
       <c r="G43" s="68">
-        <f>'[2]Empaque (9)'!H43</f>
+        <f>'[1]Empaque (9)'!H43</f>
         <v>0</v>
       </c>
       <c r="H43" s="67">
-        <f>'[2]Empaque (9)'!I43</f>
+        <f>'[1]Empaque (9)'!I43</f>
         <v>0</v>
       </c>
       <c r="I43" s="53">
-        <f>'[2]Empaque (9)'!J43</f>
+        <f>'[1]Empaque (9)'!J43</f>
         <v>0</v>
       </c>
       <c r="J43" s="54">
-        <f>'[2]Empaque (9)'!K43</f>
+        <f>'[1]Empaque (9)'!K43</f>
         <v>0</v>
       </c>
       <c r="K43" s="69"/>
@@ -12357,43 +12352,43 @@
     </row>
     <row r="44" spans="1:36" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="46" t="str">
-        <f>'[2]Empaque (9)'!A44</f>
+        <f>'[1]Empaque (9)'!A44</f>
         <v>Lg</v>
       </c>
-      <c r="B44" s="194">
-        <f>'[2]Empaque (9)'!B44</f>
+      <c r="B44" s="173">
+        <f>'[1]Empaque (9)'!B44</f>
         <v>22</v>
       </c>
       <c r="C44" s="67">
-        <f>'[2]Empaque (9)'!C44</f>
+        <f>'[1]Empaque (9)'!C44</f>
         <v>0</v>
       </c>
       <c r="D44" s="49" t="str">
-        <f>'[2]Empaque (9)'!D44</f>
+        <f>'[1]Empaque (9)'!D44</f>
         <v/>
       </c>
       <c r="E44" s="50">
-        <f>'[2]Empaque (9)'!F44</f>
+        <f>'[1]Empaque (9)'!F44</f>
         <v>0</v>
       </c>
       <c r="F44" s="51">
-        <f>'[2]Empaque (9)'!G44</f>
+        <f>'[1]Empaque (9)'!G44</f>
         <v>0</v>
       </c>
       <c r="G44" s="68">
-        <f>'[2]Empaque (9)'!H44</f>
+        <f>'[1]Empaque (9)'!H44</f>
         <v>0</v>
       </c>
       <c r="H44" s="67">
-        <f>'[2]Empaque (9)'!I44</f>
+        <f>'[1]Empaque (9)'!I44</f>
         <v>0</v>
       </c>
       <c r="I44" s="53">
-        <f>'[2]Empaque (9)'!J44</f>
+        <f>'[1]Empaque (9)'!J44</f>
         <v>0</v>
       </c>
       <c r="J44" s="54">
-        <f>'[2]Empaque (9)'!K44</f>
+        <f>'[1]Empaque (9)'!K44</f>
         <v>0</v>
       </c>
       <c r="K44" s="69"/>
@@ -12417,43 +12412,43 @@
     </row>
     <row r="45" spans="1:36" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="46" t="str">
-        <f>'[2]Empaque (9)'!A45</f>
+        <f>'[1]Empaque (9)'!A45</f>
         <v>Md</v>
       </c>
-      <c r="B45" s="195">
-        <f>'[2]Empaque (9)'!B45</f>
+      <c r="B45" s="174">
+        <f>'[1]Empaque (9)'!B45</f>
         <v>22</v>
       </c>
       <c r="C45" s="67">
-        <f>'[2]Empaque (9)'!C45</f>
+        <f>'[1]Empaque (9)'!C45</f>
         <v>0</v>
       </c>
       <c r="D45" s="49" t="str">
-        <f>'[2]Empaque (9)'!D45</f>
+        <f>'[1]Empaque (9)'!D45</f>
         <v/>
       </c>
       <c r="E45" s="50">
-        <f>'[2]Empaque (9)'!F45</f>
+        <f>'[1]Empaque (9)'!F45</f>
         <v>0</v>
       </c>
       <c r="F45" s="51">
-        <f>'[2]Empaque (9)'!G45</f>
+        <f>'[1]Empaque (9)'!G45</f>
         <v>0</v>
       </c>
       <c r="G45" s="68">
-        <f>'[2]Empaque (9)'!H45</f>
+        <f>'[1]Empaque (9)'!H45</f>
         <v>0</v>
       </c>
       <c r="H45" s="67">
-        <f>'[2]Empaque (9)'!I45</f>
+        <f>'[1]Empaque (9)'!I45</f>
         <v>0</v>
       </c>
       <c r="I45" s="53">
-        <f>'[2]Empaque (9)'!J45</f>
+        <f>'[1]Empaque (9)'!J45</f>
         <v>0</v>
       </c>
       <c r="J45" s="54">
-        <f>'[2]Empaque (9)'!K45</f>
+        <f>'[1]Empaque (9)'!K45</f>
         <v>0</v>
       </c>
       <c r="K45" s="69"/>
@@ -12477,43 +12472,43 @@
     </row>
     <row r="46" spans="1:36" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="46" t="str">
-        <f>'[2]Empaque (9)'!A46</f>
+        <f>'[1]Empaque (9)'!A46</f>
         <v>Sm</v>
       </c>
-      <c r="B46" s="194">
-        <f>'[2]Empaque (9)'!B46</f>
+      <c r="B46" s="173">
+        <f>'[1]Empaque (9)'!B46</f>
         <v>22</v>
       </c>
       <c r="C46" s="67">
-        <f>'[2]Empaque (9)'!C46</f>
+        <f>'[1]Empaque (9)'!C46</f>
         <v>0</v>
       </c>
       <c r="D46" s="49" t="str">
-        <f>'[2]Empaque (9)'!D46</f>
+        <f>'[1]Empaque (9)'!D46</f>
         <v/>
       </c>
       <c r="E46" s="50">
-        <f>'[2]Empaque (9)'!F46</f>
+        <f>'[1]Empaque (9)'!F46</f>
         <v>0</v>
       </c>
       <c r="F46" s="51">
-        <f>'[2]Empaque (9)'!G46</f>
+        <f>'[1]Empaque (9)'!G46</f>
         <v>0</v>
       </c>
       <c r="G46" s="68">
-        <f>'[2]Empaque (9)'!H46</f>
+        <f>'[1]Empaque (9)'!H46</f>
         <v>0</v>
       </c>
       <c r="H46" s="67">
-        <f>'[2]Empaque (9)'!I46</f>
+        <f>'[1]Empaque (9)'!I46</f>
         <v>0</v>
       </c>
       <c r="I46" s="53">
-        <f>'[2]Empaque (9)'!J46</f>
+        <f>'[1]Empaque (9)'!J46</f>
         <v>0</v>
       </c>
       <c r="J46" s="54">
-        <f>'[2]Empaque (9)'!K46</f>
+        <f>'[1]Empaque (9)'!K46</f>
         <v>0</v>
       </c>
       <c r="K46" s="69"/>
@@ -12537,43 +12532,43 @@
     </row>
     <row r="47" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="79" t="str">
-        <f>'[2]Empaque (9)'!A47</f>
+        <f>'[1]Empaque (9)'!A47</f>
         <v>Mixto</v>
       </c>
-      <c r="B47" s="196">
-        <f>'[2]Empaque (9)'!B47</f>
+      <c r="B47" s="175">
+        <f>'[1]Empaque (9)'!B47</f>
         <v>0</v>
       </c>
       <c r="C47" s="81">
-        <f>'[2]Empaque (9)'!C47</f>
+        <f>'[1]Empaque (9)'!C47</f>
         <v>0</v>
       </c>
       <c r="D47" s="82" t="str">
-        <f>'[2]Empaque (9)'!D47</f>
+        <f>'[1]Empaque (9)'!D47</f>
         <v/>
       </c>
       <c r="E47" s="83">
-        <f>'[2]Empaque (9)'!F47</f>
+        <f>'[1]Empaque (9)'!F47</f>
         <v>0</v>
       </c>
       <c r="F47" s="84">
-        <f>'[2]Empaque (9)'!G47</f>
+        <f>'[1]Empaque (9)'!G47</f>
         <v>0</v>
       </c>
       <c r="G47" s="85">
-        <f>'[2]Empaque (9)'!H47</f>
+        <f>'[1]Empaque (9)'!H47</f>
         <v>0</v>
       </c>
       <c r="H47" s="81">
-        <f>'[2]Empaque (9)'!I47</f>
+        <f>'[1]Empaque (9)'!I47</f>
         <v>0</v>
       </c>
       <c r="I47" s="86">
-        <f>'[2]Empaque (9)'!J47</f>
+        <f>'[1]Empaque (9)'!J47</f>
         <v>0</v>
       </c>
       <c r="J47" s="87">
-        <f>'[2]Empaque (9)'!K47</f>
+        <f>'[1]Empaque (9)'!K47</f>
         <v>0</v>
       </c>
       <c r="K47" s="88"/>
@@ -12598,35 +12593,35 @@
     </row>
     <row r="48" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C48" s="96">
-        <f>'[2]Empaque (9)'!C48</f>
+        <f>'[1]Empaque (9)'!C48</f>
         <v>0</v>
       </c>
       <c r="D48" s="97" t="str">
-        <f>'[2]Empaque (9)'!D48</f>
+        <f>'[1]Empaque (9)'!D48</f>
         <v/>
       </c>
       <c r="E48" s="98">
-        <f>'[2]Empaque (9)'!F48</f>
+        <f>'[1]Empaque (9)'!F48</f>
         <v>0</v>
       </c>
       <c r="F48" s="99">
-        <f>'[2]Empaque (9)'!G48</f>
+        <f>'[1]Empaque (9)'!G48</f>
         <v>0</v>
       </c>
       <c r="G48" s="100">
-        <f>'[2]Empaque (9)'!H48</f>
+        <f>'[1]Empaque (9)'!H48</f>
         <v>0</v>
       </c>
       <c r="H48" s="100">
-        <f>'[2]Empaque (9)'!I48</f>
+        <f>'[1]Empaque (9)'!I48</f>
         <v>0</v>
       </c>
       <c r="I48" s="100">
-        <f>'[2]Empaque (9)'!J48</f>
+        <f>'[1]Empaque (9)'!J48</f>
         <v>0</v>
       </c>
       <c r="J48" s="101">
-        <f>'[2]Empaque (9)'!K48</f>
+        <f>'[1]Empaque (9)'!K48</f>
         <v>0</v>
       </c>
       <c r="K48" s="102">
@@ -12654,11 +12649,11 @@
     </row>
     <row r="49" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="41" t="str">
-        <f>'[2]Empaque (9)'!A49</f>
+        <f>'[1]Empaque (9)'!A49</f>
         <v>DF Clam 24 Lb x 50</v>
       </c>
       <c r="B49" s="42" t="str">
-        <f>'[2]Empaque (9)'!B49</f>
+        <f>'[1]Empaque (9)'!B49</f>
         <v>lb</v>
       </c>
       <c r="C49" s="109"/>
@@ -12679,11 +12674,11 @@
       <c r="P49" s="58"/>
       <c r="S49" s="10"/>
       <c r="Z49" s="41" t="str">
-        <f>'[2]Empaque (9)'!AA49</f>
+        <f>'[1]Empaque (9)'!AA49</f>
         <v>DF Clam 24 Lb x 50</v>
       </c>
       <c r="AA49" s="44" t="str">
-        <f>'[2]Empaque (9)'!AB49</f>
+        <f>'[1]Empaque (9)'!AB49</f>
         <v>lb</v>
       </c>
       <c r="AE49" s="6" t="s">
@@ -12697,43 +12692,43 @@
     </row>
     <row r="50" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="46" t="str">
-        <f>'[2]Empaque (9)'!A50</f>
+        <f>'[1]Empaque (9)'!A50</f>
         <v>Jb</v>
       </c>
       <c r="B50" s="47">
-        <f>'[2]Empaque (9)'!B50</f>
+        <f>'[1]Empaque (9)'!B50</f>
         <v>24</v>
       </c>
       <c r="C50" s="48">
-        <f>'[2]Empaque (9)'!C50</f>
+        <f>'[1]Empaque (9)'!C50</f>
         <v>0</v>
       </c>
       <c r="D50" s="49" t="str">
-        <f>'[2]Empaque (9)'!D50</f>
+        <f>'[1]Empaque (9)'!D50</f>
         <v/>
       </c>
       <c r="E50" s="50">
-        <f>'[2]Empaque (9)'!F50</f>
+        <f>'[1]Empaque (9)'!F50</f>
         <v>0</v>
       </c>
       <c r="F50" s="51">
-        <f>'[2]Empaque (9)'!G50</f>
+        <f>'[1]Empaque (9)'!G50</f>
         <v>0</v>
       </c>
       <c r="G50" s="52">
-        <f>'[2]Empaque (9)'!H50</f>
+        <f>'[1]Empaque (9)'!H50</f>
         <v>0</v>
       </c>
       <c r="H50" s="48">
-        <f>'[2]Empaque (9)'!I50</f>
+        <f>'[1]Empaque (9)'!I50</f>
         <v>0</v>
       </c>
       <c r="I50" s="53">
-        <f>'[2]Empaque (9)'!J50</f>
+        <f>'[1]Empaque (9)'!J50</f>
         <v>0</v>
       </c>
       <c r="J50" s="117">
-        <f>'[2]Empaque (9)'!K50</f>
+        <f>'[1]Empaque (9)'!K50</f>
         <v>0</v>
       </c>
       <c r="K50" s="55"/>
@@ -12766,19 +12761,19 @@
         <v>0</v>
       </c>
       <c r="Z50" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA50</f>
+        <f>'[1]Empaque (9)'!AA50</f>
         <v>Jb</v>
       </c>
       <c r="AA50" s="61">
-        <f>'[2]Empaque (9)'!AB50</f>
+        <f>'[1]Empaque (9)'!AB50</f>
         <v>24</v>
       </c>
       <c r="AB50" s="62">
-        <f>'[2]Empaque (9)'!AC50</f>
+        <f>'[1]Empaque (9)'!AC50</f>
         <v>0</v>
       </c>
       <c r="AC50" s="63">
-        <f>'[2]Empaque (9)'!AD50</f>
+        <f>'[1]Empaque (9)'!AD50</f>
         <v>0</v>
       </c>
       <c r="AG50" s="64"/>
@@ -12791,43 +12786,43 @@
     </row>
     <row r="51" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="46" t="str">
-        <f>'[2]Empaque (9)'!A51</f>
+        <f>'[1]Empaque (9)'!A51</f>
         <v>Xl</v>
       </c>
       <c r="B51" s="66">
-        <f>'[2]Empaque (9)'!B51</f>
+        <f>'[1]Empaque (9)'!B51</f>
         <v>24</v>
       </c>
       <c r="C51" s="67">
-        <f>'[2]Empaque (9)'!C51</f>
+        <f>'[1]Empaque (9)'!C51</f>
         <v>0</v>
       </c>
       <c r="D51" s="49" t="str">
-        <f>'[2]Empaque (9)'!D51</f>
+        <f>'[1]Empaque (9)'!D51</f>
         <v/>
       </c>
       <c r="E51" s="50">
-        <f>'[2]Empaque (9)'!F51</f>
+        <f>'[1]Empaque (9)'!F51</f>
         <v>0</v>
       </c>
       <c r="F51" s="51">
-        <f>'[2]Empaque (9)'!G51</f>
+        <f>'[1]Empaque (9)'!G51</f>
         <v>0</v>
       </c>
       <c r="G51" s="68">
-        <f>'[2]Empaque (9)'!H51</f>
+        <f>'[1]Empaque (9)'!H51</f>
         <v>0</v>
       </c>
       <c r="H51" s="67">
-        <f>'[2]Empaque (9)'!I51</f>
+        <f>'[1]Empaque (9)'!I51</f>
         <v>0</v>
       </c>
       <c r="I51" s="53">
-        <f>'[2]Empaque (9)'!J51</f>
+        <f>'[1]Empaque (9)'!J51</f>
         <v>0</v>
       </c>
       <c r="J51" s="117">
-        <f>'[2]Empaque (9)'!K51</f>
+        <f>'[1]Empaque (9)'!K51</f>
         <v>0</v>
       </c>
       <c r="K51" s="69"/>
@@ -12845,19 +12840,19 @@
       </c>
       <c r="S51" s="10"/>
       <c r="Z51" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA51</f>
+        <f>'[1]Empaque (9)'!AA51</f>
         <v>Xl</v>
       </c>
       <c r="AA51" s="72">
-        <f>'[2]Empaque (9)'!AB51</f>
+        <f>'[1]Empaque (9)'!AB51</f>
         <v>24</v>
       </c>
       <c r="AB51" s="62">
-        <f>'[2]Empaque (9)'!AC51</f>
+        <f>'[1]Empaque (9)'!AC51</f>
         <v>0</v>
       </c>
       <c r="AC51" s="63">
-        <f>'[2]Empaque (9)'!AD51</f>
+        <f>'[1]Empaque (9)'!AD51</f>
         <v>0</v>
       </c>
       <c r="AG51" s="73"/>
@@ -12870,43 +12865,43 @@
     </row>
     <row r="52" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="46" t="str">
-        <f>'[2]Empaque (9)'!A52</f>
+        <f>'[1]Empaque (9)'!A52</f>
         <v>Lg</v>
       </c>
       <c r="B52" s="47">
-        <f>'[2]Empaque (9)'!B52</f>
+        <f>'[1]Empaque (9)'!B52</f>
         <v>24</v>
       </c>
       <c r="C52" s="67">
-        <f>'[2]Empaque (9)'!C52</f>
+        <f>'[1]Empaque (9)'!C52</f>
         <v>0</v>
       </c>
       <c r="D52" s="49" t="str">
-        <f>'[2]Empaque (9)'!D52</f>
+        <f>'[1]Empaque (9)'!D52</f>
         <v/>
       </c>
       <c r="E52" s="50">
-        <f>'[2]Empaque (9)'!F52</f>
+        <f>'[1]Empaque (9)'!F52</f>
         <v>0</v>
       </c>
       <c r="F52" s="51">
-        <f>'[2]Empaque (9)'!G52</f>
+        <f>'[1]Empaque (9)'!G52</f>
         <v>0</v>
       </c>
       <c r="G52" s="68">
-        <f>'[2]Empaque (9)'!H52</f>
+        <f>'[1]Empaque (9)'!H52</f>
         <v>0</v>
       </c>
       <c r="H52" s="67">
-        <f>'[2]Empaque (9)'!I52</f>
+        <f>'[1]Empaque (9)'!I52</f>
         <v>0</v>
       </c>
       <c r="I52" s="53">
-        <f>'[2]Empaque (9)'!J52</f>
+        <f>'[1]Empaque (9)'!J52</f>
         <v>0</v>
       </c>
       <c r="J52" s="117">
-        <f>'[2]Empaque (9)'!K52</f>
+        <f>'[1]Empaque (9)'!K52</f>
         <v>0</v>
       </c>
       <c r="K52" s="69"/>
@@ -12924,19 +12919,19 @@
       </c>
       <c r="S52" s="10"/>
       <c r="Z52" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA52</f>
+        <f>'[1]Empaque (9)'!AA52</f>
         <v>Lg</v>
       </c>
       <c r="AA52" s="61">
-        <f>'[2]Empaque (9)'!AB52</f>
+        <f>'[1]Empaque (9)'!AB52</f>
         <v>24</v>
       </c>
       <c r="AB52" s="62">
-        <f>'[2]Empaque (9)'!AC52</f>
+        <f>'[1]Empaque (9)'!AC52</f>
         <v>0</v>
       </c>
       <c r="AC52" s="63">
-        <f>'[2]Empaque (9)'!AD52</f>
+        <f>'[1]Empaque (9)'!AD52</f>
         <v>0</v>
       </c>
       <c r="AG52" s="73"/>
@@ -12949,43 +12944,43 @@
     </row>
     <row r="53" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="46" t="str">
-        <f>'[2]Empaque (9)'!A53</f>
+        <f>'[1]Empaque (9)'!A53</f>
         <v>Md</v>
       </c>
       <c r="B53" s="66">
-        <f>'[2]Empaque (9)'!B53</f>
+        <f>'[1]Empaque (9)'!B53</f>
         <v>24</v>
       </c>
       <c r="C53" s="67">
-        <f>'[2]Empaque (9)'!C53</f>
+        <f>'[1]Empaque (9)'!C53</f>
         <v>0</v>
       </c>
       <c r="D53" s="49" t="str">
-        <f>'[2]Empaque (9)'!D53</f>
+        <f>'[1]Empaque (9)'!D53</f>
         <v/>
       </c>
       <c r="E53" s="50">
-        <f>'[2]Empaque (9)'!F53</f>
+        <f>'[1]Empaque (9)'!F53</f>
         <v>0</v>
       </c>
       <c r="F53" s="51">
-        <f>'[2]Empaque (9)'!G53</f>
+        <f>'[1]Empaque (9)'!G53</f>
         <v>0</v>
       </c>
       <c r="G53" s="68">
-        <f>'[2]Empaque (9)'!H53</f>
+        <f>'[1]Empaque (9)'!H53</f>
         <v>0</v>
       </c>
       <c r="H53" s="67">
-        <f>'[2]Empaque (9)'!I53</f>
+        <f>'[1]Empaque (9)'!I53</f>
         <v>0</v>
       </c>
       <c r="I53" s="53">
-        <f>'[2]Empaque (9)'!J53</f>
+        <f>'[1]Empaque (9)'!J53</f>
         <v>0</v>
       </c>
       <c r="J53" s="117">
-        <f>'[2]Empaque (9)'!K53</f>
+        <f>'[1]Empaque (9)'!K53</f>
         <v>0</v>
       </c>
       <c r="K53" s="69"/>
@@ -13003,19 +12998,19 @@
       </c>
       <c r="S53" s="10"/>
       <c r="Z53" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA53</f>
+        <f>'[1]Empaque (9)'!AA53</f>
         <v>Md</v>
       </c>
       <c r="AA53" s="72">
-        <f>'[2]Empaque (9)'!AB53</f>
+        <f>'[1]Empaque (9)'!AB53</f>
         <v>24</v>
       </c>
       <c r="AB53" s="62">
-        <f>'[2]Empaque (9)'!AC53</f>
+        <f>'[1]Empaque (9)'!AC53</f>
         <v>0</v>
       </c>
       <c r="AC53" s="63">
-        <f>'[2]Empaque (9)'!AD53</f>
+        <f>'[1]Empaque (9)'!AD53</f>
         <v>0</v>
       </c>
       <c r="AG53" s="73"/>
@@ -13028,43 +13023,43 @@
     </row>
     <row r="54" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="46" t="str">
-        <f>'[2]Empaque (9)'!A54</f>
+        <f>'[1]Empaque (9)'!A54</f>
         <v>Sm</v>
       </c>
       <c r="B54" s="47">
-        <f>'[2]Empaque (9)'!B54</f>
+        <f>'[1]Empaque (9)'!B54</f>
         <v>24</v>
       </c>
       <c r="C54" s="67">
-        <f>'[2]Empaque (9)'!C54</f>
+        <f>'[1]Empaque (9)'!C54</f>
         <v>0</v>
       </c>
       <c r="D54" s="49" t="str">
-        <f>'[2]Empaque (9)'!D54</f>
+        <f>'[1]Empaque (9)'!D54</f>
         <v/>
       </c>
       <c r="E54" s="50">
-        <f>'[2]Empaque (9)'!F54</f>
+        <f>'[1]Empaque (9)'!F54</f>
         <v>0</v>
       </c>
       <c r="F54" s="51">
-        <f>'[2]Empaque (9)'!G54</f>
+        <f>'[1]Empaque (9)'!G54</f>
         <v>0</v>
       </c>
       <c r="G54" s="68">
-        <f>'[2]Empaque (9)'!H54</f>
+        <f>'[1]Empaque (9)'!H54</f>
         <v>0</v>
       </c>
       <c r="H54" s="67">
-        <f>'[2]Empaque (9)'!I54</f>
+        <f>'[1]Empaque (9)'!I54</f>
         <v>0</v>
       </c>
       <c r="I54" s="53">
-        <f>'[2]Empaque (9)'!J54</f>
+        <f>'[1]Empaque (9)'!J54</f>
         <v>0</v>
       </c>
       <c r="J54" s="117">
-        <f>'[2]Empaque (9)'!K54</f>
+        <f>'[1]Empaque (9)'!K54</f>
         <v>0</v>
       </c>
       <c r="K54" s="69"/>
@@ -13081,19 +13076,19 @@
         <v>0</v>
       </c>
       <c r="Z54" s="60" t="str">
-        <f>'[2]Empaque (9)'!AA54</f>
+        <f>'[1]Empaque (9)'!AA54</f>
         <v>Sm</v>
       </c>
       <c r="AA54" s="61">
-        <f>'[2]Empaque (9)'!AB54</f>
+        <f>'[1]Empaque (9)'!AB54</f>
         <v>24</v>
       </c>
       <c r="AB54" s="77">
-        <f>'[2]Empaque (9)'!AC54</f>
+        <f>'[1]Empaque (9)'!AC54</f>
         <v>0</v>
       </c>
       <c r="AC54" s="63">
-        <f>'[2]Empaque (9)'!AD54</f>
+        <f>'[1]Empaque (9)'!AD54</f>
         <v>0</v>
       </c>
       <c r="AG54" s="64"/>
@@ -13106,43 +13101,43 @@
     </row>
     <row r="55" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="79" t="str">
-        <f>'[2]Empaque (9)'!A55</f>
+        <f>'[1]Empaque (9)'!A55</f>
         <v>Mixto</v>
       </c>
       <c r="B55" s="85">
-        <f>'[2]Empaque (9)'!B55</f>
+        <f>'[1]Empaque (9)'!B55</f>
         <v>0</v>
       </c>
       <c r="C55" s="81">
-        <f>'[2]Empaque (9)'!C55</f>
+        <f>'[1]Empaque (9)'!C55</f>
         <v>0</v>
       </c>
       <c r="D55" s="82" t="str">
-        <f>'[2]Empaque (9)'!D55</f>
+        <f>'[1]Empaque (9)'!D55</f>
         <v/>
       </c>
       <c r="E55" s="83">
-        <f>'[2]Empaque (9)'!F55</f>
+        <f>'[1]Empaque (9)'!F55</f>
         <v>0</v>
       </c>
       <c r="F55" s="84">
-        <f>'[2]Empaque (9)'!G55</f>
+        <f>'[1]Empaque (9)'!G55</f>
         <v>0</v>
       </c>
       <c r="G55" s="85">
-        <f>'[2]Empaque (9)'!H55</f>
+        <f>'[1]Empaque (9)'!H55</f>
         <v>0</v>
       </c>
       <c r="H55" s="81">
-        <f>'[2]Empaque (9)'!I55</f>
+        <f>'[1]Empaque (9)'!I55</f>
         <v>0</v>
       </c>
       <c r="I55" s="86">
-        <f>'[2]Empaque (9)'!J55</f>
+        <f>'[1]Empaque (9)'!J55</f>
         <v>0</v>
       </c>
       <c r="J55" s="118">
-        <f>'[2]Empaque (9)'!K55</f>
+        <f>'[1]Empaque (9)'!K55</f>
         <v>0</v>
       </c>
       <c r="K55" s="88"/>
@@ -13160,19 +13155,19 @@
         <v>0</v>
       </c>
       <c r="Z55" s="90" t="str">
-        <f>'[2]Empaque (9)'!AA55</f>
+        <f>'[1]Empaque (9)'!AA55</f>
         <v>xs</v>
       </c>
       <c r="AA55" s="91">
-        <f>'[2]Empaque (9)'!AB55</f>
+        <f>'[1]Empaque (9)'!AB55</f>
         <v>0</v>
       </c>
       <c r="AB55" s="92">
-        <f>'[2]Empaque (9)'!AC55</f>
+        <f>'[1]Empaque (9)'!AC55</f>
         <v>0</v>
       </c>
       <c r="AC55" s="93">
-        <f>'[2]Empaque (9)'!AD55</f>
+        <f>'[1]Empaque (9)'!AD55</f>
         <v>0</v>
       </c>
       <c r="AG55" s="94"/>
@@ -13185,35 +13180,35 @@
     </row>
     <row r="56" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C56" s="96">
-        <f>'[2]Empaque (9)'!C56</f>
+        <f>'[1]Empaque (9)'!C56</f>
         <v>0</v>
       </c>
       <c r="D56" s="97" t="str">
-        <f>'[2]Empaque (9)'!D56</f>
+        <f>'[1]Empaque (9)'!D56</f>
         <v/>
       </c>
       <c r="E56" s="98">
-        <f>'[2]Empaque (9)'!F56</f>
+        <f>'[1]Empaque (9)'!F56</f>
         <v>0</v>
       </c>
       <c r="F56" s="99">
-        <f>'[2]Empaque (9)'!G56</f>
+        <f>'[1]Empaque (9)'!G56</f>
         <v>0</v>
       </c>
       <c r="G56" s="100">
-        <f>'[2]Empaque (9)'!H56</f>
+        <f>'[1]Empaque (9)'!H56</f>
         <v>0</v>
       </c>
       <c r="H56" s="100">
-        <f>'[2]Empaque (9)'!I56</f>
+        <f>'[1]Empaque (9)'!I56</f>
         <v>0</v>
       </c>
       <c r="I56" s="100">
-        <f>'[2]Empaque (9)'!J56</f>
+        <f>'[1]Empaque (9)'!J56</f>
         <v>0</v>
       </c>
       <c r="J56" s="119">
-        <f>'[2]Empaque (9)'!K56</f>
+        <f>'[1]Empaque (9)'!K56</f>
         <v>0</v>
       </c>
       <c r="K56" s="102">
@@ -13232,11 +13227,11 @@
       <c r="O56" s="55"/>
       <c r="AA56" s="104"/>
       <c r="AB56" s="105">
-        <f>'[2]Empaque (9)'!AC56</f>
+        <f>'[1]Empaque (9)'!AC56</f>
         <v>0</v>
       </c>
       <c r="AC56" s="106">
-        <f>'[2]Empaque (9)'!AD56</f>
+        <f>'[1]Empaque (9)'!AD56</f>
         <v>0</v>
       </c>
       <c r="AH56" s="107">
@@ -13267,34 +13262,34 @@
         <v>34</v>
       </c>
       <c r="C58" s="96">
-        <f>'[2]Empaque (9)'!C58</f>
+        <f>'[1]Empaque (9)'!C58</f>
         <v>372</v>
       </c>
       <c r="E58" s="121">
-        <f>'[2]Empaque (9)'!F59</f>
+        <f>'[1]Empaque (9)'!F59</f>
         <v>0</v>
       </c>
       <c r="F58" s="122">
-        <f>'[2]Empaque (9)'!G58</f>
+        <f>'[1]Empaque (9)'!G58</f>
         <v>0</v>
       </c>
       <c r="G58" s="96">
-        <f>'[2]Empaque (9)'!H58</f>
+        <f>'[1]Empaque (9)'!H58</f>
         <v>0</v>
       </c>
       <c r="H58" s="122">
-        <f>'[2]Empaque (9)'!I58</f>
+        <f>'[1]Empaque (9)'!I58</f>
         <v>696</v>
       </c>
       <c r="I58" s="96">
-        <f>'[2]Empaque (9)'!J58</f>
+        <f>'[1]Empaque (9)'!J58</f>
         <v>0</v>
       </c>
       <c r="J58" s="122">
-        <f>'[2]Empaque (9)'!K58</f>
-        <v>0</v>
-      </c>
-      <c r="K58" s="197">
+        <f>'[1]Empaque (9)'!K58</f>
+        <v>0</v>
+      </c>
+      <c r="K58" s="176">
         <f>(K26*C26)+(K27*C27)+(K28*C28)+(K29*C29)+(K30*C30)+(K31*C31)</f>
         <v>148800</v>
       </c>
@@ -13310,16 +13305,16 @@
         <v>2</v>
       </c>
       <c r="Q58" s="124">
-        <f>'[2]Empaque (9)'!O58</f>
+        <f>'[1]Empaque (9)'!O58</f>
         <v>4650</v>
       </c>
       <c r="Z58" s="1" t="str">
-        <f>'[2]Empaque (9)'!AA58</f>
+        <f>'[1]Empaque (9)'!AA58</f>
         <v>Totales</v>
       </c>
       <c r="AA58" s="104"/>
       <c r="AB58" s="96">
-        <f>'[2]Empaque (9)'!AC58</f>
+        <f>'[1]Empaque (9)'!AC58</f>
         <v>1587</v>
       </c>
       <c r="AC58" s="125"/>
@@ -13342,15 +13337,15 @@
     <row r="59" spans="1:36" x14ac:dyDescent="0.3">
       <c r="C59" s="109"/>
       <c r="G59" s="7"/>
-      <c r="I59" s="198" t="s">
+      <c r="I59" s="177" t="s">
         <v>20</v>
       </c>
-      <c r="J59" s="199">
+      <c r="J59" s="178">
         <f>I16+I24+I56</f>
         <v>0</v>
       </c>
       <c r="AB59" s="128">
-        <f>'[2]Empaque (9)'!AC59</f>
+        <f>'[1]Empaque (9)'!AC59</f>
         <v>317.39999999999998</v>
       </c>
       <c r="AC59" s="20" t="s">
@@ -13362,13 +13357,13 @@
         <v>35</v>
       </c>
       <c r="C60" s="130">
-        <f>'[2]Empaque (9)'!C60</f>
+        <f>'[1]Empaque (9)'!C60</f>
         <v>297.60000000000002</v>
       </c>
-      <c r="I60" s="198" t="s">
+      <c r="I60" s="177" t="s">
         <v>21</v>
       </c>
-      <c r="J60" s="199">
+      <c r="J60" s="178">
         <f>I32+I40</f>
         <v>0</v>
       </c>
@@ -13404,15 +13399,15 @@
         <v>2</v>
       </c>
       <c r="G63" s="135">
-        <f>'[2]Empaque (9)'!R2</f>
+        <f>'[1]Empaque (9)'!R2</f>
         <v>4650</v>
       </c>
       <c r="H63" s="136">
-        <f ca="1">'[2]Empaque (9)'!S2</f>
+        <f ca="1">'[1]Empaque (9)'!S2</f>
         <v>0.90921533738732574</v>
       </c>
       <c r="I63" s="6" t="str">
-        <f>'[2]Empaque (9)'!T2</f>
+        <f>'[1]Empaque (9)'!T2</f>
         <v>% emp kg</v>
       </c>
       <c r="Z63" s="133" t="s">
@@ -13428,26 +13423,26 @@
         <v>41</v>
       </c>
       <c r="B64" s="138">
-        <f>'[2]Empaque (9)'!N3</f>
+        <f>'[1]Empaque (9)'!N3</f>
         <v>0</v>
       </c>
       <c r="C64" s="139">
-        <f>'[2]Empaque (9)'!O3</f>
+        <f>'[1]Empaque (9)'!O3</f>
         <v>0</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G64" s="140">
-        <f>'[2]Empaque (9)'!R3</f>
+        <f>'[1]Empaque (9)'!R3</f>
         <v>0.96505376344086025</v>
       </c>
       <c r="H64" s="141">
-        <f>'[2]Empaque (9)'!S3</f>
+        <f>'[1]Empaque (9)'!S3</f>
         <v>0.91129032258064513</v>
       </c>
       <c r="I64" s="142" t="str">
-        <f>'[2]Empaque (9)'!T3</f>
+        <f>'[1]Empaque (9)'!T3</f>
         <v>Jb, XL</v>
       </c>
       <c r="Z64" s="1"/>
@@ -13457,26 +13452,26 @@
         <v>43</v>
       </c>
       <c r="B65" s="143">
-        <f ca="1">'[2]Empaque (9)'!N4</f>
+        <f ca="1">'[1]Empaque (9)'!N4</f>
         <v>13.266666666666667</v>
       </c>
       <c r="C65" s="139">
-        <f ca="1">'[2]Empaque (9)'!O4</f>
+        <f ca="1">'[1]Empaque (9)'!O4</f>
         <v>5114.3</v>
       </c>
-      <c r="G65" s="200">
-        <f ca="1">'[2]Empaque (9)'!R4</f>
+      <c r="G65" s="179">
+        <f ca="1">'[1]Empaque (9)'!R4</f>
         <v>0.9346733668341709</v>
       </c>
       <c r="H65" s="20" t="str">
-        <f>'[2]Empaque (9)'!S4</f>
+        <f>'[1]Empaque (9)'!S4</f>
         <v>cajas x cubeta</v>
       </c>
       <c r="Z65" s="144" t="s">
         <v>44</v>
       </c>
       <c r="AB65" s="145" t="e">
-        <f>SUMIFS([2]Listado!H6:H100,[2]Listado!B6:B135,"&gt;="&amp;AE1,[2]Listado!B6:B135,"&lt;="&amp;AF1)</f>
+        <f>SUMIFS([1]Listado!H6:H100,[1]Listado!B6:B135,"&gt;="&amp;AE1,[1]Listado!B6:B135,"&lt;="&amp;AF1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -13485,29 +13480,29 @@
         <v>45</v>
       </c>
       <c r="B66" s="138">
-        <f ca="1">'[2]Empaque (9)'!N5</f>
+        <f ca="1">'[1]Empaque (9)'!N5</f>
         <v>0</v>
       </c>
       <c r="C66" s="139">
-        <f ca="1">'[2]Empaque (9)'!O5</f>
+        <f ca="1">'[1]Empaque (9)'!O5</f>
         <v>0</v>
       </c>
       <c r="G66" s="146">
-        <f ca="1">'[2]Empaque (9)'!R5</f>
+        <f ca="1">'[1]Empaque (9)'!R5</f>
         <v>28.040201005025125</v>
       </c>
       <c r="H66" s="20" t="str">
-        <f>'[2]Empaque (9)'!S5</f>
+        <f>'[1]Empaque (9)'!S5</f>
         <v>Cajas x bin</v>
       </c>
     </row>
     <row r="67" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C67" s="147">
-        <f ca="1">'[2]Empaque (9)'!O6</f>
+        <f ca="1">'[1]Empaque (9)'!O6</f>
         <v>5114.3</v>
       </c>
       <c r="G67" s="2" t="str">
-        <f>'[2]Empaque (9)'!R6</f>
+        <f>'[1]Empaque (9)'!R6</f>
         <v>Por pasar y reproc</v>
       </c>
       <c r="H67" s="2"/>
@@ -13517,18 +13512,18 @@
         <v>46</v>
       </c>
       <c r="C68" s="136">
-        <f>'[2]Empaque (9)'!O7</f>
+        <f>'[1]Empaque (9)'!O7</f>
         <v>0</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>43</v>
       </c>
       <c r="G68" s="148">
-        <f>'[2]Empaque (9)'!R7</f>
+        <f>'[1]Empaque (9)'!R7</f>
         <v>0</v>
       </c>
       <c r="H68" s="149">
-        <f>'[2]Empaque (9)'!S7</f>
+        <f>'[1]Empaque (9)'!S7</f>
         <v>0</v>
       </c>
       <c r="I68" s="37"/>
@@ -13538,18 +13533,18 @@
         <v>47</v>
       </c>
       <c r="C69" s="136">
-        <f>'[2]Empaque (9)'!O8</f>
+        <f>'[1]Empaque (9)'!O8</f>
         <v>1</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>45</v>
       </c>
       <c r="G69" s="148">
-        <f>'[2]Empaque (9)'!R8</f>
+        <f>'[1]Empaque (9)'!R8</f>
         <v>0</v>
       </c>
       <c r="H69" s="149">
-        <f>'[2]Empaque (9)'!S8</f>
+        <f>'[1]Empaque (9)'!S8</f>
         <v>0</v>
       </c>
       <c r="I69" s="37"/>
@@ -13580,7 +13575,7 @@
         <v>45</v>
       </c>
       <c r="B72" s="154">
-        <f ca="1">'[2]Cajas x Semana'!F130</f>
+        <f ca="1">'[1]Cajas x Semana'!F130</f>
         <v>372</v>
       </c>
       <c r="C72" s="155">
@@ -13597,7 +13592,7 @@
         <v>49</v>
       </c>
       <c r="B73" s="156">
-        <f ca="1">'[2]Cajas x Semana'!F132</f>
+        <f ca="1">'[1]Cajas x Semana'!F132</f>
         <v>0.91129032258064513</v>
       </c>
       <c r="C73" s="17"/>
@@ -13620,7 +13615,7 @@
         <v>69</v>
       </c>
       <c r="B76" s="161">
-        <f ca="1">VLOOKUP(G4,'[2]Cajas Acum x Fecha'!$B$11:$I$147,8,FALSE)</f>
+        <f ca="1">VLOOKUP(G4,'[1]Cajas Acum x Fecha'!$B$11:$I$147,8,FALSE)</f>
         <v>1269.5999999999999</v>
       </c>
     </row>
@@ -13665,14 +13660,14 @@
     </row>
     <row r="80" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A80" s="14"/>
-      <c r="B80" s="201"/>
-      <c r="C80" s="202"/>
-      <c r="L80" s="203"/>
+      <c r="B80" s="180"/>
+      <c r="C80" s="181"/>
+      <c r="L80" s="182"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="14"/>
-      <c r="B81" s="201"/>
-      <c r="C81" s="202"/>
+      <c r="B81" s="180"/>
+      <c r="C81" s="181"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
@@ -13753,7 +13748,7 @@
         <v>45889</v>
       </c>
       <c r="C96" s="169">
-        <f>[2]Corte!J7</f>
+        <f>[1]Corte!J7</f>
         <v>46134</v>
       </c>
       <c r="D96" s="169">
@@ -13860,16 +13855,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="Z7:Z8"/>
-    <mergeCell ref="AA7:AA8"/>
-    <mergeCell ref="AB7:AB8"/>
-    <mergeCell ref="AC7:AC8"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="A1:C1"/>
@@ -13878,6 +13863,16 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="G4:J4"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="Z7:Z8"/>
+    <mergeCell ref="AA7:AA8"/>
+    <mergeCell ref="AB7:AB8"/>
+    <mergeCell ref="AC7:AC8"/>
   </mergeCells>
   <conditionalFormatting sqref="C85:C87">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/Info para Claude/Reportes/Empaque/PNG Reportes/Empaque_Hoy.xlsx
+++ b/Info para Claude/Reportes/Empaque/PNG Reportes/Empaque_Hoy.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f087611319785eae/Documentos/GitHub/H2E-Crown/Info para Claude/Reportes/Empaque/PNG Reportes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{62FC8FF9-F488-46BD-B4C6-E467AFC29EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{639F9143-B60B-4909-B9EA-F76D239B12C1}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{62FC8FF9-F488-46BD-B4C6-E467AFC29EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21937FBF-569B-4997-BFC9-F3BEFE0F9FAB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3C31BBD7-DEED-4F95-A4CD-7DCF87BD03C6}"/>
   </bookViews>
   <sheets>
-    <sheet name="p PDF" sheetId="3" r:id="rId1"/>
+    <sheet name="p PDF" sheetId="4" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
@@ -903,7 +903,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1163,42 +1163,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1214,6 +1178,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1226,7 +1193,39 @@
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -1273,7 +1272,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D512800-AEFA-4778-B2A0-61ABE054BD8D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1806DCE3-84D8-43DA-986A-B52935C56BB2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1303,6 +1302,58 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls driveId="F087611319785EAE" itemId="F087611319785EAE!s7c1e8e829e4c4ea1bb203222ae643022">
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Liq"/>
+      <sheetName val="Liq-P&amp;P"/>
+      <sheetName val="Listado"/>
+      <sheetName val="Prom x Semana"/>
+      <sheetName val="Transacciones"/>
+      <sheetName val="Ing - Egr Pend"/>
+      <sheetName val="Reporte Semanal"/>
+      <sheetName val="VENTAS"/>
+      <sheetName val="Retorno x Cliente Nac"/>
+      <sheetName val="Hoja1"/>
+      <sheetName val="Pending 2 Inv (26-1)"/>
+      <sheetName val="GWR Transactions"/>
+      <sheetName val="Listado (2)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6">
+        <row r="74">
+          <cell r="C74">
+            <v>2.4123999999999999</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="C75">
+            <v>0.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1394,8 +1445,8 @@
       <sheetName val="Empaque (80)"/>
       <sheetName val="Totales"/>
       <sheetName val="Tamaños"/>
+      <sheetName val="Cajas x Semana"/>
       <sheetName val="Recuperacion"/>
-      <sheetName val="Cajas x Semana"/>
       <sheetName val="Listado"/>
       <sheetName val="Corte x Var"/>
       <sheetName val="Gráfica Producción"/>
@@ -1414,16 +1465,17 @@
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9">
         <row r="2">
           <cell r="K2">
-            <v>9</v>
+            <v>10</v>
           </cell>
           <cell r="R2">
-            <v>4650</v>
+            <v>3587.5</v>
           </cell>
           <cell r="S2">
-            <v>0.90921533738732574</v>
+            <v>0.91535370287682605</v>
           </cell>
           <cell r="T2" t="str">
             <v>% emp kg</v>
@@ -1437,10 +1489,10 @@
             <v>0</v>
           </cell>
           <cell r="R3">
-            <v>0.96505376344086025</v>
+            <v>0.93728222996515675</v>
           </cell>
           <cell r="S3">
-            <v>0.91129032258064513</v>
+            <v>0.86759581881533099</v>
           </cell>
           <cell r="T3" t="str">
             <v>Jb, XL</v>
@@ -1448,16 +1500,16 @@
         </row>
         <row r="4">
           <cell r="H4">
-            <v>46153</v>
+            <v>46155</v>
           </cell>
           <cell r="N4">
-            <v>13.266666666666667</v>
+            <v>10.166666666666666</v>
           </cell>
           <cell r="O4">
-            <v>5114.3</v>
+            <v>3919.2499999999995</v>
           </cell>
           <cell r="R4">
-            <v>0.9346733668341709</v>
+            <v>0.94098360655737701</v>
           </cell>
           <cell r="S4" t="str">
             <v>cajas x cubeta</v>
@@ -1471,7 +1523,7 @@
             <v>0</v>
           </cell>
           <cell r="R5">
-            <v>28.040201005025125</v>
+            <v>28.229508196721312</v>
           </cell>
           <cell r="S5" t="str">
             <v>Cajas x bin</v>
@@ -1479,7 +1531,7 @@
         </row>
         <row r="6">
           <cell r="O6">
-            <v>5114.3</v>
+            <v>3919.2499999999995</v>
           </cell>
           <cell r="R6" t="str">
             <v>Por pasar y reproc</v>
@@ -1963,19 +2015,19 @@
             <v>12.5</v>
           </cell>
           <cell r="C26">
-            <v>288</v>
+            <v>184</v>
           </cell>
           <cell r="D26">
-            <v>0.77419354838709675</v>
+            <v>0.64111498257839716</v>
           </cell>
           <cell r="I26">
-            <v>516</v>
+            <v>169</v>
           </cell>
           <cell r="J26">
-            <v>0</v>
+            <v>15</v>
           </cell>
           <cell r="K26">
-            <v>0</v>
+            <v>0.20833333333333334</v>
           </cell>
           <cell r="AA26" t="str">
             <v>Jb</v>
@@ -1984,10 +2036,10 @@
             <v>12.5</v>
           </cell>
           <cell r="AC26">
-            <v>1316</v>
+            <v>1500</v>
           </cell>
           <cell r="AD26">
-            <v>0.8292375551354757</v>
+            <v>0.80042689434365</v>
           </cell>
         </row>
         <row r="27">
@@ -1998,19 +2050,16 @@
             <v>12.5</v>
           </cell>
           <cell r="C27">
-            <v>51</v>
+            <v>65</v>
           </cell>
           <cell r="D27">
-            <v>0.13709677419354838</v>
-          </cell>
-          <cell r="I27">
-            <v>110</v>
+            <v>0.2264808362369338</v>
           </cell>
           <cell r="J27">
-            <v>0</v>
+            <v>65</v>
           </cell>
           <cell r="K27">
-            <v>0</v>
+            <v>0.90277777777777779</v>
           </cell>
           <cell r="AA27" t="str">
             <v>Xl</v>
@@ -2019,10 +2068,10 @@
             <v>12.5</v>
           </cell>
           <cell r="AC27">
-            <v>150</v>
+            <v>215</v>
           </cell>
           <cell r="AD27">
-            <v>9.4517958412098299E-2</v>
+            <v>0.11472785485592316</v>
           </cell>
         </row>
         <row r="28">
@@ -2036,16 +2085,16 @@
             <v>20</v>
           </cell>
           <cell r="D28">
-            <v>5.3763440860215055E-2</v>
+            <v>6.968641114982578E-2</v>
           </cell>
           <cell r="I28">
-            <v>38</v>
+            <v>1</v>
           </cell>
           <cell r="J28">
-            <v>0</v>
+            <v>19</v>
           </cell>
           <cell r="K28">
-            <v>0</v>
+            <v>0.2638888888888889</v>
           </cell>
           <cell r="AA28" t="str">
             <v>Lg</v>
@@ -2054,10 +2103,10 @@
             <v>12.5</v>
           </cell>
           <cell r="AC28">
-            <v>65</v>
+            <v>85</v>
           </cell>
           <cell r="AD28">
-            <v>4.0957781978575927E-2</v>
+            <v>4.5357524012806828E-2</v>
           </cell>
         </row>
         <row r="29">
@@ -2068,19 +2117,16 @@
             <v>12.5</v>
           </cell>
           <cell r="C29">
-            <v>4</v>
+            <v>7</v>
           </cell>
           <cell r="D29">
-            <v>1.0752688172043012E-2</v>
-          </cell>
-          <cell r="I29">
-            <v>14</v>
+            <v>2.4390243902439025E-2</v>
           </cell>
           <cell r="J29">
-            <v>0</v>
+            <v>7</v>
           </cell>
           <cell r="K29">
-            <v>0</v>
+            <v>9.7222222222222224E-2</v>
           </cell>
           <cell r="AA29" t="str">
             <v>Md</v>
@@ -2089,10 +2135,10 @@
             <v>12.5</v>
           </cell>
           <cell r="AC29">
-            <v>30</v>
+            <v>37</v>
           </cell>
           <cell r="AD29">
-            <v>1.890359168241966E-2</v>
+            <v>1.9743863393810034E-2</v>
           </cell>
         </row>
         <row r="30">
@@ -2103,19 +2149,16 @@
             <v>12.5</v>
           </cell>
           <cell r="C30">
-            <v>4</v>
+            <v>8</v>
           </cell>
           <cell r="D30">
-            <v>1.0752688172043012E-2</v>
-          </cell>
-          <cell r="I30">
-            <v>13</v>
+            <v>2.7874564459930314E-2</v>
           </cell>
           <cell r="J30">
-            <v>0</v>
+            <v>8</v>
           </cell>
           <cell r="K30">
-            <v>0</v>
+            <v>0.1111111111111111</v>
           </cell>
           <cell r="AA30" t="str">
             <v>Sm</v>
@@ -2124,10 +2167,10 @@
             <v>12.5</v>
           </cell>
           <cell r="AC30">
-            <v>21</v>
+            <v>29</v>
           </cell>
           <cell r="AD30">
-            <v>1.3232514177693762E-2</v>
+            <v>1.5474919957310566E-2</v>
           </cell>
         </row>
         <row r="31">
@@ -2138,19 +2181,16 @@
             <v>12.5</v>
           </cell>
           <cell r="C31">
-            <v>5</v>
+            <v>3</v>
           </cell>
           <cell r="D31">
-            <v>1.3440860215053764E-2</v>
-          </cell>
-          <cell r="I31">
-            <v>5</v>
+            <v>1.0452961672473868E-2</v>
           </cell>
           <cell r="J31">
-            <v>0</v>
+            <v>3</v>
           </cell>
           <cell r="K31">
-            <v>0</v>
+            <v>4.1666666666666664E-2</v>
           </cell>
           <cell r="AA31" t="str">
             <v>xs</v>
@@ -2159,15 +2199,15 @@
             <v>12.5</v>
           </cell>
           <cell r="AC31">
-            <v>5</v>
+            <v>8</v>
           </cell>
           <cell r="AD31">
-            <v>3.1505986137366098E-3</v>
+            <v>4.2689434364994666E-3</v>
           </cell>
         </row>
         <row r="32">
           <cell r="C32">
-            <v>372</v>
+            <v>287</v>
           </cell>
           <cell r="D32">
             <v>1</v>
@@ -2182,19 +2222,19 @@
             <v>0</v>
           </cell>
           <cell r="I32">
-            <v>696</v>
+            <v>170</v>
           </cell>
           <cell r="J32">
-            <v>0</v>
+            <v>117</v>
           </cell>
           <cell r="K32">
-            <v>0</v>
+            <v>1.625</v>
           </cell>
           <cell r="AC32">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="AD32">
-            <v>0.99999999999999989</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="33">
@@ -2775,7 +2815,7 @@
         </row>
         <row r="58">
           <cell r="C58">
-            <v>372</v>
+            <v>287</v>
           </cell>
           <cell r="G58">
             <v>0</v>
@@ -2784,22 +2824,22 @@
             <v>0</v>
           </cell>
           <cell r="I58">
-            <v>696</v>
+            <v>170</v>
           </cell>
           <cell r="J58">
-            <v>0</v>
+            <v>117</v>
           </cell>
           <cell r="K58">
-            <v>0</v>
+            <v>1.625</v>
           </cell>
           <cell r="O58">
-            <v>4650</v>
+            <v>3587.5</v>
           </cell>
           <cell r="AA58" t="str">
             <v>Totales</v>
           </cell>
           <cell r="AC58">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
         </row>
         <row r="59">
@@ -2807,16 +2847,15 @@
             <v>0</v>
           </cell>
           <cell r="AC59">
-            <v>317.39999999999998</v>
+            <v>267.71428571428572</v>
           </cell>
         </row>
         <row r="60">
           <cell r="C60">
-            <v>297.60000000000002</v>
+            <v>229.6</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
@@ -2897,19 +2936,19 @@
       <sheetData sheetId="81"/>
       <sheetData sheetId="82"/>
       <sheetData sheetId="83"/>
-      <sheetData sheetId="84"/>
-      <sheetData sheetId="85">
+      <sheetData sheetId="84">
         <row r="130">
           <cell r="F130">
-            <v>372</v>
+            <v>659</v>
           </cell>
         </row>
         <row r="132">
           <cell r="F132">
-            <v>0.91129032258064513</v>
+            <v>0.89226100151745069</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="85"/>
       <sheetData sheetId="86">
         <row r="6">
           <cell r="B6">
@@ -2985,10 +3024,10 @@
         </row>
         <row r="15">
           <cell r="B15">
-            <v>0</v>
+            <v>46155</v>
           </cell>
           <cell r="H15">
-            <v>0</v>
+            <v>287</v>
           </cell>
         </row>
         <row r="16">
@@ -3597,8 +3636,8 @@
           </cell>
         </row>
         <row r="123">
-          <cell r="B123" t="e">
-            <v>#VALUE!</v>
+          <cell r="B123">
+            <v>28.229508196721312</v>
           </cell>
         </row>
         <row r="124">
@@ -3876,25 +3915,25 @@
         </row>
         <row r="20">
           <cell r="B20">
-            <v>0</v>
+            <v>46155</v>
           </cell>
           <cell r="C20" t="str">
             <v>H2E México SA de CV</v>
           </cell>
-          <cell r="D20" t="str">
-            <v/>
-          </cell>
-          <cell r="E20" t="str">
-            <v/>
+          <cell r="D20">
+            <v>10.166666666666666</v>
+          </cell>
+          <cell r="E20">
+            <v>0</v>
           </cell>
           <cell r="G20">
-            <v>0</v>
+            <v>287</v>
           </cell>
           <cell r="H20">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I20">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="21">
@@ -3914,10 +3953,10 @@
             <v>0</v>
           </cell>
           <cell r="H21">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I21">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="22">
@@ -3937,10 +3976,10 @@
             <v>0</v>
           </cell>
           <cell r="H22">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I22">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="23">
@@ -3960,10 +3999,10 @@
             <v>0</v>
           </cell>
           <cell r="H23">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I23">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="24">
@@ -3983,10 +4022,10 @@
             <v>0</v>
           </cell>
           <cell r="H24">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I24">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="25">
@@ -4006,10 +4045,10 @@
             <v>0</v>
           </cell>
           <cell r="H25">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I25">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="26">
@@ -4029,10 +4068,10 @@
             <v>0</v>
           </cell>
           <cell r="H26">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I26">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="27">
@@ -4052,10 +4091,10 @@
             <v>0</v>
           </cell>
           <cell r="H27">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I27">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="28">
@@ -4075,10 +4114,10 @@
             <v>0</v>
           </cell>
           <cell r="H28">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I28">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="29">
@@ -4098,10 +4137,10 @@
             <v>0</v>
           </cell>
           <cell r="H29">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I29">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="30">
@@ -4121,10 +4160,10 @@
             <v>0</v>
           </cell>
           <cell r="H30">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I30">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="31">
@@ -4144,10 +4183,10 @@
             <v>0</v>
           </cell>
           <cell r="H31">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I31">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="32">
@@ -4167,10 +4206,10 @@
             <v>0</v>
           </cell>
           <cell r="H32">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I32">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="33">
@@ -4190,10 +4229,10 @@
             <v>0</v>
           </cell>
           <cell r="H33">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I33">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="34">
@@ -4213,10 +4252,10 @@
             <v>0</v>
           </cell>
           <cell r="H34">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I34">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="35">
@@ -4236,10 +4275,10 @@
             <v>0</v>
           </cell>
           <cell r="H35">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I35">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="36">
@@ -4259,10 +4298,10 @@
             <v>0</v>
           </cell>
           <cell r="H36">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I36">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="37">
@@ -4282,10 +4321,10 @@
             <v>0</v>
           </cell>
           <cell r="H37">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I37">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="38">
@@ -4305,10 +4344,10 @@
             <v>0</v>
           </cell>
           <cell r="H38">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I38">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="39">
@@ -4328,10 +4367,10 @@
             <v>0</v>
           </cell>
           <cell r="H39">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I39">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="40">
@@ -4351,10 +4390,10 @@
             <v>0</v>
           </cell>
           <cell r="H40">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I40">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="41">
@@ -4374,10 +4413,10 @@
             <v>0</v>
           </cell>
           <cell r="H41">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I41">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="42">
@@ -4397,10 +4436,10 @@
             <v>0</v>
           </cell>
           <cell r="H42">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I42">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="43">
@@ -4420,10 +4459,10 @@
             <v>0</v>
           </cell>
           <cell r="H43">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I43">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="44">
@@ -4443,10 +4482,10 @@
             <v>0</v>
           </cell>
           <cell r="H44">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I44">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="45">
@@ -4466,10 +4505,10 @@
             <v>0</v>
           </cell>
           <cell r="H45">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I45">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="46">
@@ -4489,10 +4528,10 @@
             <v>0</v>
           </cell>
           <cell r="H46">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I46">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="47">
@@ -4512,10 +4551,10 @@
             <v>0</v>
           </cell>
           <cell r="H47">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I47">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="48">
@@ -4535,10 +4574,10 @@
             <v>0</v>
           </cell>
           <cell r="H48">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I48">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="49">
@@ -4558,10 +4597,10 @@
             <v>0</v>
           </cell>
           <cell r="H49">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I49">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="50">
@@ -4581,10 +4620,10 @@
             <v>0</v>
           </cell>
           <cell r="H50">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I50">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="51">
@@ -4604,10 +4643,10 @@
             <v>0</v>
           </cell>
           <cell r="H51">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I51">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="52">
@@ -4627,10 +4666,10 @@
             <v>0</v>
           </cell>
           <cell r="H52">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I52">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="53">
@@ -4650,10 +4689,10 @@
             <v>0</v>
           </cell>
           <cell r="H53">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I53">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="54">
@@ -4673,10 +4712,10 @@
             <v>0</v>
           </cell>
           <cell r="H54">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I54">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="55">
@@ -4696,10 +4735,10 @@
             <v>0</v>
           </cell>
           <cell r="H55">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I55">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="56">
@@ -4719,10 +4758,10 @@
             <v>0</v>
           </cell>
           <cell r="H56">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I56">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="57">
@@ -4742,10 +4781,10 @@
             <v>0</v>
           </cell>
           <cell r="H57">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I57">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="58">
@@ -4765,10 +4804,10 @@
             <v>0</v>
           </cell>
           <cell r="H58">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I58">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="59">
@@ -4788,10 +4827,10 @@
             <v>0</v>
           </cell>
           <cell r="H59">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I59">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="60">
@@ -4811,10 +4850,10 @@
             <v>0</v>
           </cell>
           <cell r="H60">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I60">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="61">
@@ -4834,10 +4873,10 @@
             <v>0</v>
           </cell>
           <cell r="H61">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I61">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="62">
@@ -4857,10 +4896,10 @@
             <v>0</v>
           </cell>
           <cell r="H62">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I62">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="63">
@@ -4880,10 +4919,10 @@
             <v>0</v>
           </cell>
           <cell r="H63">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I63">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="64">
@@ -4903,10 +4942,10 @@
             <v>0</v>
           </cell>
           <cell r="H64">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I64">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="65">
@@ -4926,10 +4965,10 @@
             <v>0</v>
           </cell>
           <cell r="H65">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I65">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="66">
@@ -4949,10 +4988,10 @@
             <v>0</v>
           </cell>
           <cell r="H66">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I66">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="67">
@@ -4972,10 +5011,10 @@
             <v>0</v>
           </cell>
           <cell r="H67">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I67">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="68">
@@ -4995,10 +5034,10 @@
             <v>0</v>
           </cell>
           <cell r="H68">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I68">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="69">
@@ -5018,10 +5057,10 @@
             <v>0</v>
           </cell>
           <cell r="H69">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I69">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="70">
@@ -5041,10 +5080,10 @@
             <v>0</v>
           </cell>
           <cell r="H70">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I70">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="71">
@@ -5064,10 +5103,10 @@
             <v>0</v>
           </cell>
           <cell r="H71">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I71">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="72">
@@ -5087,10 +5126,10 @@
             <v>0</v>
           </cell>
           <cell r="H72">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I72">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="73">
@@ -5110,10 +5149,10 @@
             <v>0</v>
           </cell>
           <cell r="H73">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I73">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="74">
@@ -5133,10 +5172,10 @@
             <v>0</v>
           </cell>
           <cell r="H74">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I74">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="75">
@@ -5156,10 +5195,10 @@
             <v>0</v>
           </cell>
           <cell r="H75">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I75">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="76">
@@ -5179,10 +5218,10 @@
             <v>0</v>
           </cell>
           <cell r="H76">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I76">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="77">
@@ -5202,10 +5241,10 @@
             <v>0</v>
           </cell>
           <cell r="H77">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I77">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="78">
@@ -5225,10 +5264,10 @@
             <v>0</v>
           </cell>
           <cell r="H78">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I78">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="79">
@@ -5248,10 +5287,10 @@
             <v>0</v>
           </cell>
           <cell r="H79">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I79">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="80">
@@ -5271,10 +5310,10 @@
             <v>0</v>
           </cell>
           <cell r="H80">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I80">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="81">
@@ -5294,10 +5333,10 @@
             <v>0</v>
           </cell>
           <cell r="H81">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I81">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="82">
@@ -5317,10 +5356,10 @@
             <v>0</v>
           </cell>
           <cell r="H82">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I82">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="83">
@@ -5340,10 +5379,10 @@
             <v>0</v>
           </cell>
           <cell r="H83">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I83">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="84">
@@ -5363,10 +5402,10 @@
             <v>0</v>
           </cell>
           <cell r="H84">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I84">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="85">
@@ -5386,10 +5425,10 @@
             <v>0</v>
           </cell>
           <cell r="H85">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I85">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="86">
@@ -5409,10 +5448,10 @@
             <v>0</v>
           </cell>
           <cell r="H86">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I86">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="87">
@@ -5432,10 +5471,10 @@
             <v>0</v>
           </cell>
           <cell r="H87">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I87">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="88">
@@ -5455,10 +5494,10 @@
             <v>0</v>
           </cell>
           <cell r="H88">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I88">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="89">
@@ -5478,10 +5517,10 @@
             <v>0</v>
           </cell>
           <cell r="H89">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I89">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="90">
@@ -5501,10 +5540,10 @@
             <v>0</v>
           </cell>
           <cell r="H90">
-            <v>1587</v>
+            <v>1874</v>
           </cell>
           <cell r="I90">
-            <v>1269.5999999999999</v>
+            <v>1499.2</v>
           </cell>
         </row>
         <row r="106">
@@ -5760,74 +5799,10 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls driveId="F087611319785EAE" itemId="F087611319785EAE!s7c1e8e829e4c4ea1bb203222ae643022">
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Liq"/>
-      <sheetName val="Liq-P&amp;P"/>
-      <sheetName val="Listado"/>
-      <sheetName val="Prom x Semana"/>
-      <sheetName val="Transacciones"/>
-      <sheetName val="Ing - Egr Pend"/>
-      <sheetName val="Reporte Semanal"/>
-      <sheetName val="VENTAS"/>
-      <sheetName val="Retorno x Cliente Nac"/>
-      <sheetName val="Hoja1"/>
-      <sheetName val="Pending 2 Inv (26-1)"/>
-      <sheetName val="GWR Transactions"/>
-      <sheetName val="Listado (2)"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="E2">
-            <v>191554</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="1">
-          <cell r="T1">
-            <v>1532.432</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6">
-        <row r="74">
-          <cell r="C74">
-            <v>2.4123999999999999</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="C75">
-            <v>0.1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
+    <xxl21:alternateUrls driveId="F087611319785EAE" itemId="F087611319785EAE!s22f961c7922f414d9901c4d6434e7d9b">
       <xxl21:absoluteUrl r:id="rId2"/>
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
@@ -9468,7 +9443,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8B67981-883E-4619-B718-D1B03A8FA5A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F514E507-AF52-4A61-9262-D602E6DFFEC3}">
   <sheetPr codeName="Hoja42">
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
@@ -9508,18 +9483,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="199" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
+      <c r="A1" s="187" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="N1" s="2"/>
-      <c r="P1" s="183"/>
-      <c r="Q1" s="183"/>
-      <c r="R1" s="183"/>
+      <c r="P1" s="188"/>
+      <c r="Q1" s="188"/>
+      <c r="R1" s="188"/>
       <c r="S1" s="3"/>
       <c r="V1" s="4" t="s">
         <v>1</v>
@@ -9533,14 +9508,14 @@
       <c r="Y1" s="7"/>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="G2" s="200" t="s">
+      <c r="G2" s="189" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="189"/>
       <c r="J2" s="9">
-        <f>'[1]Empaque (9)'!K2</f>
-        <v>9</v>
+        <f>'[2]Empaque (10)'!K2</f>
+        <v>10</v>
       </c>
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
@@ -9563,15 +9538,15 @@
       <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="201" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="201"/>
-      <c r="D3" s="201"/>
+      <c r="B3" s="190" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
       <c r="L3" s="10"/>
-      <c r="M3" s="204"/>
+      <c r="M3" s="10"/>
       <c r="N3" s="16"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="17"/>
@@ -9588,21 +9563,21 @@
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A4" s="202" t="s">
+      <c r="A4" s="191" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="202"/>
-      <c r="C4" s="202"/>
+      <c r="B4" s="191"/>
+      <c r="C4" s="191"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="203">
-        <f>'[1]Empaque (9)'!H4</f>
-        <v>46153</v>
-      </c>
-      <c r="H4" s="203"/>
-      <c r="I4" s="203"/>
-      <c r="J4" s="203"/>
+      <c r="G4" s="192">
+        <f>'[2]Empaque (10)'!H4</f>
+        <v>46155</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="192"/>
       <c r="L4" s="10"/>
       <c r="M4" s="18"/>
       <c r="N4" s="16"/>
@@ -9650,30 +9625,30 @@
       <c r="AI5" s="24"/>
     </row>
     <row r="6" spans="1:36" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="186" t="s">
+      <c r="A6" s="194" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="186" t="s">
+      <c r="B6" s="194" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="188" t="s">
+      <c r="C6" s="196" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="193" t="s">
+      <c r="D6" s="198" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="25"/>
-      <c r="F6" s="195" t="s">
+      <c r="F6" s="183" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="196"/>
-      <c r="H6" s="197"/>
+      <c r="G6" s="184"/>
+      <c r="H6" s="185"/>
       <c r="I6" s="26"/>
       <c r="J6" s="27"/>
-      <c r="K6" s="198"/>
+      <c r="K6" s="186"/>
       <c r="N6" s="28"/>
-      <c r="Q6" s="183"/>
-      <c r="R6" s="183"/>
+      <c r="Q6" s="188"/>
+      <c r="R6" s="188"/>
       <c r="V6" s="4" t="s">
         <v>17</v>
       </c>
@@ -9688,10 +9663,10 @@
       <c r="AI6" s="24"/>
     </row>
     <row r="7" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="187"/>
-      <c r="B7" s="187"/>
-      <c r="C7" s="189"/>
-      <c r="D7" s="194"/>
+      <c r="A7" s="195"/>
+      <c r="B7" s="195"/>
+      <c r="C7" s="197"/>
+      <c r="D7" s="199"/>
       <c r="E7" s="29" t="s">
         <v>18</v>
       </c>
@@ -9710,7 +9685,7 @@
       <c r="J7" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="198"/>
+      <c r="K7" s="186"/>
       <c r="M7" s="35"/>
       <c r="N7" s="36"/>
       <c r="P7" s="11"/>
@@ -9732,24 +9707,24 @@
       <c r="X7" s="39">
         <v>0</v>
       </c>
-      <c r="Z7" s="184" t="s">
+      <c r="Z7" s="200" t="s">
         <v>12</v>
       </c>
-      <c r="AA7" s="186" t="s">
+      <c r="AA7" s="194" t="s">
         <v>13</v>
       </c>
-      <c r="AB7" s="188" t="s">
+      <c r="AB7" s="196" t="s">
         <v>14</v>
       </c>
-      <c r="AC7" s="190" t="s">
+      <c r="AC7" s="202" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="192" t="s">
+      <c r="A8" s="193" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="192"/>
+      <c r="B8" s="193"/>
       <c r="M8" s="8"/>
       <c r="N8" s="36"/>
       <c r="P8" s="11"/>
@@ -9771,10 +9746,10 @@
       <c r="X8" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="Z8" s="185"/>
-      <c r="AA8" s="187"/>
-      <c r="AB8" s="189"/>
-      <c r="AC8" s="191"/>
+      <c r="Z8" s="201"/>
+      <c r="AA8" s="195"/>
+      <c r="AB8" s="197"/>
+      <c r="AC8" s="203"/>
       <c r="AH8" s="40" t="s">
         <v>16</v>
       </c>
@@ -9785,11 +9760,11 @@
     </row>
     <row r="9" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="41" t="str">
-        <f>'[1]Empaque (9)'!A9</f>
+        <f>'[2]Empaque (10)'!A9</f>
         <v>Campo Gusto x 72</v>
       </c>
       <c r="B9" s="42" t="str">
-        <f>'[1]Empaque (9)'!B9</f>
+        <f>'[2]Empaque (10)'!B9</f>
         <v>lb</v>
       </c>
       <c r="K9" s="43" t="s">
@@ -9804,11 +9779,11 @@
       <c r="N9" s="20"/>
       <c r="O9" s="20"/>
       <c r="Z9" s="41" t="str">
-        <f>'[1]Empaque (9)'!AA9</f>
+        <f>'[2]Empaque (10)'!AA9</f>
         <v>Campo Gusto x 72</v>
       </c>
       <c r="AA9" s="44" t="str">
-        <f>'[1]Empaque (9)'!AB9</f>
+        <f>'[2]Empaque (10)'!AB9</f>
         <v>lb</v>
       </c>
       <c r="AE9" s="6" t="s">
@@ -9826,43 +9801,43 @@
     </row>
     <row r="10" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="46" t="str">
-        <f>'[1]Empaque (9)'!A10</f>
+        <f>'[2]Empaque (10)'!A10</f>
         <v>Jb</v>
       </c>
       <c r="B10" s="47">
-        <f>'[1]Empaque (9)'!B10</f>
+        <f>'[2]Empaque (10)'!B10</f>
         <v>25</v>
       </c>
       <c r="C10" s="48">
-        <f>'[1]Empaque (9)'!C10</f>
+        <f>'[2]Empaque (10)'!C10</f>
         <v>0</v>
       </c>
       <c r="D10" s="49" t="str">
-        <f>'[1]Empaque (9)'!D10</f>
+        <f>'[2]Empaque (10)'!D10</f>
         <v/>
       </c>
       <c r="E10" s="50">
-        <f>'[1]Empaque (9)'!F10</f>
+        <f>'[2]Empaque (10)'!F10</f>
         <v>0</v>
       </c>
       <c r="F10" s="51">
-        <f>'[1]Empaque (9)'!G10</f>
+        <f>'[2]Empaque (10)'!G10</f>
         <v>0</v>
       </c>
       <c r="G10" s="52">
-        <f>'[1]Empaque (9)'!H10</f>
+        <f>'[2]Empaque (10)'!H10</f>
         <v>0</v>
       </c>
       <c r="H10" s="48">
-        <f>'[1]Empaque (9)'!I10</f>
+        <f>'[2]Empaque (10)'!I10</f>
         <v>0</v>
       </c>
       <c r="I10" s="53">
-        <f>'[1]Empaque (9)'!J10</f>
+        <f>'[2]Empaque (10)'!J10</f>
         <v>0</v>
       </c>
       <c r="J10" s="54">
-        <f>'[1]Empaque (9)'!K10</f>
+        <f>'[2]Empaque (10)'!K10</f>
         <v>0</v>
       </c>
       <c r="K10" s="55"/>
@@ -9895,19 +9870,19 @@
         <v>0</v>
       </c>
       <c r="Z10" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA10</f>
+        <f>'[2]Empaque (10)'!AA10</f>
         <v>Jb</v>
       </c>
       <c r="AA10" s="61">
-        <f>'[1]Empaque (9)'!AB10</f>
+        <f>'[2]Empaque (10)'!AB10</f>
         <v>25</v>
       </c>
       <c r="AB10" s="62">
-        <f>'[1]Empaque (9)'!AC10</f>
+        <f>'[2]Empaque (10)'!AC10</f>
         <v>0</v>
       </c>
       <c r="AC10" s="63">
-        <f>'[1]Empaque (9)'!AD10</f>
+        <f>'[2]Empaque (10)'!AD10</f>
         <v>0</v>
       </c>
       <c r="AG10" s="64"/>
@@ -9920,43 +9895,43 @@
     </row>
     <row r="11" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="46" t="str">
-        <f>'[1]Empaque (9)'!A11</f>
+        <f>'[2]Empaque (10)'!A11</f>
         <v>Xl</v>
       </c>
       <c r="B11" s="66">
-        <f>'[1]Empaque (9)'!B11</f>
+        <f>'[2]Empaque (10)'!B11</f>
         <v>25</v>
       </c>
       <c r="C11" s="67">
-        <f>'[1]Empaque (9)'!C11</f>
+        <f>'[2]Empaque (10)'!C11</f>
         <v>0</v>
       </c>
       <c r="D11" s="49" t="str">
-        <f>'[1]Empaque (9)'!D11</f>
+        <f>'[2]Empaque (10)'!D11</f>
         <v/>
       </c>
       <c r="E11" s="50">
-        <f>'[1]Empaque (9)'!F11</f>
+        <f>'[2]Empaque (10)'!F11</f>
         <v>0</v>
       </c>
       <c r="F11" s="51">
-        <f>'[1]Empaque (9)'!G11</f>
+        <f>'[2]Empaque (10)'!G11</f>
         <v>0</v>
       </c>
       <c r="G11" s="68">
-        <f>'[1]Empaque (9)'!H11</f>
+        <f>'[2]Empaque (10)'!H11</f>
         <v>0</v>
       </c>
       <c r="H11" s="67">
-        <f>'[1]Empaque (9)'!I11</f>
+        <f>'[2]Empaque (10)'!I11</f>
         <v>0</v>
       </c>
       <c r="I11" s="53">
-        <f>'[1]Empaque (9)'!J11</f>
+        <f>'[2]Empaque (10)'!J11</f>
         <v>0</v>
       </c>
       <c r="J11" s="54">
-        <f>'[1]Empaque (9)'!K11</f>
+        <f>'[2]Empaque (10)'!K11</f>
         <v>0</v>
       </c>
       <c r="K11" s="69"/>
@@ -9974,19 +9949,19 @@
       </c>
       <c r="S11" s="10"/>
       <c r="Z11" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA11</f>
+        <f>'[2]Empaque (10)'!AA11</f>
         <v>Xl</v>
       </c>
       <c r="AA11" s="72">
-        <f>'[1]Empaque (9)'!AB11</f>
+        <f>'[2]Empaque (10)'!AB11</f>
         <v>25</v>
       </c>
       <c r="AB11" s="62">
-        <f>'[1]Empaque (9)'!AC11</f>
+        <f>'[2]Empaque (10)'!AC11</f>
         <v>0</v>
       </c>
       <c r="AC11" s="63">
-        <f>'[1]Empaque (9)'!AD11</f>
+        <f>'[2]Empaque (10)'!AD11</f>
         <v>0</v>
       </c>
       <c r="AG11" s="73"/>
@@ -9999,43 +9974,43 @@
     </row>
     <row r="12" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="46" t="str">
-        <f>'[1]Empaque (9)'!A12</f>
+        <f>'[2]Empaque (10)'!A12</f>
         <v>Lg</v>
       </c>
       <c r="B12" s="47">
-        <f>'[1]Empaque (9)'!B12</f>
+        <f>'[2]Empaque (10)'!B12</f>
         <v>25</v>
       </c>
       <c r="C12" s="67">
-        <f>'[1]Empaque (9)'!C12</f>
+        <f>'[2]Empaque (10)'!C12</f>
         <v>0</v>
       </c>
       <c r="D12" s="49" t="str">
-        <f>'[1]Empaque (9)'!D12</f>
+        <f>'[2]Empaque (10)'!D12</f>
         <v/>
       </c>
       <c r="E12" s="50">
-        <f>'[1]Empaque (9)'!F12</f>
+        <f>'[2]Empaque (10)'!F12</f>
         <v>0</v>
       </c>
       <c r="F12" s="51">
-        <f>'[1]Empaque (9)'!G12</f>
+        <f>'[2]Empaque (10)'!G12</f>
         <v>0</v>
       </c>
       <c r="G12" s="68">
-        <f>'[1]Empaque (9)'!H12</f>
+        <f>'[2]Empaque (10)'!H12</f>
         <v>0</v>
       </c>
       <c r="H12" s="67">
-        <f>'[1]Empaque (9)'!I12</f>
+        <f>'[2]Empaque (10)'!I12</f>
         <v>0</v>
       </c>
       <c r="I12" s="53">
-        <f>'[1]Empaque (9)'!J12</f>
+        <f>'[2]Empaque (10)'!J12</f>
         <v>0</v>
       </c>
       <c r="J12" s="54">
-        <f>'[1]Empaque (9)'!K12</f>
+        <f>'[2]Empaque (10)'!K12</f>
         <v>0</v>
       </c>
       <c r="K12" s="69"/>
@@ -10053,19 +10028,19 @@
       </c>
       <c r="S12" s="10"/>
       <c r="Z12" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA12</f>
+        <f>'[2]Empaque (10)'!AA12</f>
         <v>Lg</v>
       </c>
       <c r="AA12" s="61">
-        <f>'[1]Empaque (9)'!AB12</f>
+        <f>'[2]Empaque (10)'!AB12</f>
         <v>25</v>
       </c>
       <c r="AB12" s="62">
-        <f>'[1]Empaque (9)'!AC12</f>
+        <f>'[2]Empaque (10)'!AC12</f>
         <v>0</v>
       </c>
       <c r="AC12" s="63">
-        <f>'[1]Empaque (9)'!AD12</f>
+        <f>'[2]Empaque (10)'!AD12</f>
         <v>0</v>
       </c>
       <c r="AG12" s="73"/>
@@ -10078,43 +10053,43 @@
     </row>
     <row r="13" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="46" t="str">
-        <f>'[1]Empaque (9)'!A13</f>
+        <f>'[2]Empaque (10)'!A13</f>
         <v>Md</v>
       </c>
       <c r="B13" s="66">
-        <f>'[1]Empaque (9)'!B13</f>
+        <f>'[2]Empaque (10)'!B13</f>
         <v>25</v>
       </c>
       <c r="C13" s="67">
-        <f>'[1]Empaque (9)'!C13</f>
+        <f>'[2]Empaque (10)'!C13</f>
         <v>0</v>
       </c>
       <c r="D13" s="49" t="str">
-        <f>'[1]Empaque (9)'!D13</f>
+        <f>'[2]Empaque (10)'!D13</f>
         <v/>
       </c>
       <c r="E13" s="50">
-        <f>'[1]Empaque (9)'!F13</f>
+        <f>'[2]Empaque (10)'!F13</f>
         <v>0</v>
       </c>
       <c r="F13" s="51">
-        <f>'[1]Empaque (9)'!G13</f>
+        <f>'[2]Empaque (10)'!G13</f>
         <v>0</v>
       </c>
       <c r="G13" s="68">
-        <f>'[1]Empaque (9)'!H13</f>
+        <f>'[2]Empaque (10)'!H13</f>
         <v>0</v>
       </c>
       <c r="H13" s="67">
-        <f>'[1]Empaque (9)'!I13</f>
+        <f>'[2]Empaque (10)'!I13</f>
         <v>0</v>
       </c>
       <c r="I13" s="53">
-        <f>'[1]Empaque (9)'!J13</f>
+        <f>'[2]Empaque (10)'!J13</f>
         <v>0</v>
       </c>
       <c r="J13" s="54">
-        <f>'[1]Empaque (9)'!K13</f>
+        <f>'[2]Empaque (10)'!K13</f>
         <v>0</v>
       </c>
       <c r="K13" s="69"/>
@@ -10132,19 +10107,19 @@
       </c>
       <c r="S13" s="10"/>
       <c r="Z13" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA13</f>
+        <f>'[2]Empaque (10)'!AA13</f>
         <v>Md</v>
       </c>
       <c r="AA13" s="72">
-        <f>'[1]Empaque (9)'!AB13</f>
+        <f>'[2]Empaque (10)'!AB13</f>
         <v>25</v>
       </c>
       <c r="AB13" s="62">
-        <f>'[1]Empaque (9)'!AC13</f>
+        <f>'[2]Empaque (10)'!AC13</f>
         <v>0</v>
       </c>
       <c r="AC13" s="63">
-        <f>'[1]Empaque (9)'!AD13</f>
+        <f>'[2]Empaque (10)'!AD13</f>
         <v>0</v>
       </c>
       <c r="AG13" s="73"/>
@@ -10157,43 +10132,43 @@
     </row>
     <row r="14" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="46" t="str">
-        <f>'[1]Empaque (9)'!A14</f>
+        <f>'[2]Empaque (10)'!A14</f>
         <v>Sm</v>
       </c>
       <c r="B14" s="47">
-        <f>'[1]Empaque (9)'!B14</f>
+        <f>'[2]Empaque (10)'!B14</f>
         <v>25</v>
       </c>
       <c r="C14" s="67">
-        <f>'[1]Empaque (9)'!C14</f>
+        <f>'[2]Empaque (10)'!C14</f>
         <v>0</v>
       </c>
       <c r="D14" s="49" t="str">
-        <f>'[1]Empaque (9)'!D14</f>
+        <f>'[2]Empaque (10)'!D14</f>
         <v/>
       </c>
       <c r="E14" s="50">
-        <f>'[1]Empaque (9)'!F14</f>
+        <f>'[2]Empaque (10)'!F14</f>
         <v>0</v>
       </c>
       <c r="F14" s="51">
-        <f>'[1]Empaque (9)'!G14</f>
+        <f>'[2]Empaque (10)'!G14</f>
         <v>0</v>
       </c>
       <c r="G14" s="68">
-        <f>'[1]Empaque (9)'!H14</f>
+        <f>'[2]Empaque (10)'!H14</f>
         <v>0</v>
       </c>
       <c r="H14" s="67">
-        <f>'[1]Empaque (9)'!I14</f>
+        <f>'[2]Empaque (10)'!I14</f>
         <v>0</v>
       </c>
       <c r="I14" s="53">
-        <f>'[1]Empaque (9)'!J14</f>
+        <f>'[2]Empaque (10)'!J14</f>
         <v>0</v>
       </c>
       <c r="J14" s="54">
-        <f>'[1]Empaque (9)'!K14</f>
+        <f>'[2]Empaque (10)'!K14</f>
         <v>0</v>
       </c>
       <c r="K14" s="69"/>
@@ -10211,19 +10186,19 @@
       </c>
       <c r="S14" s="10"/>
       <c r="Z14" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA14</f>
+        <f>'[2]Empaque (10)'!AA14</f>
         <v>Sm</v>
       </c>
       <c r="AA14" s="61">
-        <f>'[1]Empaque (9)'!AB14</f>
+        <f>'[2]Empaque (10)'!AB14</f>
         <v>25</v>
       </c>
       <c r="AB14" s="77">
-        <f>'[1]Empaque (9)'!AC14</f>
+        <f>'[2]Empaque (10)'!AC14</f>
         <v>0</v>
       </c>
       <c r="AC14" s="63">
-        <f>'[1]Empaque (9)'!AD14</f>
+        <f>'[2]Empaque (10)'!AD14</f>
         <v>0</v>
       </c>
       <c r="AG14" s="64"/>
@@ -10236,43 +10211,43 @@
     </row>
     <row r="15" spans="1:36" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="79" t="str">
-        <f>'[1]Empaque (9)'!A15</f>
+        <f>'[2]Empaque (10)'!A15</f>
         <v>Mixto</v>
       </c>
       <c r="B15" s="80">
-        <f>'[1]Empaque (9)'!B15</f>
+        <f>'[2]Empaque (10)'!B15</f>
         <v>25</v>
       </c>
       <c r="C15" s="81">
-        <f>'[1]Empaque (9)'!C15</f>
+        <f>'[2]Empaque (10)'!C15</f>
         <v>0</v>
       </c>
       <c r="D15" s="82" t="str">
-        <f>'[1]Empaque (9)'!D15</f>
+        <f>'[2]Empaque (10)'!D15</f>
         <v/>
       </c>
       <c r="E15" s="83">
-        <f>'[1]Empaque (9)'!F15</f>
+        <f>'[2]Empaque (10)'!F15</f>
         <v>0</v>
       </c>
       <c r="F15" s="84">
-        <f>'[1]Empaque (9)'!G15</f>
+        <f>'[2]Empaque (10)'!G15</f>
         <v>0</v>
       </c>
       <c r="G15" s="85">
-        <f>'[1]Empaque (9)'!H15</f>
+        <f>'[2]Empaque (10)'!H15</f>
         <v>0</v>
       </c>
       <c r="H15" s="81">
-        <f>'[1]Empaque (9)'!I15</f>
+        <f>'[2]Empaque (10)'!I15</f>
         <v>0</v>
       </c>
       <c r="I15" s="86">
-        <f>'[1]Empaque (9)'!J15</f>
+        <f>'[2]Empaque (10)'!J15</f>
         <v>0</v>
       </c>
       <c r="J15" s="87">
-        <f>'[1]Empaque (9)'!K15</f>
+        <f>'[2]Empaque (10)'!K15</f>
         <v>0</v>
       </c>
       <c r="K15" s="88"/>
@@ -10290,19 +10265,19 @@
       </c>
       <c r="S15" s="10"/>
       <c r="Z15" s="90" t="str">
-        <f>'[1]Empaque (9)'!AA15</f>
+        <f>'[2]Empaque (10)'!AA15</f>
         <v>xs</v>
       </c>
       <c r="AA15" s="91">
-        <f>'[1]Empaque (9)'!AB15</f>
+        <f>'[2]Empaque (10)'!AB15</f>
         <v>25</v>
       </c>
       <c r="AB15" s="92">
-        <f>'[1]Empaque (9)'!AC15</f>
+        <f>'[2]Empaque (10)'!AC15</f>
         <v>0</v>
       </c>
       <c r="AC15" s="93">
-        <f>'[1]Empaque (9)'!AD15</f>
+        <f>'[2]Empaque (10)'!AD15</f>
         <v>0</v>
       </c>
       <c r="AG15" s="94"/>
@@ -10315,35 +10290,35 @@
     </row>
     <row r="16" spans="1:36" ht="15" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C16" s="96">
-        <f>'[1]Empaque (9)'!C16</f>
+        <f>'[2]Empaque (10)'!C16</f>
         <v>0</v>
       </c>
       <c r="D16" s="97" t="str">
-        <f>'[1]Empaque (9)'!D16</f>
+        <f>'[2]Empaque (10)'!D16</f>
         <v/>
       </c>
       <c r="E16" s="98">
-        <f>'[1]Empaque (9)'!F16</f>
+        <f>'[2]Empaque (10)'!F16</f>
         <v>0</v>
       </c>
       <c r="F16" s="99">
-        <f>'[1]Empaque (9)'!G16</f>
+        <f>'[2]Empaque (10)'!G16</f>
         <v>0</v>
       </c>
       <c r="G16" s="100">
-        <f>'[1]Empaque (9)'!H16</f>
+        <f>'[2]Empaque (10)'!H16</f>
         <v>0</v>
       </c>
       <c r="H16" s="100">
-        <f>'[1]Empaque (9)'!I16</f>
+        <f>'[2]Empaque (10)'!I16</f>
         <v>0</v>
       </c>
       <c r="I16" s="100">
-        <f>'[1]Empaque (9)'!J16</f>
+        <f>'[2]Empaque (10)'!J16</f>
         <v>0</v>
       </c>
       <c r="J16" s="101">
-        <f>'[1]Empaque (9)'!K16</f>
+        <f>'[2]Empaque (10)'!K16</f>
         <v>0</v>
       </c>
       <c r="K16" s="102">
@@ -10362,11 +10337,11 @@
       <c r="S16" s="10"/>
       <c r="AA16" s="104"/>
       <c r="AB16" s="105">
-        <f>'[1]Empaque (9)'!AC16</f>
+        <f>'[2]Empaque (10)'!AC16</f>
         <v>0</v>
       </c>
       <c r="AC16" s="106">
-        <f>'[1]Empaque (9)'!AD16</f>
+        <f>'[2]Empaque (10)'!AD16</f>
         <v>0</v>
       </c>
       <c r="AH16" s="107">
@@ -10381,11 +10356,11 @@
     </row>
     <row r="17" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="41" t="str">
-        <f>'[1]Empaque (9)'!A17</f>
+        <f>'[2]Empaque (10)'!A17</f>
         <v>H2E (2da) x 72</v>
       </c>
       <c r="B17" s="42" t="str">
-        <f>'[1]Empaque (9)'!B17</f>
+        <f>'[2]Empaque (10)'!B17</f>
         <v>lb</v>
       </c>
       <c r="C17" s="109"/>
@@ -10407,11 +10382,11 @@
       <c r="P17" s="58"/>
       <c r="S17" s="10"/>
       <c r="Z17" s="41" t="str">
-        <f>'[1]Empaque (9)'!AA17</f>
+        <f>'[2]Empaque (10)'!AA17</f>
         <v>H2E (2da) x 72</v>
       </c>
       <c r="AA17" s="44" t="str">
-        <f>'[1]Empaque (9)'!AB17</f>
+        <f>'[2]Empaque (10)'!AB17</f>
         <v>lb</v>
       </c>
       <c r="AE17" s="6" t="s">
@@ -10425,43 +10400,43 @@
     </row>
     <row r="18" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="46" t="str">
-        <f>'[1]Empaque (9)'!A18</f>
+        <f>'[2]Empaque (10)'!A18</f>
         <v>Jb</v>
       </c>
       <c r="B18" s="47">
-        <f>'[1]Empaque (9)'!B18</f>
+        <f>'[2]Empaque (10)'!B18</f>
         <v>25</v>
       </c>
       <c r="C18" s="48">
-        <f>'[1]Empaque (9)'!C18</f>
+        <f>'[2]Empaque (10)'!C18</f>
         <v>0</v>
       </c>
       <c r="D18" s="49" t="str">
-        <f>'[1]Empaque (9)'!D18</f>
+        <f>'[2]Empaque (10)'!D18</f>
         <v/>
       </c>
       <c r="E18" s="50">
-        <f>'[1]Empaque (9)'!F18</f>
+        <f>'[2]Empaque (10)'!F18</f>
         <v>0</v>
       </c>
       <c r="F18" s="51">
-        <f>'[1]Empaque (9)'!G18</f>
+        <f>'[2]Empaque (10)'!G18</f>
         <v>0</v>
       </c>
       <c r="G18" s="52">
-        <f>'[1]Empaque (9)'!H18</f>
+        <f>'[2]Empaque (10)'!H18</f>
         <v>0</v>
       </c>
       <c r="H18" s="48">
-        <f>'[1]Empaque (9)'!I18</f>
+        <f>'[2]Empaque (10)'!I18</f>
         <v>0</v>
       </c>
       <c r="I18" s="53">
-        <f>'[1]Empaque (9)'!J18</f>
+        <f>'[2]Empaque (10)'!J18</f>
         <v>0</v>
       </c>
       <c r="J18" s="54">
-        <f>'[1]Empaque (9)'!K18</f>
+        <f>'[2]Empaque (10)'!K18</f>
         <v>0</v>
       </c>
       <c r="K18" s="55"/>
@@ -10494,19 +10469,19 @@
         <v>0</v>
       </c>
       <c r="Z18" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA18</f>
+        <f>'[2]Empaque (10)'!AA18</f>
         <v>Jb</v>
       </c>
       <c r="AA18" s="61">
-        <f>'[1]Empaque (9)'!AB18</f>
+        <f>'[2]Empaque (10)'!AB18</f>
         <v>25</v>
       </c>
       <c r="AB18" s="62">
-        <f>'[1]Empaque (9)'!AC18</f>
+        <f>'[2]Empaque (10)'!AC18</f>
         <v>0</v>
       </c>
       <c r="AC18" s="63">
-        <f>'[1]Empaque (9)'!AD18</f>
+        <f>'[2]Empaque (10)'!AD18</f>
         <v>0</v>
       </c>
       <c r="AG18" s="64"/>
@@ -10519,43 +10494,43 @@
     </row>
     <row r="19" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="46" t="str">
-        <f>'[1]Empaque (9)'!A19</f>
+        <f>'[2]Empaque (10)'!A19</f>
         <v>Xl</v>
       </c>
       <c r="B19" s="66">
-        <f>'[1]Empaque (9)'!B19</f>
+        <f>'[2]Empaque (10)'!B19</f>
         <v>25</v>
       </c>
       <c r="C19" s="67">
-        <f>'[1]Empaque (9)'!C19</f>
+        <f>'[2]Empaque (10)'!C19</f>
         <v>0</v>
       </c>
       <c r="D19" s="49" t="str">
-        <f>'[1]Empaque (9)'!D19</f>
+        <f>'[2]Empaque (10)'!D19</f>
         <v/>
       </c>
       <c r="E19" s="50">
-        <f>'[1]Empaque (9)'!F19</f>
+        <f>'[2]Empaque (10)'!F19</f>
         <v>0</v>
       </c>
       <c r="F19" s="51">
-        <f>'[1]Empaque (9)'!G19</f>
+        <f>'[2]Empaque (10)'!G19</f>
         <v>0</v>
       </c>
       <c r="G19" s="68">
-        <f>'[1]Empaque (9)'!H19</f>
+        <f>'[2]Empaque (10)'!H19</f>
         <v>0</v>
       </c>
       <c r="H19" s="67">
-        <f>'[1]Empaque (9)'!I19</f>
+        <f>'[2]Empaque (10)'!I19</f>
         <v>0</v>
       </c>
       <c r="I19" s="53">
-        <f>'[1]Empaque (9)'!J19</f>
+        <f>'[2]Empaque (10)'!J19</f>
         <v>0</v>
       </c>
       <c r="J19" s="54">
-        <f>'[1]Empaque (9)'!K19</f>
+        <f>'[2]Empaque (10)'!K19</f>
         <v>0</v>
       </c>
       <c r="K19" s="69"/>
@@ -10573,19 +10548,19 @@
       </c>
       <c r="S19" s="10"/>
       <c r="Z19" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA19</f>
+        <f>'[2]Empaque (10)'!AA19</f>
         <v>Xl</v>
       </c>
       <c r="AA19" s="72">
-        <f>'[1]Empaque (9)'!AB19</f>
+        <f>'[2]Empaque (10)'!AB19</f>
         <v>25</v>
       </c>
       <c r="AB19" s="62">
-        <f>'[1]Empaque (9)'!AC19</f>
+        <f>'[2]Empaque (10)'!AC19</f>
         <v>0</v>
       </c>
       <c r="AC19" s="63">
-        <f>'[1]Empaque (9)'!AD19</f>
+        <f>'[2]Empaque (10)'!AD19</f>
         <v>0</v>
       </c>
       <c r="AG19" s="73"/>
@@ -10598,43 +10573,43 @@
     </row>
     <row r="20" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="46" t="str">
-        <f>'[1]Empaque (9)'!A20</f>
+        <f>'[2]Empaque (10)'!A20</f>
         <v>Lg</v>
       </c>
       <c r="B20" s="47">
-        <f>'[1]Empaque (9)'!B20</f>
+        <f>'[2]Empaque (10)'!B20</f>
         <v>25</v>
       </c>
       <c r="C20" s="67">
-        <f>'[1]Empaque (9)'!C20</f>
+        <f>'[2]Empaque (10)'!C20</f>
         <v>0</v>
       </c>
       <c r="D20" s="49" t="str">
-        <f>'[1]Empaque (9)'!D20</f>
+        <f>'[2]Empaque (10)'!D20</f>
         <v/>
       </c>
       <c r="E20" s="50">
-        <f>'[1]Empaque (9)'!F20</f>
+        <f>'[2]Empaque (10)'!F20</f>
         <v>0</v>
       </c>
       <c r="F20" s="51">
-        <f>'[1]Empaque (9)'!G20</f>
+        <f>'[2]Empaque (10)'!G20</f>
         <v>0</v>
       </c>
       <c r="G20" s="68">
-        <f>'[1]Empaque (9)'!H20</f>
+        <f>'[2]Empaque (10)'!H20</f>
         <v>0</v>
       </c>
       <c r="H20" s="67">
-        <f>'[1]Empaque (9)'!I20</f>
+        <f>'[2]Empaque (10)'!I20</f>
         <v>0</v>
       </c>
       <c r="I20" s="53">
-        <f>'[1]Empaque (9)'!J20</f>
+        <f>'[2]Empaque (10)'!J20</f>
         <v>0</v>
       </c>
       <c r="J20" s="54">
-        <f>'[1]Empaque (9)'!K20</f>
+        <f>'[2]Empaque (10)'!K20</f>
         <v>0</v>
       </c>
       <c r="K20" s="69"/>
@@ -10652,19 +10627,19 @@
       </c>
       <c r="S20" s="10"/>
       <c r="Z20" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA20</f>
+        <f>'[2]Empaque (10)'!AA20</f>
         <v>Lg</v>
       </c>
       <c r="AA20" s="61">
-        <f>'[1]Empaque (9)'!AB20</f>
+        <f>'[2]Empaque (10)'!AB20</f>
         <v>25</v>
       </c>
       <c r="AB20" s="62">
-        <f>'[1]Empaque (9)'!AC20</f>
+        <f>'[2]Empaque (10)'!AC20</f>
         <v>0</v>
       </c>
       <c r="AC20" s="63">
-        <f>'[1]Empaque (9)'!AD20</f>
+        <f>'[2]Empaque (10)'!AD20</f>
         <v>0</v>
       </c>
       <c r="AG20" s="73"/>
@@ -10677,43 +10652,43 @@
     </row>
     <row r="21" spans="1:36" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="46" t="str">
-        <f>'[1]Empaque (9)'!A21</f>
+        <f>'[2]Empaque (10)'!A21</f>
         <v>Md</v>
       </c>
       <c r="B21" s="66">
-        <f>'[1]Empaque (9)'!B21</f>
+        <f>'[2]Empaque (10)'!B21</f>
         <v>25</v>
       </c>
       <c r="C21" s="67">
-        <f>'[1]Empaque (9)'!C21</f>
+        <f>'[2]Empaque (10)'!C21</f>
         <v>0</v>
       </c>
       <c r="D21" s="49" t="str">
-        <f>'[1]Empaque (9)'!D21</f>
+        <f>'[2]Empaque (10)'!D21</f>
         <v/>
       </c>
       <c r="E21" s="50">
-        <f>'[1]Empaque (9)'!F21</f>
+        <f>'[2]Empaque (10)'!F21</f>
         <v>0</v>
       </c>
       <c r="F21" s="51">
-        <f>'[1]Empaque (9)'!G21</f>
+        <f>'[2]Empaque (10)'!G21</f>
         <v>0</v>
       </c>
       <c r="G21" s="68">
-        <f>'[1]Empaque (9)'!H21</f>
+        <f>'[2]Empaque (10)'!H21</f>
         <v>0</v>
       </c>
       <c r="H21" s="67">
-        <f>'[1]Empaque (9)'!I21</f>
+        <f>'[2]Empaque (10)'!I21</f>
         <v>0</v>
       </c>
       <c r="I21" s="53">
-        <f>'[1]Empaque (9)'!J21</f>
+        <f>'[2]Empaque (10)'!J21</f>
         <v>0</v>
       </c>
       <c r="J21" s="54">
-        <f>'[1]Empaque (9)'!K21</f>
+        <f>'[2]Empaque (10)'!K21</f>
         <v>0</v>
       </c>
       <c r="K21" s="69"/>
@@ -10731,19 +10706,19 @@
       </c>
       <c r="S21" s="10"/>
       <c r="Z21" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA21</f>
+        <f>'[2]Empaque (10)'!AA21</f>
         <v>Md</v>
       </c>
       <c r="AA21" s="72">
-        <f>'[1]Empaque (9)'!AB21</f>
+        <f>'[2]Empaque (10)'!AB21</f>
         <v>25</v>
       </c>
       <c r="AB21" s="62">
-        <f>'[1]Empaque (9)'!AC21</f>
+        <f>'[2]Empaque (10)'!AC21</f>
         <v>0</v>
       </c>
       <c r="AC21" s="63">
-        <f>'[1]Empaque (9)'!AD21</f>
+        <f>'[2]Empaque (10)'!AD21</f>
         <v>0</v>
       </c>
       <c r="AG21" s="73"/>
@@ -10756,43 +10731,43 @@
     </row>
     <row r="22" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="46" t="str">
-        <f>'[1]Empaque (9)'!A22</f>
+        <f>'[2]Empaque (10)'!A22</f>
         <v>Sm</v>
       </c>
       <c r="B22" s="47">
-        <f>'[1]Empaque (9)'!B22</f>
+        <f>'[2]Empaque (10)'!B22</f>
         <v>25</v>
       </c>
       <c r="C22" s="67">
-        <f>'[1]Empaque (9)'!C22</f>
+        <f>'[2]Empaque (10)'!C22</f>
         <v>0</v>
       </c>
       <c r="D22" s="49" t="str">
-        <f>'[1]Empaque (9)'!D22</f>
+        <f>'[2]Empaque (10)'!D22</f>
         <v/>
       </c>
       <c r="E22" s="50">
-        <f>'[1]Empaque (9)'!F22</f>
+        <f>'[2]Empaque (10)'!F22</f>
         <v>0</v>
       </c>
       <c r="F22" s="51">
-        <f>'[1]Empaque (9)'!G22</f>
+        <f>'[2]Empaque (10)'!G22</f>
         <v>0</v>
       </c>
       <c r="G22" s="68">
-        <f>'[1]Empaque (9)'!H22</f>
+        <f>'[2]Empaque (10)'!H22</f>
         <v>0</v>
       </c>
       <c r="H22" s="67">
-        <f>'[1]Empaque (9)'!I22</f>
+        <f>'[2]Empaque (10)'!I22</f>
         <v>0</v>
       </c>
       <c r="I22" s="53">
-        <f>'[1]Empaque (9)'!J22</f>
+        <f>'[2]Empaque (10)'!J22</f>
         <v>0</v>
       </c>
       <c r="J22" s="54">
-        <f>'[1]Empaque (9)'!K22</f>
+        <f>'[2]Empaque (10)'!K22</f>
         <v>0</v>
       </c>
       <c r="K22" s="69"/>
@@ -10810,19 +10785,19 @@
       </c>
       <c r="S22" s="10"/>
       <c r="Z22" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA22</f>
+        <f>'[2]Empaque (10)'!AA22</f>
         <v>Sm</v>
       </c>
       <c r="AA22" s="61">
-        <f>'[1]Empaque (9)'!AB22</f>
+        <f>'[2]Empaque (10)'!AB22</f>
         <v>25</v>
       </c>
       <c r="AB22" s="77">
-        <f>'[1]Empaque (9)'!AC22</f>
+        <f>'[2]Empaque (10)'!AC22</f>
         <v>0</v>
       </c>
       <c r="AC22" s="63">
-        <f>'[1]Empaque (9)'!AD22</f>
+        <f>'[2]Empaque (10)'!AD22</f>
         <v>0</v>
       </c>
       <c r="AG22" s="64"/>
@@ -10835,43 +10810,43 @@
     </row>
     <row r="23" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="79" t="str">
-        <f>'[1]Empaque (9)'!A23</f>
+        <f>'[2]Empaque (10)'!A23</f>
         <v>Mixto</v>
       </c>
       <c r="B23" s="80">
-        <f>'[1]Empaque (9)'!B23</f>
+        <f>'[2]Empaque (10)'!B23</f>
         <v>25</v>
       </c>
       <c r="C23" s="81">
-        <f>'[1]Empaque (9)'!C23</f>
+        <f>'[2]Empaque (10)'!C23</f>
         <v>0</v>
       </c>
       <c r="D23" s="82" t="str">
-        <f>'[1]Empaque (9)'!D23</f>
+        <f>'[2]Empaque (10)'!D23</f>
         <v/>
       </c>
       <c r="E23" s="83">
-        <f>'[1]Empaque (9)'!F23</f>
+        <f>'[2]Empaque (10)'!F23</f>
         <v>0</v>
       </c>
       <c r="F23" s="84">
-        <f>'[1]Empaque (9)'!G23</f>
+        <f>'[2]Empaque (10)'!G23</f>
         <v>0</v>
       </c>
       <c r="G23" s="85">
-        <f>'[1]Empaque (9)'!H23</f>
+        <f>'[2]Empaque (10)'!H23</f>
         <v>0</v>
       </c>
       <c r="H23" s="81">
-        <f>'[1]Empaque (9)'!I23</f>
+        <f>'[2]Empaque (10)'!I23</f>
         <v>0</v>
       </c>
       <c r="I23" s="86">
-        <f>'[1]Empaque (9)'!J23</f>
+        <f>'[2]Empaque (10)'!J23</f>
         <v>0</v>
       </c>
       <c r="J23" s="87">
-        <f>'[1]Empaque (9)'!K23</f>
+        <f>'[2]Empaque (10)'!K23</f>
         <v>0</v>
       </c>
       <c r="K23" s="88"/>
@@ -10890,19 +10865,19 @@
       </c>
       <c r="S23" s="10"/>
       <c r="Z23" s="90" t="str">
-        <f>'[1]Empaque (9)'!AA23</f>
+        <f>'[2]Empaque (10)'!AA23</f>
         <v>xs</v>
       </c>
       <c r="AA23" s="91">
-        <f>'[1]Empaque (9)'!AB23</f>
+        <f>'[2]Empaque (10)'!AB23</f>
         <v>25</v>
       </c>
       <c r="AB23" s="92">
-        <f>'[1]Empaque (9)'!AC23</f>
+        <f>'[2]Empaque (10)'!AC23</f>
         <v>0</v>
       </c>
       <c r="AC23" s="93">
-        <f>'[1]Empaque (9)'!AD23</f>
+        <f>'[2]Empaque (10)'!AD23</f>
         <v>0</v>
       </c>
       <c r="AG23" s="94"/>
@@ -10915,35 +10890,35 @@
     </row>
     <row r="24" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C24" s="96">
-        <f>'[1]Empaque (9)'!C24</f>
+        <f>'[2]Empaque (10)'!C24</f>
         <v>0</v>
       </c>
       <c r="D24" s="97" t="str">
-        <f>'[1]Empaque (9)'!D24</f>
+        <f>'[2]Empaque (10)'!D24</f>
         <v/>
       </c>
       <c r="E24" s="98">
-        <f>'[1]Empaque (9)'!F24</f>
+        <f>'[2]Empaque (10)'!F24</f>
         <v>0</v>
       </c>
       <c r="F24" s="99">
-        <f>'[1]Empaque (9)'!G24</f>
+        <f>'[2]Empaque (10)'!G24</f>
         <v>0</v>
       </c>
       <c r="G24" s="100">
-        <f>'[1]Empaque (9)'!H24</f>
+        <f>'[2]Empaque (10)'!H24</f>
         <v>0</v>
       </c>
       <c r="H24" s="100">
-        <f>'[1]Empaque (9)'!I24</f>
+        <f>'[2]Empaque (10)'!I24</f>
         <v>0</v>
       </c>
       <c r="I24" s="100">
-        <f>'[1]Empaque (9)'!J24</f>
+        <f>'[2]Empaque (10)'!J24</f>
         <v>0</v>
       </c>
       <c r="J24" s="101">
-        <f>'[1]Empaque (9)'!K24</f>
+        <f>'[2]Empaque (10)'!K24</f>
         <v>0</v>
       </c>
       <c r="K24" s="102">
@@ -10964,11 +10939,11 @@
       <c r="S24" s="10"/>
       <c r="AA24" s="104"/>
       <c r="AB24" s="105">
-        <f>'[1]Empaque (9)'!AC24</f>
+        <f>'[2]Empaque (10)'!AC24</f>
         <v>0</v>
       </c>
       <c r="AC24" s="106">
-        <f>'[1]Empaque (9)'!AD24</f>
+        <f>'[2]Empaque (10)'!AD24</f>
         <v>0</v>
       </c>
       <c r="AH24" s="107">
@@ -10983,11 +10958,11 @@
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A25" s="41" t="str">
-        <f>'[1]Empaque (9)'!A25</f>
+        <f>'[2]Empaque (10)'!A25</f>
         <v>H2E (Orig.) x 80</v>
       </c>
       <c r="B25" s="42" t="str">
-        <f>'[1]Empaque (9)'!B25</f>
+        <f>'[2]Empaque (10)'!B25</f>
         <v>kg</v>
       </c>
       <c r="C25" s="109"/>
@@ -11009,11 +10984,11 @@
       <c r="P25" s="58"/>
       <c r="S25" s="10"/>
       <c r="Z25" s="41" t="str">
-        <f>'[1]Empaque (9)'!AA25</f>
+        <f>'[2]Empaque (10)'!AA25</f>
         <v>H2E (Orig.) x 80</v>
       </c>
       <c r="AA25" s="44" t="str">
-        <f>'[1]Empaque (9)'!AB25</f>
+        <f>'[2]Empaque (10)'!AB25</f>
         <v>kg</v>
       </c>
       <c r="AE25" s="6" t="s">
@@ -11027,55 +11002,55 @@
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A26" s="46" t="str">
-        <f>'[1]Empaque (9)'!A26</f>
+        <f>'[2]Empaque (10)'!A26</f>
         <v>Jb</v>
       </c>
       <c r="B26" s="47">
-        <f>'[1]Empaque (9)'!B26</f>
+        <f>'[2]Empaque (10)'!B26</f>
         <v>12.5</v>
       </c>
       <c r="C26" s="48">
-        <f>'[1]Empaque (9)'!C26</f>
-        <v>288</v>
+        <f>'[2]Empaque (10)'!C26</f>
+        <v>184</v>
       </c>
       <c r="D26" s="49">
-        <f>'[1]Empaque (9)'!D26</f>
-        <v>0.77419354838709675</v>
+        <f>'[2]Empaque (10)'!D26</f>
+        <v>0.64111498257839716</v>
       </c>
       <c r="E26" s="50">
-        <f>'[1]Empaque (9)'!F26</f>
+        <f>'[2]Empaque (10)'!F26</f>
         <v>0</v>
       </c>
       <c r="F26" s="51">
-        <f>'[1]Empaque (9)'!G26</f>
+        <f>'[2]Empaque (10)'!G26</f>
         <v>0</v>
       </c>
       <c r="G26" s="52">
-        <f>'[1]Empaque (9)'!H26</f>
+        <f>'[2]Empaque (10)'!H26</f>
         <v>0</v>
       </c>
       <c r="H26" s="48">
-        <f>'[1]Empaque (9)'!I26</f>
-        <v>516</v>
+        <f>'[2]Empaque (10)'!I26</f>
+        <v>169</v>
       </c>
       <c r="I26" s="53">
-        <f>'[1]Empaque (9)'!J26</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!J26</f>
+        <v>15</v>
       </c>
       <c r="J26" s="54">
-        <f>'[1]Empaque (9)'!K26</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!K26</f>
+        <v>0.20833333333333334</v>
       </c>
       <c r="K26" s="55">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="L26" s="55">
         <f>IF(K26="",0,K26-$P$5)</f>
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="M26" s="55">
         <f t="shared" ref="M26:M31" si="2">(C26+E26-F26)*L26</f>
-        <v>104832</v>
+        <v>63296</v>
       </c>
       <c r="N26" s="57"/>
       <c r="P26" s="58">
@@ -11098,20 +11073,20 @@
         <v>0</v>
       </c>
       <c r="Z26" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA26</f>
+        <f>'[2]Empaque (10)'!AA26</f>
         <v>Jb</v>
       </c>
       <c r="AA26" s="61">
-        <f>'[1]Empaque (9)'!AB26</f>
+        <f>'[2]Empaque (10)'!AB26</f>
         <v>12.5</v>
       </c>
       <c r="AB26" s="62">
-        <f>'[1]Empaque (9)'!AC26</f>
-        <v>1316</v>
+        <f>'[2]Empaque (10)'!AC26</f>
+        <v>1500</v>
       </c>
       <c r="AC26" s="63">
-        <f>'[1]Empaque (9)'!AD26</f>
-        <v>0.8292375551354757</v>
+        <f>'[2]Empaque (10)'!AD26</f>
+        <v>0.80042689434365</v>
       </c>
       <c r="AG26" s="64"/>
       <c r="AH26" s="65">
@@ -11123,55 +11098,55 @@
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A27" s="46" t="str">
-        <f>'[1]Empaque (9)'!A27</f>
+        <f>'[2]Empaque (10)'!A27</f>
         <v>Xl</v>
       </c>
       <c r="B27" s="66">
-        <f>'[1]Empaque (9)'!B27</f>
+        <f>'[2]Empaque (10)'!B27</f>
         <v>12.5</v>
       </c>
       <c r="C27" s="67">
-        <f>'[1]Empaque (9)'!C27</f>
-        <v>51</v>
+        <f>'[2]Empaque (10)'!C27</f>
+        <v>65</v>
       </c>
       <c r="D27" s="49">
-        <f>'[1]Empaque (9)'!D27</f>
-        <v>0.13709677419354838</v>
+        <f>'[2]Empaque (10)'!D27</f>
+        <v>0.2264808362369338</v>
       </c>
       <c r="E27" s="50">
-        <f>'[1]Empaque (9)'!F27</f>
+        <f>'[2]Empaque (10)'!F27</f>
         <v>0</v>
       </c>
       <c r="F27" s="51">
-        <f>'[1]Empaque (9)'!G27</f>
+        <f>'[2]Empaque (10)'!G27</f>
         <v>0</v>
       </c>
       <c r="G27" s="68">
-        <f>'[1]Empaque (9)'!H27</f>
+        <f>'[2]Empaque (10)'!H27</f>
         <v>0</v>
       </c>
       <c r="H27" s="67">
-        <f>'[1]Empaque (9)'!I27</f>
-        <v>110</v>
+        <f>'[2]Empaque (10)'!I27</f>
+        <v>0</v>
       </c>
       <c r="I27" s="53">
-        <f>'[1]Empaque (9)'!J27</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!J27</f>
+        <v>65</v>
       </c>
       <c r="J27" s="54">
-        <f>'[1]Empaque (9)'!K27</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!K27</f>
+        <v>0.90277777777777779</v>
       </c>
       <c r="K27" s="69">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="L27" s="69">
         <f t="shared" ref="L27:L31" si="3">IF(K27="",0,K27-$P$5)</f>
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="M27" s="69">
         <f t="shared" si="2"/>
-        <v>18564</v>
+        <v>22360</v>
       </c>
       <c r="N27" s="71"/>
       <c r="P27" s="58">
@@ -11179,20 +11154,20 @@
       </c>
       <c r="S27" s="10"/>
       <c r="Z27" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA27</f>
+        <f>'[2]Empaque (10)'!AA27</f>
         <v>Xl</v>
       </c>
       <c r="AA27" s="72">
-        <f>'[1]Empaque (9)'!AB27</f>
+        <f>'[2]Empaque (10)'!AB27</f>
         <v>12.5</v>
       </c>
       <c r="AB27" s="62">
-        <f>'[1]Empaque (9)'!AC27</f>
-        <v>150</v>
+        <f>'[2]Empaque (10)'!AC27</f>
+        <v>215</v>
       </c>
       <c r="AC27" s="63">
-        <f>'[1]Empaque (9)'!AD27</f>
-        <v>9.4517958412098299E-2</v>
+        <f>'[2]Empaque (10)'!AD27</f>
+        <v>0.11472785485592316</v>
       </c>
       <c r="AG27" s="73"/>
       <c r="AH27" s="74">
@@ -11204,55 +11179,55 @@
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A28" s="46" t="str">
-        <f>'[1]Empaque (9)'!A28</f>
+        <f>'[2]Empaque (10)'!A28</f>
         <v>Lg</v>
       </c>
       <c r="B28" s="47">
-        <f>'[1]Empaque (9)'!B28</f>
+        <f>'[2]Empaque (10)'!B28</f>
         <v>12.5</v>
       </c>
       <c r="C28" s="67">
-        <f>'[1]Empaque (9)'!C28</f>
+        <f>'[2]Empaque (10)'!C28</f>
         <v>20</v>
       </c>
       <c r="D28" s="49">
-        <f>'[1]Empaque (9)'!D28</f>
-        <v>5.3763440860215055E-2</v>
+        <f>'[2]Empaque (10)'!D28</f>
+        <v>6.968641114982578E-2</v>
       </c>
       <c r="E28" s="50">
-        <f>'[1]Empaque (9)'!F28</f>
+        <f>'[2]Empaque (10)'!F28</f>
         <v>0</v>
       </c>
       <c r="F28" s="51">
-        <f>'[1]Empaque (9)'!G28</f>
+        <f>'[2]Empaque (10)'!G28</f>
         <v>0</v>
       </c>
       <c r="G28" s="68">
-        <f>'[1]Empaque (9)'!H28</f>
+        <f>'[2]Empaque (10)'!H28</f>
         <v>0</v>
       </c>
       <c r="H28" s="67">
-        <f>'[1]Empaque (9)'!I28</f>
-        <v>38</v>
+        <f>'[2]Empaque (10)'!I28</f>
+        <v>1</v>
       </c>
       <c r="I28" s="53">
-        <f>'[1]Empaque (9)'!J28</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!J28</f>
+        <v>19</v>
       </c>
       <c r="J28" s="54">
-        <f>'[1]Empaque (9)'!K28</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!K28</f>
+        <v>0.2638888888888889</v>
       </c>
       <c r="K28" s="69">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="L28" s="69">
         <f t="shared" si="3"/>
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="M28" s="69">
         <f t="shared" si="2"/>
-        <v>7280</v>
+        <v>6880</v>
       </c>
       <c r="N28" s="75"/>
       <c r="P28" s="58">
@@ -11260,20 +11235,20 @@
       </c>
       <c r="S28" s="10"/>
       <c r="Z28" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA28</f>
+        <f>'[2]Empaque (10)'!AA28</f>
         <v>Lg</v>
       </c>
       <c r="AA28" s="61">
-        <f>'[1]Empaque (9)'!AB28</f>
+        <f>'[2]Empaque (10)'!AB28</f>
         <v>12.5</v>
       </c>
       <c r="AB28" s="62">
-        <f>'[1]Empaque (9)'!AC28</f>
-        <v>65</v>
+        <f>'[2]Empaque (10)'!AC28</f>
+        <v>85</v>
       </c>
       <c r="AC28" s="63">
-        <f>'[1]Empaque (9)'!AD28</f>
-        <v>4.0957781978575927E-2</v>
+        <f>'[2]Empaque (10)'!AD28</f>
+        <v>4.5357524012806828E-2</v>
       </c>
       <c r="AG28" s="73"/>
       <c r="AH28" s="74">
@@ -11285,55 +11260,55 @@
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A29" s="46" t="str">
-        <f>'[1]Empaque (9)'!A29</f>
+        <f>'[2]Empaque (10)'!A29</f>
         <v>Md</v>
       </c>
       <c r="B29" s="66">
-        <f>'[1]Empaque (9)'!B29</f>
+        <f>'[2]Empaque (10)'!B29</f>
         <v>12.5</v>
       </c>
       <c r="C29" s="67">
-        <f>'[1]Empaque (9)'!C29</f>
-        <v>4</v>
+        <f>'[2]Empaque (10)'!C29</f>
+        <v>7</v>
       </c>
       <c r="D29" s="49">
-        <f>'[1]Empaque (9)'!D29</f>
-        <v>1.0752688172043012E-2</v>
+        <f>'[2]Empaque (10)'!D29</f>
+        <v>2.4390243902439025E-2</v>
       </c>
       <c r="E29" s="50">
-        <f>'[1]Empaque (9)'!F29</f>
+        <f>'[2]Empaque (10)'!F29</f>
         <v>0</v>
       </c>
       <c r="F29" s="51">
-        <f>'[1]Empaque (9)'!G29</f>
+        <f>'[2]Empaque (10)'!G29</f>
         <v>0</v>
       </c>
       <c r="G29" s="68">
-        <f>'[1]Empaque (9)'!H29</f>
+        <f>'[2]Empaque (10)'!H29</f>
         <v>0</v>
       </c>
       <c r="H29" s="67">
-        <f>'[1]Empaque (9)'!I29</f>
-        <v>14</v>
+        <f>'[2]Empaque (10)'!I29</f>
+        <v>0</v>
       </c>
       <c r="I29" s="53">
-        <f>'[1]Empaque (9)'!J29</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!J29</f>
+        <v>7</v>
       </c>
       <c r="J29" s="54">
-        <f>'[1]Empaque (9)'!K29</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!K29</f>
+        <v>9.7222222222222224E-2</v>
       </c>
       <c r="K29" s="69">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="L29" s="69">
         <f t="shared" si="3"/>
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="M29" s="69">
         <f t="shared" si="2"/>
-        <v>1456</v>
+        <v>2408</v>
       </c>
       <c r="N29" s="76"/>
       <c r="P29" s="58">
@@ -11341,20 +11316,20 @@
       </c>
       <c r="S29" s="10"/>
       <c r="Z29" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA29</f>
+        <f>'[2]Empaque (10)'!AA29</f>
         <v>Md</v>
       </c>
       <c r="AA29" s="72">
-        <f>'[1]Empaque (9)'!AB29</f>
+        <f>'[2]Empaque (10)'!AB29</f>
         <v>12.5</v>
       </c>
       <c r="AB29" s="62">
-        <f>'[1]Empaque (9)'!AC29</f>
-        <v>30</v>
+        <f>'[2]Empaque (10)'!AC29</f>
+        <v>37</v>
       </c>
       <c r="AC29" s="63">
-        <f>'[1]Empaque (9)'!AD29</f>
-        <v>1.890359168241966E-2</v>
+        <f>'[2]Empaque (10)'!AD29</f>
+        <v>1.9743863393810034E-2</v>
       </c>
       <c r="AG29" s="73"/>
       <c r="AH29" s="74">
@@ -11366,55 +11341,55 @@
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A30" s="46" t="str">
-        <f>'[1]Empaque (9)'!A30</f>
+        <f>'[2]Empaque (10)'!A30</f>
         <v>Sm</v>
       </c>
       <c r="B30" s="47">
-        <f>'[1]Empaque (9)'!B30</f>
+        <f>'[2]Empaque (10)'!B30</f>
         <v>12.5</v>
       </c>
       <c r="C30" s="67">
-        <f>'[1]Empaque (9)'!C30</f>
-        <v>4</v>
+        <f>'[2]Empaque (10)'!C30</f>
+        <v>8</v>
       </c>
       <c r="D30" s="49">
-        <f>'[1]Empaque (9)'!D30</f>
-        <v>1.0752688172043012E-2</v>
+        <f>'[2]Empaque (10)'!D30</f>
+        <v>2.7874564459930314E-2</v>
       </c>
       <c r="E30" s="50">
-        <f>'[1]Empaque (9)'!F30</f>
+        <f>'[2]Empaque (10)'!F30</f>
         <v>0</v>
       </c>
       <c r="F30" s="51">
-        <f>'[1]Empaque (9)'!G30</f>
+        <f>'[2]Empaque (10)'!G30</f>
         <v>0</v>
       </c>
       <c r="G30" s="68">
-        <f>'[1]Empaque (9)'!H30</f>
+        <f>'[2]Empaque (10)'!H30</f>
         <v>0</v>
       </c>
       <c r="H30" s="67">
-        <f>'[1]Empaque (9)'!I30</f>
-        <v>13</v>
+        <f>'[2]Empaque (10)'!I30</f>
+        <v>0</v>
       </c>
       <c r="I30" s="53">
-        <f>'[1]Empaque (9)'!J30</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!J30</f>
+        <v>8</v>
       </c>
       <c r="J30" s="54">
-        <f>'[1]Empaque (9)'!K30</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!K30</f>
+        <v>0.1111111111111111</v>
       </c>
       <c r="K30" s="69">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="L30" s="69">
         <f t="shared" si="3"/>
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="M30" s="69">
         <f t="shared" si="2"/>
-        <v>1456</v>
+        <v>2752</v>
       </c>
       <c r="N30" s="76"/>
       <c r="P30" s="58">
@@ -11422,20 +11397,20 @@
       </c>
       <c r="S30" s="10"/>
       <c r="Z30" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA30</f>
+        <f>'[2]Empaque (10)'!AA30</f>
         <v>Sm</v>
       </c>
       <c r="AA30" s="61">
-        <f>'[1]Empaque (9)'!AB30</f>
+        <f>'[2]Empaque (10)'!AB30</f>
         <v>12.5</v>
       </c>
       <c r="AB30" s="77">
-        <f>'[1]Empaque (9)'!AC30</f>
-        <v>21</v>
+        <f>'[2]Empaque (10)'!AC30</f>
+        <v>29</v>
       </c>
       <c r="AC30" s="63">
-        <f>'[1]Empaque (9)'!AD30</f>
-        <v>1.3232514177693762E-2</v>
+        <f>'[2]Empaque (10)'!AD30</f>
+        <v>1.5474919957310566E-2</v>
       </c>
       <c r="AG30" s="64"/>
       <c r="AH30" s="78">
@@ -11447,55 +11422,55 @@
     </row>
     <row r="31" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="79" t="str">
-        <f>'[1]Empaque (9)'!A31</f>
+        <f>'[2]Empaque (10)'!A31</f>
         <v>Mixto</v>
       </c>
       <c r="B31" s="111">
-        <f>'[1]Empaque (9)'!B31</f>
+        <f>'[2]Empaque (10)'!B31</f>
         <v>12.5</v>
       </c>
       <c r="C31" s="81">
-        <f>'[1]Empaque (9)'!C31</f>
-        <v>5</v>
+        <f>'[2]Empaque (10)'!C31</f>
+        <v>3</v>
       </c>
       <c r="D31" s="82">
-        <f>'[1]Empaque (9)'!D31</f>
-        <v>1.3440860215053764E-2</v>
+        <f>'[2]Empaque (10)'!D31</f>
+        <v>1.0452961672473868E-2</v>
       </c>
       <c r="E31" s="83">
-        <f>'[1]Empaque (9)'!F31</f>
+        <f>'[2]Empaque (10)'!F31</f>
         <v>0</v>
       </c>
       <c r="F31" s="84">
-        <f>'[1]Empaque (9)'!G31</f>
+        <f>'[2]Empaque (10)'!G31</f>
         <v>0</v>
       </c>
       <c r="G31" s="85">
-        <f>'[1]Empaque (9)'!H31</f>
+        <f>'[2]Empaque (10)'!H31</f>
         <v>0</v>
       </c>
       <c r="H31" s="81">
-        <f>'[1]Empaque (9)'!I31</f>
-        <v>5</v>
+        <f>'[2]Empaque (10)'!I31</f>
+        <v>0</v>
       </c>
       <c r="I31" s="86">
-        <f>'[1]Empaque (9)'!J31</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!J31</f>
+        <v>3</v>
       </c>
       <c r="J31" s="87">
-        <f>'[1]Empaque (9)'!K31</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!K31</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="K31" s="88">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="L31" s="88">
         <f t="shared" si="3"/>
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="M31" s="88">
         <f t="shared" si="2"/>
-        <v>1820</v>
+        <v>1032</v>
       </c>
       <c r="N31" s="43"/>
       <c r="O31" s="43"/>
@@ -11504,20 +11479,20 @@
       </c>
       <c r="S31" s="10"/>
       <c r="Z31" s="90" t="str">
-        <f>'[1]Empaque (9)'!AA31</f>
+        <f>'[2]Empaque (10)'!AA31</f>
         <v>xs</v>
       </c>
       <c r="AA31" s="91">
-        <f>'[1]Empaque (9)'!AB31</f>
+        <f>'[2]Empaque (10)'!AB31</f>
         <v>12.5</v>
       </c>
       <c r="AB31" s="92">
-        <f>'[1]Empaque (9)'!AC31</f>
-        <v>5</v>
+        <f>'[2]Empaque (10)'!AC31</f>
+        <v>8</v>
       </c>
       <c r="AC31" s="93">
-        <f>'[1]Empaque (9)'!AD31</f>
-        <v>3.1505986137366098E-3</v>
+        <f>'[2]Empaque (10)'!AD31</f>
+        <v>4.2689434364994666E-3</v>
       </c>
       <c r="AG31" s="94"/>
       <c r="AH31" s="95">
@@ -11529,48 +11504,48 @@
     </row>
     <row r="32" spans="1:36" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C32" s="96">
-        <f>'[1]Empaque (9)'!C32</f>
-        <v>372</v>
+        <f>'[2]Empaque (10)'!C32</f>
+        <v>287</v>
       </c>
       <c r="D32" s="97">
-        <f>'[1]Empaque (9)'!D32</f>
+        <f>'[2]Empaque (10)'!D32</f>
         <v>1</v>
       </c>
       <c r="E32" s="98">
-        <f>'[1]Empaque (9)'!F32</f>
+        <f>'[2]Empaque (10)'!F32</f>
         <v>0</v>
       </c>
       <c r="F32" s="99">
-        <f>'[1]Empaque (9)'!G32</f>
+        <f>'[2]Empaque (10)'!G32</f>
         <v>0</v>
       </c>
       <c r="G32" s="100">
-        <f>'[1]Empaque (9)'!H32</f>
+        <f>'[2]Empaque (10)'!H32</f>
         <v>0</v>
       </c>
       <c r="H32" s="100">
-        <f>'[1]Empaque (9)'!I32</f>
-        <v>696</v>
+        <f>'[2]Empaque (10)'!I32</f>
+        <v>170</v>
       </c>
       <c r="I32" s="100">
-        <f>'[1]Empaque (9)'!J32</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!J32</f>
+        <v>117</v>
       </c>
       <c r="J32" s="101">
-        <f>'[1]Empaque (9)'!K32</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!K32</f>
+        <v>1.625</v>
       </c>
       <c r="K32" s="102">
         <f>IFERROR((C26*K26+C27*K27+C28*K28+C29*K29+C30*K30+C31*K31)/C32,0)</f>
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="L32" s="103">
         <f>IFERROR(M32/C32,0)</f>
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="M32" s="103">
         <f>SUM(M26:M31)</f>
-        <v>135408</v>
+        <v>98728</v>
       </c>
       <c r="N32" s="55"/>
       <c r="O32" s="55"/>
@@ -11578,12 +11553,12 @@
       <c r="S32" s="10"/>
       <c r="AA32" s="104"/>
       <c r="AB32" s="105">
-        <f>'[1]Empaque (9)'!AC32</f>
-        <v>1587</v>
+        <f>'[2]Empaque (10)'!AC32</f>
+        <v>1874</v>
       </c>
       <c r="AC32" s="106">
-        <f>'[1]Empaque (9)'!AD32</f>
-        <v>0.99999999999999989</v>
+        <f>'[2]Empaque (10)'!AD32</f>
+        <v>1</v>
       </c>
       <c r="AH32" s="107">
         <v>0</v>
@@ -11597,11 +11572,11 @@
     </row>
     <row r="33" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="41" t="str">
-        <f>'[1]Empaque (9)'!A33</f>
+        <f>'[2]Empaque (10)'!A33</f>
         <v>Genérica x 80</v>
       </c>
       <c r="B33" s="172" t="str">
-        <f>'[1]Empaque (9)'!B33</f>
+        <f>'[2]Empaque (10)'!B33</f>
         <v>kg</v>
       </c>
       <c r="C33" s="109"/>
@@ -11623,11 +11598,11 @@
       <c r="P33" s="58"/>
       <c r="S33" s="10"/>
       <c r="Z33" s="41" t="str">
-        <f>'[1]Empaque (9)'!AA33</f>
+        <f>'[2]Empaque (10)'!AA33</f>
         <v>Genérica x 80</v>
       </c>
       <c r="AA33" s="44" t="str">
-        <f>'[1]Empaque (9)'!AB33</f>
+        <f>'[2]Empaque (10)'!AB33</f>
         <v>kg</v>
       </c>
       <c r="AE33" s="6" t="s">
@@ -11641,48 +11616,48 @@
     </row>
     <row r="34" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="46" t="str">
-        <f>'[1]Empaque (9)'!A34</f>
+        <f>'[2]Empaque (10)'!A34</f>
         <v>Jb</v>
       </c>
       <c r="B34" s="173">
-        <f>'[1]Empaque (9)'!B34</f>
+        <f>'[2]Empaque (10)'!B34</f>
         <v>13</v>
       </c>
       <c r="C34" s="48">
-        <f>'[1]Empaque (9)'!C34</f>
+        <f>'[2]Empaque (10)'!C34</f>
         <v>0</v>
       </c>
       <c r="D34" s="49" t="str">
-        <f>'[1]Empaque (9)'!D34</f>
+        <f>'[2]Empaque (10)'!D34</f>
         <v/>
       </c>
       <c r="E34" s="50">
-        <f>'[1]Empaque (9)'!F34</f>
+        <f>'[2]Empaque (10)'!F34</f>
         <v>0</v>
       </c>
       <c r="F34" s="51">
-        <f>'[1]Empaque (9)'!G34</f>
+        <f>'[2]Empaque (10)'!G34</f>
         <v>0</v>
       </c>
       <c r="G34" s="52">
-        <f>'[1]Empaque (9)'!H34</f>
+        <f>'[2]Empaque (10)'!H34</f>
         <v>0</v>
       </c>
       <c r="H34" s="48">
-        <f>'[1]Empaque (9)'!I34</f>
+        <f>'[2]Empaque (10)'!I34</f>
         <v>0</v>
       </c>
       <c r="I34" s="53">
-        <f>'[1]Empaque (9)'!J34</f>
+        <f>'[2]Empaque (10)'!J34</f>
         <v>0</v>
       </c>
       <c r="J34" s="54">
-        <f>'[1]Empaque (9)'!K34</f>
+        <f>'[2]Empaque (10)'!K34</f>
         <v>0</v>
       </c>
       <c r="K34" s="55"/>
       <c r="L34" s="55">
-        <f>IF(C34=0+E34-F34,0,(K34-'[2]Reporte Semanal'!$C$74)-(K34*'[2]Reporte Semanal'!$C$75))</f>
+        <f>IF(C34=0+E34-F34,0,(K34-'[1]Reporte Semanal'!$C$74)-(K34*'[1]Reporte Semanal'!$C$75))</f>
         <v>0</v>
       </c>
       <c r="M34" s="55">
@@ -11710,19 +11685,19 @@
         <v>0</v>
       </c>
       <c r="Z34" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA34</f>
+        <f>'[2]Empaque (10)'!AA34</f>
         <v>Jb</v>
       </c>
       <c r="AA34" s="61">
-        <f>'[1]Empaque (9)'!AB34</f>
+        <f>'[2]Empaque (10)'!AB34</f>
         <v>13</v>
       </c>
       <c r="AB34" s="62">
-        <f>'[1]Empaque (9)'!AC34</f>
+        <f>'[2]Empaque (10)'!AC34</f>
         <v>0</v>
       </c>
       <c r="AC34" s="63">
-        <f>'[1]Empaque (9)'!AD34</f>
+        <f>'[2]Empaque (10)'!AD34</f>
         <v>0</v>
       </c>
       <c r="AG34" s="64"/>
@@ -11735,48 +11710,48 @@
     </row>
     <row r="35" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="46" t="str">
-        <f>'[1]Empaque (9)'!A35</f>
+        <f>'[2]Empaque (10)'!A35</f>
         <v>Xl</v>
       </c>
       <c r="B35" s="174">
-        <f>'[1]Empaque (9)'!B35</f>
+        <f>'[2]Empaque (10)'!B35</f>
         <v>13</v>
       </c>
       <c r="C35" s="67">
-        <f>'[1]Empaque (9)'!C35</f>
+        <f>'[2]Empaque (10)'!C35</f>
         <v>0</v>
       </c>
       <c r="D35" s="49" t="str">
-        <f>'[1]Empaque (9)'!D35</f>
+        <f>'[2]Empaque (10)'!D35</f>
         <v/>
       </c>
       <c r="E35" s="50">
-        <f>'[1]Empaque (9)'!F35</f>
+        <f>'[2]Empaque (10)'!F35</f>
         <v>0</v>
       </c>
       <c r="F35" s="51">
-        <f>'[1]Empaque (9)'!G35</f>
+        <f>'[2]Empaque (10)'!G35</f>
         <v>0</v>
       </c>
       <c r="G35" s="68">
-        <f>'[1]Empaque (9)'!H35</f>
+        <f>'[2]Empaque (10)'!H35</f>
         <v>0</v>
       </c>
       <c r="H35" s="67">
-        <f>'[1]Empaque (9)'!I35</f>
+        <f>'[2]Empaque (10)'!I35</f>
         <v>0</v>
       </c>
       <c r="I35" s="53">
-        <f>'[1]Empaque (9)'!J35</f>
+        <f>'[2]Empaque (10)'!J35</f>
         <v>0</v>
       </c>
       <c r="J35" s="54">
-        <f>'[1]Empaque (9)'!K35</f>
+        <f>'[2]Empaque (10)'!K35</f>
         <v>0</v>
       </c>
       <c r="K35" s="69"/>
       <c r="L35" s="69">
-        <f>IF(C35=0+E35-F35,0,(K35-'[2]Reporte Semanal'!$C$74)-(K35*'[2]Reporte Semanal'!$C$75))</f>
+        <f>IF(C35=0+E35-F35,0,(K35-'[1]Reporte Semanal'!$C$74)-(K35*'[1]Reporte Semanal'!$C$75))</f>
         <v>0</v>
       </c>
       <c r="M35" s="69">
@@ -11789,19 +11764,19 @@
       </c>
       <c r="S35" s="10"/>
       <c r="Z35" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA35</f>
+        <f>'[2]Empaque (10)'!AA35</f>
         <v>Xl</v>
       </c>
       <c r="AA35" s="72">
-        <f>'[1]Empaque (9)'!AB35</f>
+        <f>'[2]Empaque (10)'!AB35</f>
         <v>13</v>
       </c>
       <c r="AB35" s="62">
-        <f>'[1]Empaque (9)'!AC35</f>
+        <f>'[2]Empaque (10)'!AC35</f>
         <v>0</v>
       </c>
       <c r="AC35" s="63">
-        <f>'[1]Empaque (9)'!AD35</f>
+        <f>'[2]Empaque (10)'!AD35</f>
         <v>0</v>
       </c>
       <c r="AG35" s="73"/>
@@ -11814,48 +11789,48 @@
     </row>
     <row r="36" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="46" t="str">
-        <f>'[1]Empaque (9)'!A36</f>
+        <f>'[2]Empaque (10)'!A36</f>
         <v>Lg</v>
       </c>
       <c r="B36" s="173">
-        <f>'[1]Empaque (9)'!B36</f>
+        <f>'[2]Empaque (10)'!B36</f>
         <v>13</v>
       </c>
       <c r="C36" s="67">
-        <f>'[1]Empaque (9)'!C36</f>
+        <f>'[2]Empaque (10)'!C36</f>
         <v>0</v>
       </c>
       <c r="D36" s="49" t="str">
-        <f>'[1]Empaque (9)'!D36</f>
+        <f>'[2]Empaque (10)'!D36</f>
         <v/>
       </c>
       <c r="E36" s="50">
-        <f>'[1]Empaque (9)'!F36</f>
+        <f>'[2]Empaque (10)'!F36</f>
         <v>0</v>
       </c>
       <c r="F36" s="51">
-        <f>'[1]Empaque (9)'!G36</f>
+        <f>'[2]Empaque (10)'!G36</f>
         <v>0</v>
       </c>
       <c r="G36" s="68">
-        <f>'[1]Empaque (9)'!H36</f>
+        <f>'[2]Empaque (10)'!H36</f>
         <v>0</v>
       </c>
       <c r="H36" s="67">
-        <f>'[1]Empaque (9)'!I36</f>
+        <f>'[2]Empaque (10)'!I36</f>
         <v>0</v>
       </c>
       <c r="I36" s="53">
-        <f>'[1]Empaque (9)'!J36</f>
+        <f>'[2]Empaque (10)'!J36</f>
         <v>0</v>
       </c>
       <c r="J36" s="54">
-        <f>'[1]Empaque (9)'!K36</f>
+        <f>'[2]Empaque (10)'!K36</f>
         <v>0</v>
       </c>
       <c r="K36" s="69"/>
       <c r="L36" s="69">
-        <f>IF(C36=0+E36-F36,0,(K36-'[2]Reporte Semanal'!$C$74)-(K36*'[2]Reporte Semanal'!$C$75))</f>
+        <f>IF(C36=0+E36-F36,0,(K36-'[1]Reporte Semanal'!$C$74)-(K36*'[1]Reporte Semanal'!$C$75))</f>
         <v>0</v>
       </c>
       <c r="M36" s="69">
@@ -11868,19 +11843,19 @@
       </c>
       <c r="S36" s="10"/>
       <c r="Z36" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA36</f>
+        <f>'[2]Empaque (10)'!AA36</f>
         <v>Lg</v>
       </c>
       <c r="AA36" s="61">
-        <f>'[1]Empaque (9)'!AB36</f>
+        <f>'[2]Empaque (10)'!AB36</f>
         <v>13</v>
       </c>
       <c r="AB36" s="62">
-        <f>'[1]Empaque (9)'!AC36</f>
+        <f>'[2]Empaque (10)'!AC36</f>
         <v>0</v>
       </c>
       <c r="AC36" s="63">
-        <f>'[1]Empaque (9)'!AD36</f>
+        <f>'[2]Empaque (10)'!AD36</f>
         <v>0</v>
       </c>
       <c r="AG36" s="73"/>
@@ -11893,48 +11868,48 @@
     </row>
     <row r="37" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="46" t="str">
-        <f>'[1]Empaque (9)'!A37</f>
+        <f>'[2]Empaque (10)'!A37</f>
         <v>Md</v>
       </c>
       <c r="B37" s="174">
-        <f>'[1]Empaque (9)'!B37</f>
+        <f>'[2]Empaque (10)'!B37</f>
         <v>13</v>
       </c>
       <c r="C37" s="67">
-        <f>'[1]Empaque (9)'!C37</f>
+        <f>'[2]Empaque (10)'!C37</f>
         <v>0</v>
       </c>
       <c r="D37" s="49" t="str">
-        <f>'[1]Empaque (9)'!D37</f>
+        <f>'[2]Empaque (10)'!D37</f>
         <v/>
       </c>
       <c r="E37" s="50">
-        <f>'[1]Empaque (9)'!F37</f>
+        <f>'[2]Empaque (10)'!F37</f>
         <v>0</v>
       </c>
       <c r="F37" s="51">
-        <f>'[1]Empaque (9)'!G37</f>
+        <f>'[2]Empaque (10)'!G37</f>
         <v>0</v>
       </c>
       <c r="G37" s="68">
-        <f>'[1]Empaque (9)'!H37</f>
+        <f>'[2]Empaque (10)'!H37</f>
         <v>0</v>
       </c>
       <c r="H37" s="67">
-        <f>'[1]Empaque (9)'!I37</f>
+        <f>'[2]Empaque (10)'!I37</f>
         <v>0</v>
       </c>
       <c r="I37" s="53">
-        <f>'[1]Empaque (9)'!J37</f>
+        <f>'[2]Empaque (10)'!J37</f>
         <v>0</v>
       </c>
       <c r="J37" s="54">
-        <f>'[1]Empaque (9)'!K37</f>
+        <f>'[2]Empaque (10)'!K37</f>
         <v>0</v>
       </c>
       <c r="K37" s="69"/>
       <c r="L37" s="69">
-        <f>IF(C37=0+E37-F37,0,(K37-'[2]Reporte Semanal'!$C$74)-(K37*'[2]Reporte Semanal'!$C$75))</f>
+        <f>IF(C37=0+E37-F37,0,(K37-'[1]Reporte Semanal'!$C$74)-(K37*'[1]Reporte Semanal'!$C$75))</f>
         <v>0</v>
       </c>
       <c r="M37" s="69">
@@ -11947,19 +11922,19 @@
       </c>
       <c r="S37" s="10"/>
       <c r="Z37" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA37</f>
+        <f>'[2]Empaque (10)'!AA37</f>
         <v>Md</v>
       </c>
       <c r="AA37" s="72">
-        <f>'[1]Empaque (9)'!AB37</f>
+        <f>'[2]Empaque (10)'!AB37</f>
         <v>13</v>
       </c>
       <c r="AB37" s="62">
-        <f>'[1]Empaque (9)'!AC37</f>
+        <f>'[2]Empaque (10)'!AC37</f>
         <v>0</v>
       </c>
       <c r="AC37" s="63">
-        <f>'[1]Empaque (9)'!AD37</f>
+        <f>'[2]Empaque (10)'!AD37</f>
         <v>0</v>
       </c>
       <c r="AG37" s="73"/>
@@ -11972,48 +11947,48 @@
     </row>
     <row r="38" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="46" t="str">
-        <f>'[1]Empaque (9)'!A38</f>
+        <f>'[2]Empaque (10)'!A38</f>
         <v>Sm</v>
       </c>
       <c r="B38" s="173">
-        <f>'[1]Empaque (9)'!B38</f>
+        <f>'[2]Empaque (10)'!B38</f>
         <v>13</v>
       </c>
       <c r="C38" s="67">
-        <f>'[1]Empaque (9)'!C38</f>
+        <f>'[2]Empaque (10)'!C38</f>
         <v>0</v>
       </c>
       <c r="D38" s="49" t="str">
-        <f>'[1]Empaque (9)'!D38</f>
+        <f>'[2]Empaque (10)'!D38</f>
         <v/>
       </c>
       <c r="E38" s="50">
-        <f>'[1]Empaque (9)'!F38</f>
+        <f>'[2]Empaque (10)'!F38</f>
         <v>0</v>
       </c>
       <c r="F38" s="51">
-        <f>'[1]Empaque (9)'!G38</f>
+        <f>'[2]Empaque (10)'!G38</f>
         <v>0</v>
       </c>
       <c r="G38" s="68">
-        <f>'[1]Empaque (9)'!H38</f>
+        <f>'[2]Empaque (10)'!H38</f>
         <v>0</v>
       </c>
       <c r="H38" s="67">
-        <f>'[1]Empaque (9)'!I38</f>
+        <f>'[2]Empaque (10)'!I38</f>
         <v>0</v>
       </c>
       <c r="I38" s="53">
-        <f>'[1]Empaque (9)'!J38</f>
+        <f>'[2]Empaque (10)'!J38</f>
         <v>0</v>
       </c>
       <c r="J38" s="54">
-        <f>'[1]Empaque (9)'!K38</f>
+        <f>'[2]Empaque (10)'!K38</f>
         <v>0</v>
       </c>
       <c r="K38" s="69"/>
       <c r="L38" s="69">
-        <f>IF(C38=0+E38-F38,0,(K38-'[2]Reporte Semanal'!$C$74)-(K38*'[2]Reporte Semanal'!$C$75))</f>
+        <f>IF(C38=0+E38-F38,0,(K38-'[1]Reporte Semanal'!$C$74)-(K38*'[1]Reporte Semanal'!$C$75))</f>
         <v>0</v>
       </c>
       <c r="M38" s="69">
@@ -12026,19 +12001,19 @@
       </c>
       <c r="S38" s="10"/>
       <c r="Z38" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA38</f>
+        <f>'[2]Empaque (10)'!AA38</f>
         <v>Sm</v>
       </c>
       <c r="AA38" s="61">
-        <f>'[1]Empaque (9)'!AB38</f>
+        <f>'[2]Empaque (10)'!AB38</f>
         <v>13</v>
       </c>
       <c r="AB38" s="77">
-        <f>'[1]Empaque (9)'!AC38</f>
+        <f>'[2]Empaque (10)'!AC38</f>
         <v>0</v>
       </c>
       <c r="AC38" s="63">
-        <f>'[1]Empaque (9)'!AD38</f>
+        <f>'[2]Empaque (10)'!AD38</f>
         <v>0</v>
       </c>
       <c r="AG38" s="64"/>
@@ -12051,48 +12026,48 @@
     </row>
     <row r="39" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="79" t="str">
-        <f>'[1]Empaque (9)'!A39</f>
+        <f>'[2]Empaque (10)'!A39</f>
         <v>Mixto</v>
       </c>
       <c r="B39" s="175">
-        <f>'[1]Empaque (9)'!B39</f>
+        <f>'[2]Empaque (10)'!B39</f>
         <v>0</v>
       </c>
       <c r="C39" s="81">
-        <f>'[1]Empaque (9)'!C39</f>
+        <f>'[2]Empaque (10)'!C39</f>
         <v>0</v>
       </c>
       <c r="D39" s="82" t="str">
-        <f>'[1]Empaque (9)'!D39</f>
+        <f>'[2]Empaque (10)'!D39</f>
         <v/>
       </c>
       <c r="E39" s="83">
-        <f>'[1]Empaque (9)'!F39</f>
+        <f>'[2]Empaque (10)'!F39</f>
         <v>0</v>
       </c>
       <c r="F39" s="84">
-        <f>'[1]Empaque (9)'!G39</f>
+        <f>'[2]Empaque (10)'!G39</f>
         <v>0</v>
       </c>
       <c r="G39" s="85">
-        <f>'[1]Empaque (9)'!H39</f>
+        <f>'[2]Empaque (10)'!H39</f>
         <v>0</v>
       </c>
       <c r="H39" s="81">
-        <f>'[1]Empaque (9)'!I39</f>
+        <f>'[2]Empaque (10)'!I39</f>
         <v>0</v>
       </c>
       <c r="I39" s="86">
-        <f>'[1]Empaque (9)'!J39</f>
+        <f>'[2]Empaque (10)'!J39</f>
         <v>0</v>
       </c>
       <c r="J39" s="87">
-        <f>'[1]Empaque (9)'!K39</f>
+        <f>'[2]Empaque (10)'!K39</f>
         <v>0</v>
       </c>
       <c r="K39" s="88"/>
       <c r="L39" s="88">
-        <f>IF(C39=0+E39-F39,0,(K39-'[2]Reporte Semanal'!$C$74)-(K39*'[2]Reporte Semanal'!$C$75))</f>
+        <f>IF(C39=0+E39-F39,0,(K39-'[1]Reporte Semanal'!$C$74)-(K39*'[1]Reporte Semanal'!$C$75))</f>
         <v>0</v>
       </c>
       <c r="M39" s="88">
@@ -12106,19 +12081,19 @@
       </c>
       <c r="S39" s="10"/>
       <c r="Z39" s="90" t="str">
-        <f>'[1]Empaque (9)'!AA39</f>
+        <f>'[2]Empaque (10)'!AA39</f>
         <v>xs</v>
       </c>
       <c r="AA39" s="91">
-        <f>'[1]Empaque (9)'!AB39</f>
+        <f>'[2]Empaque (10)'!AB39</f>
         <v>0</v>
       </c>
       <c r="AB39" s="92">
-        <f>'[1]Empaque (9)'!AC39</f>
+        <f>'[2]Empaque (10)'!AC39</f>
         <v>0</v>
       </c>
       <c r="AC39" s="93">
-        <f>'[1]Empaque (9)'!AD39</f>
+        <f>'[2]Empaque (10)'!AD39</f>
         <v>0</v>
       </c>
       <c r="AG39" s="94"/>
@@ -12131,35 +12106,35 @@
     </row>
     <row r="40" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C40" s="96">
-        <f>'[1]Empaque (9)'!C40</f>
+        <f>'[2]Empaque (10)'!C40</f>
         <v>0</v>
       </c>
       <c r="D40" s="97" t="str">
-        <f>'[1]Empaque (9)'!D40</f>
+        <f>'[2]Empaque (10)'!D40</f>
         <v/>
       </c>
       <c r="E40" s="98">
-        <f>'[1]Empaque (9)'!F40</f>
+        <f>'[2]Empaque (10)'!F40</f>
         <v>0</v>
       </c>
       <c r="F40" s="99">
-        <f>'[1]Empaque (9)'!G40</f>
+        <f>'[2]Empaque (10)'!G40</f>
         <v>0</v>
       </c>
       <c r="G40" s="100">
-        <f>'[1]Empaque (9)'!H40</f>
+        <f>'[2]Empaque (10)'!H40</f>
         <v>0</v>
       </c>
       <c r="H40" s="100">
-        <f>'[1]Empaque (9)'!I40</f>
+        <f>'[2]Empaque (10)'!I40</f>
         <v>0</v>
       </c>
       <c r="I40" s="100">
-        <f>'[1]Empaque (9)'!J40</f>
+        <f>'[2]Empaque (10)'!J40</f>
         <v>0</v>
       </c>
       <c r="J40" s="101">
-        <f>'[1]Empaque (9)'!K40</f>
+        <f>'[2]Empaque (10)'!K40</f>
         <v>0</v>
       </c>
       <c r="K40" s="102" t="e">
@@ -12180,11 +12155,11 @@
       <c r="S40" s="10"/>
       <c r="AA40" s="104"/>
       <c r="AB40" s="105">
-        <f>'[1]Empaque (9)'!AC40</f>
+        <f>'[2]Empaque (10)'!AC40</f>
         <v>0</v>
       </c>
       <c r="AC40" s="106">
-        <f>'[1]Empaque (9)'!AD40</f>
+        <f>'[2]Empaque (10)'!AD40</f>
         <v>0</v>
       </c>
       <c r="AH40" s="107">
@@ -12199,11 +12174,11 @@
     </row>
     <row r="41" spans="1:36" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="41" t="str">
-        <f>'[1]Empaque (9)'!A41</f>
+        <f>'[2]Empaque (10)'!A41</f>
         <v>1 1/9 x 80</v>
       </c>
       <c r="B41" s="172" t="str">
-        <f>'[1]Empaque (9)'!B41</f>
+        <f>'[2]Empaque (10)'!B41</f>
         <v>kg</v>
       </c>
       <c r="C41" s="109"/>
@@ -12232,43 +12207,43 @@
     </row>
     <row r="42" spans="1:36" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="46" t="str">
-        <f>'[1]Empaque (9)'!A42</f>
+        <f>'[2]Empaque (10)'!A42</f>
         <v>Jb</v>
       </c>
       <c r="B42" s="173">
-        <f>'[1]Empaque (9)'!B42</f>
+        <f>'[2]Empaque (10)'!B42</f>
         <v>22</v>
       </c>
       <c r="C42" s="48">
-        <f>'[1]Empaque (9)'!C42</f>
+        <f>'[2]Empaque (10)'!C42</f>
         <v>0</v>
       </c>
       <c r="D42" s="49" t="str">
-        <f>'[1]Empaque (9)'!D42</f>
+        <f>'[2]Empaque (10)'!D42</f>
         <v/>
       </c>
       <c r="E42" s="50">
-        <f>'[1]Empaque (9)'!F42</f>
+        <f>'[2]Empaque (10)'!F42</f>
         <v>0</v>
       </c>
       <c r="F42" s="51">
-        <f>'[1]Empaque (9)'!G42</f>
+        <f>'[2]Empaque (10)'!G42</f>
         <v>0</v>
       </c>
       <c r="G42" s="52">
-        <f>'[1]Empaque (9)'!H42</f>
+        <f>'[2]Empaque (10)'!H42</f>
         <v>0</v>
       </c>
       <c r="H42" s="48">
-        <f>'[1]Empaque (9)'!I42</f>
+        <f>'[2]Empaque (10)'!I42</f>
         <v>0</v>
       </c>
       <c r="I42" s="53">
-        <f>'[1]Empaque (9)'!J42</f>
+        <f>'[2]Empaque (10)'!J42</f>
         <v>0</v>
       </c>
       <c r="J42" s="54">
-        <f>'[1]Empaque (9)'!K42</f>
+        <f>'[2]Empaque (10)'!K42</f>
         <v>0</v>
       </c>
       <c r="K42" s="55"/>
@@ -12292,43 +12267,43 @@
     </row>
     <row r="43" spans="1:36" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="46" t="str">
-        <f>'[1]Empaque (9)'!A43</f>
+        <f>'[2]Empaque (10)'!A43</f>
         <v>Xl</v>
       </c>
       <c r="B43" s="174">
-        <f>'[1]Empaque (9)'!B43</f>
+        <f>'[2]Empaque (10)'!B43</f>
         <v>22</v>
       </c>
       <c r="C43" s="67">
-        <f>'[1]Empaque (9)'!C43</f>
+        <f>'[2]Empaque (10)'!C43</f>
         <v>0</v>
       </c>
       <c r="D43" s="49" t="str">
-        <f>'[1]Empaque (9)'!D43</f>
+        <f>'[2]Empaque (10)'!D43</f>
         <v/>
       </c>
       <c r="E43" s="50">
-        <f>'[1]Empaque (9)'!F43</f>
+        <f>'[2]Empaque (10)'!F43</f>
         <v>0</v>
       </c>
       <c r="F43" s="51">
-        <f>'[1]Empaque (9)'!G43</f>
+        <f>'[2]Empaque (10)'!G43</f>
         <v>0</v>
       </c>
       <c r="G43" s="68">
-        <f>'[1]Empaque (9)'!H43</f>
+        <f>'[2]Empaque (10)'!H43</f>
         <v>0</v>
       </c>
       <c r="H43" s="67">
-        <f>'[1]Empaque (9)'!I43</f>
+        <f>'[2]Empaque (10)'!I43</f>
         <v>0</v>
       </c>
       <c r="I43" s="53">
-        <f>'[1]Empaque (9)'!J43</f>
+        <f>'[2]Empaque (10)'!J43</f>
         <v>0</v>
       </c>
       <c r="J43" s="54">
-        <f>'[1]Empaque (9)'!K43</f>
+        <f>'[2]Empaque (10)'!K43</f>
         <v>0</v>
       </c>
       <c r="K43" s="69"/>
@@ -12352,43 +12327,43 @@
     </row>
     <row r="44" spans="1:36" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="46" t="str">
-        <f>'[1]Empaque (9)'!A44</f>
+        <f>'[2]Empaque (10)'!A44</f>
         <v>Lg</v>
       </c>
       <c r="B44" s="173">
-        <f>'[1]Empaque (9)'!B44</f>
+        <f>'[2]Empaque (10)'!B44</f>
         <v>22</v>
       </c>
       <c r="C44" s="67">
-        <f>'[1]Empaque (9)'!C44</f>
+        <f>'[2]Empaque (10)'!C44</f>
         <v>0</v>
       </c>
       <c r="D44" s="49" t="str">
-        <f>'[1]Empaque (9)'!D44</f>
+        <f>'[2]Empaque (10)'!D44</f>
         <v/>
       </c>
       <c r="E44" s="50">
-        <f>'[1]Empaque (9)'!F44</f>
+        <f>'[2]Empaque (10)'!F44</f>
         <v>0</v>
       </c>
       <c r="F44" s="51">
-        <f>'[1]Empaque (9)'!G44</f>
+        <f>'[2]Empaque (10)'!G44</f>
         <v>0</v>
       </c>
       <c r="G44" s="68">
-        <f>'[1]Empaque (9)'!H44</f>
+        <f>'[2]Empaque (10)'!H44</f>
         <v>0</v>
       </c>
       <c r="H44" s="67">
-        <f>'[1]Empaque (9)'!I44</f>
+        <f>'[2]Empaque (10)'!I44</f>
         <v>0</v>
       </c>
       <c r="I44" s="53">
-        <f>'[1]Empaque (9)'!J44</f>
+        <f>'[2]Empaque (10)'!J44</f>
         <v>0</v>
       </c>
       <c r="J44" s="54">
-        <f>'[1]Empaque (9)'!K44</f>
+        <f>'[2]Empaque (10)'!K44</f>
         <v>0</v>
       </c>
       <c r="K44" s="69"/>
@@ -12412,43 +12387,43 @@
     </row>
     <row r="45" spans="1:36" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="46" t="str">
-        <f>'[1]Empaque (9)'!A45</f>
+        <f>'[2]Empaque (10)'!A45</f>
         <v>Md</v>
       </c>
       <c r="B45" s="174">
-        <f>'[1]Empaque (9)'!B45</f>
+        <f>'[2]Empaque (10)'!B45</f>
         <v>22</v>
       </c>
       <c r="C45" s="67">
-        <f>'[1]Empaque (9)'!C45</f>
+        <f>'[2]Empaque (10)'!C45</f>
         <v>0</v>
       </c>
       <c r="D45" s="49" t="str">
-        <f>'[1]Empaque (9)'!D45</f>
+        <f>'[2]Empaque (10)'!D45</f>
         <v/>
       </c>
       <c r="E45" s="50">
-        <f>'[1]Empaque (9)'!F45</f>
+        <f>'[2]Empaque (10)'!F45</f>
         <v>0</v>
       </c>
       <c r="F45" s="51">
-        <f>'[1]Empaque (9)'!G45</f>
+        <f>'[2]Empaque (10)'!G45</f>
         <v>0</v>
       </c>
       <c r="G45" s="68">
-        <f>'[1]Empaque (9)'!H45</f>
+        <f>'[2]Empaque (10)'!H45</f>
         <v>0</v>
       </c>
       <c r="H45" s="67">
-        <f>'[1]Empaque (9)'!I45</f>
+        <f>'[2]Empaque (10)'!I45</f>
         <v>0</v>
       </c>
       <c r="I45" s="53">
-        <f>'[1]Empaque (9)'!J45</f>
+        <f>'[2]Empaque (10)'!J45</f>
         <v>0</v>
       </c>
       <c r="J45" s="54">
-        <f>'[1]Empaque (9)'!K45</f>
+        <f>'[2]Empaque (10)'!K45</f>
         <v>0</v>
       </c>
       <c r="K45" s="69"/>
@@ -12472,43 +12447,43 @@
     </row>
     <row r="46" spans="1:36" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="46" t="str">
-        <f>'[1]Empaque (9)'!A46</f>
+        <f>'[2]Empaque (10)'!A46</f>
         <v>Sm</v>
       </c>
       <c r="B46" s="173">
-        <f>'[1]Empaque (9)'!B46</f>
+        <f>'[2]Empaque (10)'!B46</f>
         <v>22</v>
       </c>
       <c r="C46" s="67">
-        <f>'[1]Empaque (9)'!C46</f>
+        <f>'[2]Empaque (10)'!C46</f>
         <v>0</v>
       </c>
       <c r="D46" s="49" t="str">
-        <f>'[1]Empaque (9)'!D46</f>
+        <f>'[2]Empaque (10)'!D46</f>
         <v/>
       </c>
       <c r="E46" s="50">
-        <f>'[1]Empaque (9)'!F46</f>
+        <f>'[2]Empaque (10)'!F46</f>
         <v>0</v>
       </c>
       <c r="F46" s="51">
-        <f>'[1]Empaque (9)'!G46</f>
+        <f>'[2]Empaque (10)'!G46</f>
         <v>0</v>
       </c>
       <c r="G46" s="68">
-        <f>'[1]Empaque (9)'!H46</f>
+        <f>'[2]Empaque (10)'!H46</f>
         <v>0</v>
       </c>
       <c r="H46" s="67">
-        <f>'[1]Empaque (9)'!I46</f>
+        <f>'[2]Empaque (10)'!I46</f>
         <v>0</v>
       </c>
       <c r="I46" s="53">
-        <f>'[1]Empaque (9)'!J46</f>
+        <f>'[2]Empaque (10)'!J46</f>
         <v>0</v>
       </c>
       <c r="J46" s="54">
-        <f>'[1]Empaque (9)'!K46</f>
+        <f>'[2]Empaque (10)'!K46</f>
         <v>0</v>
       </c>
       <c r="K46" s="69"/>
@@ -12532,43 +12507,43 @@
     </row>
     <row r="47" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="79" t="str">
-        <f>'[1]Empaque (9)'!A47</f>
+        <f>'[2]Empaque (10)'!A47</f>
         <v>Mixto</v>
       </c>
       <c r="B47" s="175">
-        <f>'[1]Empaque (9)'!B47</f>
+        <f>'[2]Empaque (10)'!B47</f>
         <v>0</v>
       </c>
       <c r="C47" s="81">
-        <f>'[1]Empaque (9)'!C47</f>
+        <f>'[2]Empaque (10)'!C47</f>
         <v>0</v>
       </c>
       <c r="D47" s="82" t="str">
-        <f>'[1]Empaque (9)'!D47</f>
+        <f>'[2]Empaque (10)'!D47</f>
         <v/>
       </c>
       <c r="E47" s="83">
-        <f>'[1]Empaque (9)'!F47</f>
+        <f>'[2]Empaque (10)'!F47</f>
         <v>0</v>
       </c>
       <c r="F47" s="84">
-        <f>'[1]Empaque (9)'!G47</f>
+        <f>'[2]Empaque (10)'!G47</f>
         <v>0</v>
       </c>
       <c r="G47" s="85">
-        <f>'[1]Empaque (9)'!H47</f>
+        <f>'[2]Empaque (10)'!H47</f>
         <v>0</v>
       </c>
       <c r="H47" s="81">
-        <f>'[1]Empaque (9)'!I47</f>
+        <f>'[2]Empaque (10)'!I47</f>
         <v>0</v>
       </c>
       <c r="I47" s="86">
-        <f>'[1]Empaque (9)'!J47</f>
+        <f>'[2]Empaque (10)'!J47</f>
         <v>0</v>
       </c>
       <c r="J47" s="87">
-        <f>'[1]Empaque (9)'!K47</f>
+        <f>'[2]Empaque (10)'!K47</f>
         <v>0</v>
       </c>
       <c r="K47" s="88"/>
@@ -12593,35 +12568,35 @@
     </row>
     <row r="48" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C48" s="96">
-        <f>'[1]Empaque (9)'!C48</f>
+        <f>'[2]Empaque (10)'!C48</f>
         <v>0</v>
       </c>
       <c r="D48" s="97" t="str">
-        <f>'[1]Empaque (9)'!D48</f>
+        <f>'[2]Empaque (10)'!D48</f>
         <v/>
       </c>
       <c r="E48" s="98">
-        <f>'[1]Empaque (9)'!F48</f>
+        <f>'[2]Empaque (10)'!F48</f>
         <v>0</v>
       </c>
       <c r="F48" s="99">
-        <f>'[1]Empaque (9)'!G48</f>
+        <f>'[2]Empaque (10)'!G48</f>
         <v>0</v>
       </c>
       <c r="G48" s="100">
-        <f>'[1]Empaque (9)'!H48</f>
+        <f>'[2]Empaque (10)'!H48</f>
         <v>0</v>
       </c>
       <c r="H48" s="100">
-        <f>'[1]Empaque (9)'!I48</f>
+        <f>'[2]Empaque (10)'!I48</f>
         <v>0</v>
       </c>
       <c r="I48" s="100">
-        <f>'[1]Empaque (9)'!J48</f>
+        <f>'[2]Empaque (10)'!J48</f>
         <v>0</v>
       </c>
       <c r="J48" s="101">
-        <f>'[1]Empaque (9)'!K48</f>
+        <f>'[2]Empaque (10)'!K48</f>
         <v>0</v>
       </c>
       <c r="K48" s="102">
@@ -12649,11 +12624,11 @@
     </row>
     <row r="49" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="41" t="str">
-        <f>'[1]Empaque (9)'!A49</f>
+        <f>'[2]Empaque (10)'!A49</f>
         <v>DF Clam 24 Lb x 50</v>
       </c>
       <c r="B49" s="42" t="str">
-        <f>'[1]Empaque (9)'!B49</f>
+        <f>'[2]Empaque (10)'!B49</f>
         <v>lb</v>
       </c>
       <c r="C49" s="109"/>
@@ -12674,11 +12649,11 @@
       <c r="P49" s="58"/>
       <c r="S49" s="10"/>
       <c r="Z49" s="41" t="str">
-        <f>'[1]Empaque (9)'!AA49</f>
+        <f>'[2]Empaque (10)'!AA49</f>
         <v>DF Clam 24 Lb x 50</v>
       </c>
       <c r="AA49" s="44" t="str">
-        <f>'[1]Empaque (9)'!AB49</f>
+        <f>'[2]Empaque (10)'!AB49</f>
         <v>lb</v>
       </c>
       <c r="AE49" s="6" t="s">
@@ -12692,43 +12667,43 @@
     </row>
     <row r="50" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="46" t="str">
-        <f>'[1]Empaque (9)'!A50</f>
+        <f>'[2]Empaque (10)'!A50</f>
         <v>Jb</v>
       </c>
       <c r="B50" s="47">
-        <f>'[1]Empaque (9)'!B50</f>
+        <f>'[2]Empaque (10)'!B50</f>
         <v>24</v>
       </c>
       <c r="C50" s="48">
-        <f>'[1]Empaque (9)'!C50</f>
+        <f>'[2]Empaque (10)'!C50</f>
         <v>0</v>
       </c>
       <c r="D50" s="49" t="str">
-        <f>'[1]Empaque (9)'!D50</f>
+        <f>'[2]Empaque (10)'!D50</f>
         <v/>
       </c>
       <c r="E50" s="50">
-        <f>'[1]Empaque (9)'!F50</f>
+        <f>'[2]Empaque (10)'!F50</f>
         <v>0</v>
       </c>
       <c r="F50" s="51">
-        <f>'[1]Empaque (9)'!G50</f>
+        <f>'[2]Empaque (10)'!G50</f>
         <v>0</v>
       </c>
       <c r="G50" s="52">
-        <f>'[1]Empaque (9)'!H50</f>
+        <f>'[2]Empaque (10)'!H50</f>
         <v>0</v>
       </c>
       <c r="H50" s="48">
-        <f>'[1]Empaque (9)'!I50</f>
+        <f>'[2]Empaque (10)'!I50</f>
         <v>0</v>
       </c>
       <c r="I50" s="53">
-        <f>'[1]Empaque (9)'!J50</f>
+        <f>'[2]Empaque (10)'!J50</f>
         <v>0</v>
       </c>
       <c r="J50" s="117">
-        <f>'[1]Empaque (9)'!K50</f>
+        <f>'[2]Empaque (10)'!K50</f>
         <v>0</v>
       </c>
       <c r="K50" s="55"/>
@@ -12761,19 +12736,19 @@
         <v>0</v>
       </c>
       <c r="Z50" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA50</f>
+        <f>'[2]Empaque (10)'!AA50</f>
         <v>Jb</v>
       </c>
       <c r="AA50" s="61">
-        <f>'[1]Empaque (9)'!AB50</f>
+        <f>'[2]Empaque (10)'!AB50</f>
         <v>24</v>
       </c>
       <c r="AB50" s="62">
-        <f>'[1]Empaque (9)'!AC50</f>
+        <f>'[2]Empaque (10)'!AC50</f>
         <v>0</v>
       </c>
       <c r="AC50" s="63">
-        <f>'[1]Empaque (9)'!AD50</f>
+        <f>'[2]Empaque (10)'!AD50</f>
         <v>0</v>
       </c>
       <c r="AG50" s="64"/>
@@ -12786,43 +12761,43 @@
     </row>
     <row r="51" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="46" t="str">
-        <f>'[1]Empaque (9)'!A51</f>
+        <f>'[2]Empaque (10)'!A51</f>
         <v>Xl</v>
       </c>
       <c r="B51" s="66">
-        <f>'[1]Empaque (9)'!B51</f>
+        <f>'[2]Empaque (10)'!B51</f>
         <v>24</v>
       </c>
       <c r="C51" s="67">
-        <f>'[1]Empaque (9)'!C51</f>
+        <f>'[2]Empaque (10)'!C51</f>
         <v>0</v>
       </c>
       <c r="D51" s="49" t="str">
-        <f>'[1]Empaque (9)'!D51</f>
+        <f>'[2]Empaque (10)'!D51</f>
         <v/>
       </c>
       <c r="E51" s="50">
-        <f>'[1]Empaque (9)'!F51</f>
+        <f>'[2]Empaque (10)'!F51</f>
         <v>0</v>
       </c>
       <c r="F51" s="51">
-        <f>'[1]Empaque (9)'!G51</f>
+        <f>'[2]Empaque (10)'!G51</f>
         <v>0</v>
       </c>
       <c r="G51" s="68">
-        <f>'[1]Empaque (9)'!H51</f>
+        <f>'[2]Empaque (10)'!H51</f>
         <v>0</v>
       </c>
       <c r="H51" s="67">
-        <f>'[1]Empaque (9)'!I51</f>
+        <f>'[2]Empaque (10)'!I51</f>
         <v>0</v>
       </c>
       <c r="I51" s="53">
-        <f>'[1]Empaque (9)'!J51</f>
+        <f>'[2]Empaque (10)'!J51</f>
         <v>0</v>
       </c>
       <c r="J51" s="117">
-        <f>'[1]Empaque (9)'!K51</f>
+        <f>'[2]Empaque (10)'!K51</f>
         <v>0</v>
       </c>
       <c r="K51" s="69"/>
@@ -12840,19 +12815,19 @@
       </c>
       <c r="S51" s="10"/>
       <c r="Z51" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA51</f>
+        <f>'[2]Empaque (10)'!AA51</f>
         <v>Xl</v>
       </c>
       <c r="AA51" s="72">
-        <f>'[1]Empaque (9)'!AB51</f>
+        <f>'[2]Empaque (10)'!AB51</f>
         <v>24</v>
       </c>
       <c r="AB51" s="62">
-        <f>'[1]Empaque (9)'!AC51</f>
+        <f>'[2]Empaque (10)'!AC51</f>
         <v>0</v>
       </c>
       <c r="AC51" s="63">
-        <f>'[1]Empaque (9)'!AD51</f>
+        <f>'[2]Empaque (10)'!AD51</f>
         <v>0</v>
       </c>
       <c r="AG51" s="73"/>
@@ -12865,43 +12840,43 @@
     </row>
     <row r="52" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="46" t="str">
-        <f>'[1]Empaque (9)'!A52</f>
+        <f>'[2]Empaque (10)'!A52</f>
         <v>Lg</v>
       </c>
       <c r="B52" s="47">
-        <f>'[1]Empaque (9)'!B52</f>
+        <f>'[2]Empaque (10)'!B52</f>
         <v>24</v>
       </c>
       <c r="C52" s="67">
-        <f>'[1]Empaque (9)'!C52</f>
+        <f>'[2]Empaque (10)'!C52</f>
         <v>0</v>
       </c>
       <c r="D52" s="49" t="str">
-        <f>'[1]Empaque (9)'!D52</f>
+        <f>'[2]Empaque (10)'!D52</f>
         <v/>
       </c>
       <c r="E52" s="50">
-        <f>'[1]Empaque (9)'!F52</f>
+        <f>'[2]Empaque (10)'!F52</f>
         <v>0</v>
       </c>
       <c r="F52" s="51">
-        <f>'[1]Empaque (9)'!G52</f>
+        <f>'[2]Empaque (10)'!G52</f>
         <v>0</v>
       </c>
       <c r="G52" s="68">
-        <f>'[1]Empaque (9)'!H52</f>
+        <f>'[2]Empaque (10)'!H52</f>
         <v>0</v>
       </c>
       <c r="H52" s="67">
-        <f>'[1]Empaque (9)'!I52</f>
+        <f>'[2]Empaque (10)'!I52</f>
         <v>0</v>
       </c>
       <c r="I52" s="53">
-        <f>'[1]Empaque (9)'!J52</f>
+        <f>'[2]Empaque (10)'!J52</f>
         <v>0</v>
       </c>
       <c r="J52" s="117">
-        <f>'[1]Empaque (9)'!K52</f>
+        <f>'[2]Empaque (10)'!K52</f>
         <v>0</v>
       </c>
       <c r="K52" s="69"/>
@@ -12919,19 +12894,19 @@
       </c>
       <c r="S52" s="10"/>
       <c r="Z52" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA52</f>
+        <f>'[2]Empaque (10)'!AA52</f>
         <v>Lg</v>
       </c>
       <c r="AA52" s="61">
-        <f>'[1]Empaque (9)'!AB52</f>
+        <f>'[2]Empaque (10)'!AB52</f>
         <v>24</v>
       </c>
       <c r="AB52" s="62">
-        <f>'[1]Empaque (9)'!AC52</f>
+        <f>'[2]Empaque (10)'!AC52</f>
         <v>0</v>
       </c>
       <c r="AC52" s="63">
-        <f>'[1]Empaque (9)'!AD52</f>
+        <f>'[2]Empaque (10)'!AD52</f>
         <v>0</v>
       </c>
       <c r="AG52" s="73"/>
@@ -12944,43 +12919,43 @@
     </row>
     <row r="53" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="46" t="str">
-        <f>'[1]Empaque (9)'!A53</f>
+        <f>'[2]Empaque (10)'!A53</f>
         <v>Md</v>
       </c>
       <c r="B53" s="66">
-        <f>'[1]Empaque (9)'!B53</f>
+        <f>'[2]Empaque (10)'!B53</f>
         <v>24</v>
       </c>
       <c r="C53" s="67">
-        <f>'[1]Empaque (9)'!C53</f>
+        <f>'[2]Empaque (10)'!C53</f>
         <v>0</v>
       </c>
       <c r="D53" s="49" t="str">
-        <f>'[1]Empaque (9)'!D53</f>
+        <f>'[2]Empaque (10)'!D53</f>
         <v/>
       </c>
       <c r="E53" s="50">
-        <f>'[1]Empaque (9)'!F53</f>
+        <f>'[2]Empaque (10)'!F53</f>
         <v>0</v>
       </c>
       <c r="F53" s="51">
-        <f>'[1]Empaque (9)'!G53</f>
+        <f>'[2]Empaque (10)'!G53</f>
         <v>0</v>
       </c>
       <c r="G53" s="68">
-        <f>'[1]Empaque (9)'!H53</f>
+        <f>'[2]Empaque (10)'!H53</f>
         <v>0</v>
       </c>
       <c r="H53" s="67">
-        <f>'[1]Empaque (9)'!I53</f>
+        <f>'[2]Empaque (10)'!I53</f>
         <v>0</v>
       </c>
       <c r="I53" s="53">
-        <f>'[1]Empaque (9)'!J53</f>
+        <f>'[2]Empaque (10)'!J53</f>
         <v>0</v>
       </c>
       <c r="J53" s="117">
-        <f>'[1]Empaque (9)'!K53</f>
+        <f>'[2]Empaque (10)'!K53</f>
         <v>0</v>
       </c>
       <c r="K53" s="69"/>
@@ -12998,19 +12973,19 @@
       </c>
       <c r="S53" s="10"/>
       <c r="Z53" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA53</f>
+        <f>'[2]Empaque (10)'!AA53</f>
         <v>Md</v>
       </c>
       <c r="AA53" s="72">
-        <f>'[1]Empaque (9)'!AB53</f>
+        <f>'[2]Empaque (10)'!AB53</f>
         <v>24</v>
       </c>
       <c r="AB53" s="62">
-        <f>'[1]Empaque (9)'!AC53</f>
+        <f>'[2]Empaque (10)'!AC53</f>
         <v>0</v>
       </c>
       <c r="AC53" s="63">
-        <f>'[1]Empaque (9)'!AD53</f>
+        <f>'[2]Empaque (10)'!AD53</f>
         <v>0</v>
       </c>
       <c r="AG53" s="73"/>
@@ -13023,43 +12998,43 @@
     </row>
     <row r="54" spans="1:36" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="46" t="str">
-        <f>'[1]Empaque (9)'!A54</f>
+        <f>'[2]Empaque (10)'!A54</f>
         <v>Sm</v>
       </c>
       <c r="B54" s="47">
-        <f>'[1]Empaque (9)'!B54</f>
+        <f>'[2]Empaque (10)'!B54</f>
         <v>24</v>
       </c>
       <c r="C54" s="67">
-        <f>'[1]Empaque (9)'!C54</f>
+        <f>'[2]Empaque (10)'!C54</f>
         <v>0</v>
       </c>
       <c r="D54" s="49" t="str">
-        <f>'[1]Empaque (9)'!D54</f>
+        <f>'[2]Empaque (10)'!D54</f>
         <v/>
       </c>
       <c r="E54" s="50">
-        <f>'[1]Empaque (9)'!F54</f>
+        <f>'[2]Empaque (10)'!F54</f>
         <v>0</v>
       </c>
       <c r="F54" s="51">
-        <f>'[1]Empaque (9)'!G54</f>
+        <f>'[2]Empaque (10)'!G54</f>
         <v>0</v>
       </c>
       <c r="G54" s="68">
-        <f>'[1]Empaque (9)'!H54</f>
+        <f>'[2]Empaque (10)'!H54</f>
         <v>0</v>
       </c>
       <c r="H54" s="67">
-        <f>'[1]Empaque (9)'!I54</f>
+        <f>'[2]Empaque (10)'!I54</f>
         <v>0</v>
       </c>
       <c r="I54" s="53">
-        <f>'[1]Empaque (9)'!J54</f>
+        <f>'[2]Empaque (10)'!J54</f>
         <v>0</v>
       </c>
       <c r="J54" s="117">
-        <f>'[1]Empaque (9)'!K54</f>
+        <f>'[2]Empaque (10)'!K54</f>
         <v>0</v>
       </c>
       <c r="K54" s="69"/>
@@ -13076,19 +13051,19 @@
         <v>0</v>
       </c>
       <c r="Z54" s="60" t="str">
-        <f>'[1]Empaque (9)'!AA54</f>
+        <f>'[2]Empaque (10)'!AA54</f>
         <v>Sm</v>
       </c>
       <c r="AA54" s="61">
-        <f>'[1]Empaque (9)'!AB54</f>
+        <f>'[2]Empaque (10)'!AB54</f>
         <v>24</v>
       </c>
       <c r="AB54" s="77">
-        <f>'[1]Empaque (9)'!AC54</f>
+        <f>'[2]Empaque (10)'!AC54</f>
         <v>0</v>
       </c>
       <c r="AC54" s="63">
-        <f>'[1]Empaque (9)'!AD54</f>
+        <f>'[2]Empaque (10)'!AD54</f>
         <v>0</v>
       </c>
       <c r="AG54" s="64"/>
@@ -13101,43 +13076,43 @@
     </row>
     <row r="55" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="79" t="str">
-        <f>'[1]Empaque (9)'!A55</f>
+        <f>'[2]Empaque (10)'!A55</f>
         <v>Mixto</v>
       </c>
       <c r="B55" s="85">
-        <f>'[1]Empaque (9)'!B55</f>
+        <f>'[2]Empaque (10)'!B55</f>
         <v>0</v>
       </c>
       <c r="C55" s="81">
-        <f>'[1]Empaque (9)'!C55</f>
+        <f>'[2]Empaque (10)'!C55</f>
         <v>0</v>
       </c>
       <c r="D55" s="82" t="str">
-        <f>'[1]Empaque (9)'!D55</f>
+        <f>'[2]Empaque (10)'!D55</f>
         <v/>
       </c>
       <c r="E55" s="83">
-        <f>'[1]Empaque (9)'!F55</f>
+        <f>'[2]Empaque (10)'!F55</f>
         <v>0</v>
       </c>
       <c r="F55" s="84">
-        <f>'[1]Empaque (9)'!G55</f>
+        <f>'[2]Empaque (10)'!G55</f>
         <v>0</v>
       </c>
       <c r="G55" s="85">
-        <f>'[1]Empaque (9)'!H55</f>
+        <f>'[2]Empaque (10)'!H55</f>
         <v>0</v>
       </c>
       <c r="H55" s="81">
-        <f>'[1]Empaque (9)'!I55</f>
+        <f>'[2]Empaque (10)'!I55</f>
         <v>0</v>
       </c>
       <c r="I55" s="86">
-        <f>'[1]Empaque (9)'!J55</f>
+        <f>'[2]Empaque (10)'!J55</f>
         <v>0</v>
       </c>
       <c r="J55" s="118">
-        <f>'[1]Empaque (9)'!K55</f>
+        <f>'[2]Empaque (10)'!K55</f>
         <v>0</v>
       </c>
       <c r="K55" s="88"/>
@@ -13155,19 +13130,19 @@
         <v>0</v>
       </c>
       <c r="Z55" s="90" t="str">
-        <f>'[1]Empaque (9)'!AA55</f>
+        <f>'[2]Empaque (10)'!AA55</f>
         <v>xs</v>
       </c>
       <c r="AA55" s="91">
-        <f>'[1]Empaque (9)'!AB55</f>
+        <f>'[2]Empaque (10)'!AB55</f>
         <v>0</v>
       </c>
       <c r="AB55" s="92">
-        <f>'[1]Empaque (9)'!AC55</f>
+        <f>'[2]Empaque (10)'!AC55</f>
         <v>0</v>
       </c>
       <c r="AC55" s="93">
-        <f>'[1]Empaque (9)'!AD55</f>
+        <f>'[2]Empaque (10)'!AD55</f>
         <v>0</v>
       </c>
       <c r="AG55" s="94"/>
@@ -13180,35 +13155,35 @@
     </row>
     <row r="56" spans="1:36" ht="15.75" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="C56" s="96">
-        <f>'[1]Empaque (9)'!C56</f>
+        <f>'[2]Empaque (10)'!C56</f>
         <v>0</v>
       </c>
       <c r="D56" s="97" t="str">
-        <f>'[1]Empaque (9)'!D56</f>
+        <f>'[2]Empaque (10)'!D56</f>
         <v/>
       </c>
       <c r="E56" s="98">
-        <f>'[1]Empaque (9)'!F56</f>
+        <f>'[2]Empaque (10)'!F56</f>
         <v>0</v>
       </c>
       <c r="F56" s="99">
-        <f>'[1]Empaque (9)'!G56</f>
+        <f>'[2]Empaque (10)'!G56</f>
         <v>0</v>
       </c>
       <c r="G56" s="100">
-        <f>'[1]Empaque (9)'!H56</f>
+        <f>'[2]Empaque (10)'!H56</f>
         <v>0</v>
       </c>
       <c r="H56" s="100">
-        <f>'[1]Empaque (9)'!I56</f>
+        <f>'[2]Empaque (10)'!I56</f>
         <v>0</v>
       </c>
       <c r="I56" s="100">
-        <f>'[1]Empaque (9)'!J56</f>
+        <f>'[2]Empaque (10)'!J56</f>
         <v>0</v>
       </c>
       <c r="J56" s="119">
-        <f>'[1]Empaque (9)'!K56</f>
+        <f>'[2]Empaque (10)'!K56</f>
         <v>0</v>
       </c>
       <c r="K56" s="102">
@@ -13227,11 +13202,11 @@
       <c r="O56" s="55"/>
       <c r="AA56" s="104"/>
       <c r="AB56" s="105">
-        <f>'[1]Empaque (9)'!AC56</f>
+        <f>'[2]Empaque (10)'!AC56</f>
         <v>0</v>
       </c>
       <c r="AC56" s="106">
-        <f>'[1]Empaque (9)'!AD56</f>
+        <f>'[2]Empaque (10)'!AD56</f>
         <v>0</v>
       </c>
       <c r="AH56" s="107">
@@ -13262,60 +13237,60 @@
         <v>34</v>
       </c>
       <c r="C58" s="96">
-        <f>'[1]Empaque (9)'!C58</f>
-        <v>372</v>
+        <f>'[2]Empaque (10)'!C58</f>
+        <v>287</v>
       </c>
       <c r="E58" s="121">
-        <f>'[1]Empaque (9)'!F59</f>
+        <f>'[2]Empaque (10)'!F59</f>
         <v>0</v>
       </c>
       <c r="F58" s="122">
-        <f>'[1]Empaque (9)'!G58</f>
+        <f>'[2]Empaque (10)'!G58</f>
         <v>0</v>
       </c>
       <c r="G58" s="96">
-        <f>'[1]Empaque (9)'!H58</f>
+        <f>'[2]Empaque (10)'!H58</f>
         <v>0</v>
       </c>
       <c r="H58" s="122">
-        <f>'[1]Empaque (9)'!I58</f>
-        <v>696</v>
+        <f>'[2]Empaque (10)'!I58</f>
+        <v>170</v>
       </c>
       <c r="I58" s="96">
-        <f>'[1]Empaque (9)'!J58</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!J58</f>
+        <v>117</v>
       </c>
       <c r="J58" s="122">
-        <f>'[1]Empaque (9)'!K58</f>
-        <v>0</v>
+        <f>'[2]Empaque (10)'!K58</f>
+        <v>1.625</v>
       </c>
       <c r="K58" s="176">
         <f>(K26*C26)+(K27*C27)+(K28*C28)+(K29*C29)+(K30*C30)+(K31*C31)</f>
-        <v>148800</v>
+        <v>109060</v>
       </c>
       <c r="L58" s="22">
         <f>M58/C58</f>
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="M58" s="123">
         <f>M16+M24+M32+M40+M48+M56</f>
-        <v>135408</v>
+        <v>98728</v>
       </c>
       <c r="P58" s="60" t="s">
         <v>2</v>
       </c>
       <c r="Q58" s="124">
-        <f>'[1]Empaque (9)'!O58</f>
-        <v>4650</v>
+        <f>'[2]Empaque (10)'!O58</f>
+        <v>3587.5</v>
       </c>
       <c r="Z58" s="1" t="str">
-        <f>'[1]Empaque (9)'!AA58</f>
+        <f>'[2]Empaque (10)'!AA58</f>
         <v>Totales</v>
       </c>
       <c r="AA58" s="104"/>
       <c r="AB58" s="96">
-        <f>'[1]Empaque (9)'!AC58</f>
-        <v>1587</v>
+        <f>'[2]Empaque (10)'!AC58</f>
+        <v>1874</v>
       </c>
       <c r="AC58" s="125"/>
       <c r="AE58" s="43" t="s">
@@ -13345,8 +13320,8 @@
         <v>0</v>
       </c>
       <c r="AB59" s="128">
-        <f>'[1]Empaque (9)'!AC59</f>
-        <v>317.39999999999998</v>
+        <f>'[2]Empaque (10)'!AC59</f>
+        <v>267.71428571428572</v>
       </c>
       <c r="AC59" s="20" t="s">
         <v>35</v>
@@ -13357,15 +13332,15 @@
         <v>35</v>
       </c>
       <c r="C60" s="130">
-        <f>'[1]Empaque (9)'!C60</f>
-        <v>297.60000000000002</v>
+        <f>'[2]Empaque (10)'!C60</f>
+        <v>229.6</v>
       </c>
       <c r="I60" s="177" t="s">
         <v>21</v>
       </c>
       <c r="J60" s="178">
         <f>I32+I40</f>
-        <v>0</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:36" x14ac:dyDescent="0.3">
@@ -13386,7 +13361,7 @@
       </c>
       <c r="AB62" s="134">
         <f>(AB10+AB11+AB12+AB18+AB19+AB20+AB26+AB27+AB28+AB34+AB35+AB36)/AB58</f>
-        <v>0.96471329552614993</v>
+        <v>0.96051227321237997</v>
       </c>
     </row>
     <row r="63" spans="1:36" x14ac:dyDescent="0.3">
@@ -13399,15 +13374,15 @@
         <v>2</v>
       </c>
       <c r="G63" s="135">
-        <f>'[1]Empaque (9)'!R2</f>
-        <v>4650</v>
+        <f>'[2]Empaque (10)'!R2</f>
+        <v>3587.5</v>
       </c>
       <c r="H63" s="136">
-        <f ca="1">'[1]Empaque (9)'!S2</f>
-        <v>0.90921533738732574</v>
+        <f ca="1">'[2]Empaque (10)'!S2</f>
+        <v>0.91535370287682605</v>
       </c>
       <c r="I63" s="6" t="str">
-        <f>'[1]Empaque (9)'!T2</f>
+        <f>'[2]Empaque (10)'!T2</f>
         <v>% emp kg</v>
       </c>
       <c r="Z63" s="133" t="s">
@@ -13415,7 +13390,7 @@
       </c>
       <c r="AB63" s="137">
         <f>(AB10+AB11+AB18+AB19+AB26+AB27+AB34+AB35)/AB58</f>
-        <v>0.92375551354757401</v>
+        <v>0.91515474919957307</v>
       </c>
     </row>
     <row r="64" spans="1:36" x14ac:dyDescent="0.3">
@@ -13423,26 +13398,26 @@
         <v>41</v>
       </c>
       <c r="B64" s="138">
-        <f>'[1]Empaque (9)'!N3</f>
+        <f>'[2]Empaque (10)'!N3</f>
         <v>0</v>
       </c>
       <c r="C64" s="139">
-        <f>'[1]Empaque (9)'!O3</f>
+        <f>'[2]Empaque (10)'!O3</f>
         <v>0</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G64" s="140">
-        <f>'[1]Empaque (9)'!R3</f>
-        <v>0.96505376344086025</v>
+        <f>'[2]Empaque (10)'!R3</f>
+        <v>0.93728222996515675</v>
       </c>
       <c r="H64" s="141">
-        <f>'[1]Empaque (9)'!S3</f>
-        <v>0.91129032258064513</v>
+        <f>'[2]Empaque (10)'!S3</f>
+        <v>0.86759581881533099</v>
       </c>
       <c r="I64" s="142" t="str">
-        <f>'[1]Empaque (9)'!T3</f>
+        <f>'[2]Empaque (10)'!T3</f>
         <v>Jb, XL</v>
       </c>
       <c r="Z64" s="1"/>
@@ -13452,26 +13427,26 @@
         <v>43</v>
       </c>
       <c r="B65" s="143">
-        <f ca="1">'[1]Empaque (9)'!N4</f>
-        <v>13.266666666666667</v>
+        <f ca="1">'[2]Empaque (10)'!N4</f>
+        <v>10.166666666666666</v>
       </c>
       <c r="C65" s="139">
-        <f ca="1">'[1]Empaque (9)'!O4</f>
-        <v>5114.3</v>
+        <f ca="1">'[2]Empaque (10)'!O4</f>
+        <v>3919.2499999999995</v>
       </c>
       <c r="G65" s="179">
-        <f ca="1">'[1]Empaque (9)'!R4</f>
-        <v>0.9346733668341709</v>
+        <f ca="1">'[2]Empaque (10)'!R4</f>
+        <v>0.94098360655737701</v>
       </c>
       <c r="H65" s="20" t="str">
-        <f>'[1]Empaque (9)'!S4</f>
+        <f>'[2]Empaque (10)'!S4</f>
         <v>cajas x cubeta</v>
       </c>
       <c r="Z65" s="144" t="s">
         <v>44</v>
       </c>
       <c r="AB65" s="145" t="e">
-        <f>SUMIFS([1]Listado!H6:H100,[1]Listado!B6:B135,"&gt;="&amp;AE1,[1]Listado!B6:B135,"&lt;="&amp;AF1)</f>
+        <f>SUMIFS([2]Listado!H6:H100,[2]Listado!B6:B135,"&gt;="&amp;AE1,[2]Listado!B6:B135,"&lt;="&amp;AF1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -13480,29 +13455,29 @@
         <v>45</v>
       </c>
       <c r="B66" s="138">
-        <f ca="1">'[1]Empaque (9)'!N5</f>
+        <f ca="1">'[2]Empaque (10)'!N5</f>
         <v>0</v>
       </c>
       <c r="C66" s="139">
-        <f ca="1">'[1]Empaque (9)'!O5</f>
+        <f ca="1">'[2]Empaque (10)'!O5</f>
         <v>0</v>
       </c>
       <c r="G66" s="146">
-        <f ca="1">'[1]Empaque (9)'!R5</f>
-        <v>28.040201005025125</v>
+        <f ca="1">'[2]Empaque (10)'!R5</f>
+        <v>28.229508196721312</v>
       </c>
       <c r="H66" s="20" t="str">
-        <f>'[1]Empaque (9)'!S5</f>
+        <f>'[2]Empaque (10)'!S5</f>
         <v>Cajas x bin</v>
       </c>
     </row>
     <row r="67" spans="1:28" x14ac:dyDescent="0.3">
       <c r="C67" s="147">
-        <f ca="1">'[1]Empaque (9)'!O6</f>
-        <v>5114.3</v>
+        <f ca="1">'[2]Empaque (10)'!O6</f>
+        <v>3919.2499999999995</v>
       </c>
       <c r="G67" s="2" t="str">
-        <f>'[1]Empaque (9)'!R6</f>
+        <f>'[2]Empaque (10)'!R6</f>
         <v>Por pasar y reproc</v>
       </c>
       <c r="H67" s="2"/>
@@ -13512,18 +13487,18 @@
         <v>46</v>
       </c>
       <c r="C68" s="136">
-        <f>'[1]Empaque (9)'!O7</f>
+        <f>'[2]Empaque (10)'!O7</f>
         <v>0</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>43</v>
       </c>
       <c r="G68" s="148">
-        <f>'[1]Empaque (9)'!R7</f>
+        <f>'[2]Empaque (10)'!R7</f>
         <v>0</v>
       </c>
       <c r="H68" s="149">
-        <f>'[1]Empaque (9)'!S7</f>
+        <f>'[2]Empaque (10)'!S7</f>
         <v>0</v>
       </c>
       <c r="I68" s="37"/>
@@ -13533,18 +13508,18 @@
         <v>47</v>
       </c>
       <c r="C69" s="136">
-        <f>'[1]Empaque (9)'!O8</f>
+        <f>'[2]Empaque (10)'!O8</f>
         <v>1</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>45</v>
       </c>
       <c r="G69" s="148">
-        <f>'[1]Empaque (9)'!R8</f>
+        <f>'[2]Empaque (10)'!R8</f>
         <v>0</v>
       </c>
       <c r="H69" s="149">
-        <f>'[1]Empaque (9)'!S8</f>
+        <f>'[2]Empaque (10)'!S8</f>
         <v>0</v>
       </c>
       <c r="I69" s="37"/>
@@ -13575,12 +13550,12 @@
         <v>45</v>
       </c>
       <c r="B72" s="154">
-        <f ca="1">'[1]Cajas x Semana'!F130</f>
-        <v>372</v>
+        <f ca="1">'[2]Cajas x Semana'!F130</f>
+        <v>659</v>
       </c>
       <c r="C72" s="155">
         <f ca="1">B72/1.25</f>
-        <v>297.60000000000002</v>
+        <v>527.20000000000005</v>
       </c>
       <c r="F72" s="11"/>
       <c r="G72" s="3"/>
@@ -13592,8 +13567,8 @@
         <v>49</v>
       </c>
       <c r="B73" s="156">
-        <f ca="1">'[1]Cajas x Semana'!F132</f>
-        <v>0.91129032258064513</v>
+        <f ca="1">'[2]Cajas x Semana'!F132</f>
+        <v>0.89226100151745069</v>
       </c>
       <c r="C73" s="17"/>
       <c r="F73" s="11"/>
@@ -13615,8 +13590,8 @@
         <v>69</v>
       </c>
       <c r="B76" s="161">
-        <f ca="1">VLOOKUP(G4,'[1]Cajas Acum x Fecha'!$B$11:$I$147,8,FALSE)</f>
-        <v>1269.5999999999999</v>
+        <f ca="1">VLOOKUP(G4,'[2]Cajas Acum x Fecha'!$B$11:$I$147,8,FALSE)</f>
+        <v>1499.2</v>
       </c>
     </row>
     <row r="77" spans="1:28" x14ac:dyDescent="0.3">
@@ -13625,11 +13600,11 @@
       </c>
       <c r="B77" s="161">
         <f>IFERROR(VLOOKUP($G$4-365,'[3]Cajas Acum x Fecha'!$P$10:$Q$125,2,FALSE),0)</f>
-        <v>601.57142857142856</v>
+        <v>862.28571428571433</v>
       </c>
       <c r="C77" s="45">
         <f ca="1">($B$76-B77)/$B77</f>
-        <v>1.1104725718356685</v>
+        <v>0.73863485752153735</v>
       </c>
     </row>
     <row r="78" spans="1:28" x14ac:dyDescent="0.3">
@@ -13638,11 +13613,11 @@
       </c>
       <c r="B78" s="161">
         <f>VLOOKUP(G4-730,'[4]Cajas Acum x Fecha'!$P$10:$Q$125,2,FALSE)</f>
-        <v>2016.2</v>
+        <v>2276.6</v>
       </c>
       <c r="C78" s="45">
         <f ca="1">($B$76-B78)/$B78</f>
-        <v>-0.37030056542009726</v>
+        <v>-0.34147412808574185</v>
       </c>
     </row>
     <row r="79" spans="1:28" x14ac:dyDescent="0.3">
@@ -13651,11 +13626,11 @@
       </c>
       <c r="B79" s="161">
         <f>VLOOKUP(G4-1096,'[5]Cajas Acum x Fecha'!$P$10:$Q$125,2,FALSE)</f>
-        <v>2476.1999999999998</v>
+        <v>3218</v>
       </c>
       <c r="C79" s="45">
         <f ca="1">($B$76-B79)/$B79</f>
-        <v>-0.48727889508117278</v>
+        <v>-0.53412057178371652</v>
       </c>
     </row>
     <row r="80" spans="1:28" x14ac:dyDescent="0.3">
@@ -13714,7 +13689,7 @@
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B90" s="164">
         <f>G4-365</f>
-        <v>45788</v>
+        <v>45790</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -13748,7 +13723,7 @@
         <v>45889</v>
       </c>
       <c r="C96" s="169">
-        <f>[1]Corte!J7</f>
+        <f>[2]Corte!J7</f>
         <v>46134</v>
       </c>
       <c r="D96" s="169">
@@ -13855,6 +13830,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="Z7:Z8"/>
+    <mergeCell ref="AA7:AA8"/>
+    <mergeCell ref="AB7:AB8"/>
+    <mergeCell ref="AC7:AC8"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="A1:C1"/>
@@ -13863,16 +13848,6 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="G4:J4"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="Z7:Z8"/>
-    <mergeCell ref="AA7:AA8"/>
-    <mergeCell ref="AB7:AB8"/>
-    <mergeCell ref="AC7:AC8"/>
   </mergeCells>
   <conditionalFormatting sqref="C85:C87">
     <cfRule type="expression" dxfId="0" priority="1">
